--- a/BOOKING_RESULT_Milan_10_August_2026_15_August_2026_1_guests.xlsx
+++ b/BOOKING_RESULT_Milan_10_August_2026_15_August_2026_1_guests.xlsx
@@ -49,7 +49,31 @@
     <x:t>8.7</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/aiello-hotels-aparthotel-citylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1331556901_405682550_1_2_0&amp;highlighted_blocks=1331556901_405682550_1_2_0&amp;matching_block_id=1331556901_405682550_1_2_0&amp;sr_pri_blocks=1331556901_405682550_1_2_0__96490&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/aiello-hotels-aparthotel-citylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1331556901_405682550_1_2_0&amp;highlighted_blocks=1331556901_405682550_1_2_0&amp;matching_block_id=1331556901_405682550_1_2_0&amp;sr_pri_blocks=1331556901_405682550_1_2_0__96490&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartment with Terrace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Collection CityLife Suites with Terrace - Top Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/collection-city-life-suites-with-terrace-1-top-collection.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1020022002_374798637_1_0_0&amp;highlighted_blocks=1020022002_374798637_1_0_0&amp;matching_block_id=1020022002_374798637_1_0_0&amp;sr_pri_blocks=1020022002_374798637_1_0_0__47518&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easystudio Milan - Solari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easystudio-milan-solari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1057394804_377969332_0_0_0&amp;highlighted_blocks=1057394804_377969332_0_0_0&amp;matching_block_id=1057394804_377969332_0_0_0&amp;sr_pri_blocks=1057394804_377969332_0_0_0__34523&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Apartment</x:t>
@@ -64,7 +88,85 @@
     <x:t>8.4</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-monolocale-zona-washington.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=727243102_342454710_0_0_0&amp;highlighted_blocks=727243102_342454710_0_0_0&amp;matching_block_id=727243102_342454710_0_0_0&amp;sr_pri_blocks=727243102_342454710_0_0_0__38690&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-monolocale-zona-washington.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=727243102_342454710_0_0_0&amp;highlighted_blocks=727243102_342454710_0_0_0&amp;matching_block_id=727243102_342454710_0_0_0&amp;sr_pri_blocks=727243102_342454710_0_0_0__38690&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cozy Studio in Porta Genova - Via Vigevano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cozy-studio-in-porta-genova-via-vigevano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1465916401_417912633_1_0_0&amp;highlighted_blocks=1465916401_417912633_1_0_0&amp;matching_block_id=1465916401_417912633_1_0_0&amp;sr_pri_blocks=1465916401_417912633_1_0_0__39805&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio 1 Milano Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/studio-1-milano-navigli-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1043157301_376704345_1_1_0_554495&amp;highlighted_blocks=1043157301_376704345_1_1_0_554495&amp;matching_block_id=1043157301_376704345_1_1_0_554495&amp;sr_pri_blocks=1043157301_376704345_1_1_0_554495_42550&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - MonteNero 29 D - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beautiful-studio-at-10-mins-from-duomo-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=819226901_344556970_0_0_0&amp;highlighted_blocks=819226901_344556970_0_0_0&amp;matching_block_id=819226901_344556970_0_0_0&amp;sr_pri_blocks=819226901_344556970_0_0_0__39590&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RRRapido apartment - Corso San Gottardo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/rrrapido-apartment-in-corso-san-gottardo-4-people.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1256639301_398209075_1_0_0_568384&amp;highlighted_blocks=1256639301_398209075_1_0_0_568384&amp;matching_block_id=1256639301_398209075_1_0_0_568384&amp;sr_pri_blocks=1256639301_398209075_1_0_0_568384_47250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Double Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Palazzo Quantum 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/palazzo-quantum-1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1187317004_391089422_1_0_0&amp;highlighted_blocks=1187317004_391089422_1_0_0&amp;matching_block_id=1187317004_391089422_1_0_0&amp;sr_pri_blocks=1187317004_391089422_1_0_0__44660&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Smart Apartment - Milan Downtown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/smart-apartment-milan-downtown.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=479462701_152647240_1_0_0&amp;highlighted_blocks=479462701_152647240_1_0_0&amp;matching_block_id=479462701_152647240_1_0_0&amp;sr_pri_blocks=479462701_152647240_1_0_0__37430&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Superior Apartment</x:t>
@@ -76,7 +178,16 @@
     <x:t>143.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/qualys-hotel-nasco.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=8105810_92524515_1_1_0&amp;highlighted_blocks=8105810_92524515_1_1_0&amp;matching_block_id=8105810_92524515_1_1_0&amp;sr_pri_blocks=8105810_92524515_1_1_0__71760&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/qualys-hotel-nasco.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=8105810_92524515_1_1_0&amp;highlighted_blocks=8105810_92524515_1_1_0&amp;matching_block_id=8105810_92524515_1_1_0&amp;sr_pri_blocks=8105810_92524515_1_1_0__71760&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Lounge Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/urban-lounge-apartments-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1398661303_411733212_1_0_0&amp;highlighted_blocks=1398661303_411733212_1_0_0&amp;matching_block_id=1398661303_411733212_1_0_0&amp;sr_pri_blocks=1398661303_411733212_1_0_0__58983&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Appartamento</x:t>
@@ -91,7 +202,7 @@
     <x:t>8.2</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-penthouse-sui-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1073189802_379864802_2_0_0&amp;highlighted_blocks=1073189802_379864802_2_0_0&amp;matching_block_id=1073189802_379864802_2_0_0&amp;sr_pri_blocks=1073189802_379864802_2_0_0__97496&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-penthouse-sui-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1073189802_379864802_2_0_0&amp;highlighted_blocks=1073189802_379864802_2_0_0&amp;matching_block_id=1073189802_379864802_2_0_0&amp;sr_pri_blocks=1073189802_379864802_2_0_0__97496&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Melchiorre Gioia 30 - Centrale</x:t>
@@ -103,22 +214,196 @@
     <x:t>8.9</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-incantevole-abitazione-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1067604802_411297452_2_0_0&amp;highlighted_blocks=1067604802_411297452_2_0_0&amp;matching_block_id=1067604802_411297452_2_0_0&amp;sr_pri_blocks=1067604802_411297452_2_0_0__50615&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-incantevole-abitazione-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1067604802_411297452_2_0_0&amp;highlighted_blocks=1067604802_411297452_2_0_0&amp;matching_block_id=1067604802_411297452_2_0_0&amp;sr_pri_blocks=1067604802_411297452_2_0_0__50615&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milano Apartments Lombardini 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>159.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-apartments-lombardini-1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1222632502_423019779_1_0_0&amp;highlighted_blocks=1222632502_423019779_1_0_0&amp;matching_block_id=1222632502_423019779_1_0_0&amp;sr_pri_blocks=1222632502_423019779_1_0_0__79750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Cerano 6 - Tortona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-il-tuo-spazio-ideale-a-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1391665202_411134582_2_0_0&amp;highlighted_blocks=1391665202_411134582_2_0_0&amp;matching_block_id=1391665202_411134582_2_0_0&amp;sr_pri_blocks=1391665202_411134582_2_0_0__53018&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loft</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milan Royal Suites - Centro Cadorna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>161.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-magenta-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=86366116_88472507_2_0_0&amp;highlighted_blocks=86366116_88472507_2_0_0&amp;matching_block_id=86366116_88472507_2_0_0&amp;sr_pri_blocks=86366116_88472507_2_0_0__80926&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio Apartment with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Cloud Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/urban-cloud-by-blue-velvet-livings.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1283884502_401326573_1_0_0&amp;highlighted_blocks=1283884502_401326573_1_0_0&amp;matching_block_id=1283884502_401326573_1_0_0&amp;sr_pri_blocks=1283884502_401326573_1_0_0__46466&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[City life-Milano]Bright suite - Relax&amp;Deluxe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/city-life-milano-bright-suite-relax-amp-deluxe.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=957195001_368340079_2_0_0&amp;highlighted_blocks=957195001_368340079_2_0_0&amp;matching_block_id=957195001_368340079_2_0_0&amp;sr_pri_blocks=957195001_368340079_2_0_0__45800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residenza delle Città</x:t>
+  </x:si>
+  <x:si>
+    <x:t>136.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-delle-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=4270803_381695069_2_0_0&amp;highlighted_blocks=4270803_381695069_2_0_0&amp;matching_block_id=4270803_381695069_2_0_0&amp;sr_pri_blocks=4270803_381695069_2_0_0__68301&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>King Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Collection Moscova Suites 8 - Top Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/via-volta-apartment-moscova.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=643475901_403644755_2_0_0&amp;highlighted_blocks=643475901_403644755_2_0_0&amp;matching_block_id=643475901_403644755_2_0_0&amp;sr_pri_blocks=643475901_403644755_2_0_0__72370&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASATI CENTRAL STATION Metro M1, M2, M3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/casati-central-station-metro-m1-m2-m3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1366308501_408912923_2_0_0&amp;highlighted_blocks=1366308501_408912923_2_0_0&amp;matching_block_id=1366308501_408912923_2_0_0&amp;sr_pri_blocks=1366308501_408912923_2_0_0__73056&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Two-Bedroom Apartment</x:t>
   </x:si>
   <x:si>
+    <x:t>BnButler - Cesare Brivio, 21 - Ampio e Luminoso</x:t>
+  </x:si>
+  <x:si>
+    <x:t>129.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brivio-21-ampio-e-luminoso.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=979437801_370203701_2_0_0&amp;highlighted_blocks=979437801_370203701_2_0_0&amp;matching_block_id=979437801_370203701_2_0_0&amp;sr_pri_blocks=979437801_370203701_2_0_0__64568&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
     <x:t>Brand New Milano Porta Ticinese 70</x:t>
   </x:si>
   <x:si>
     <x:t>100.2</x:t>
   </x:si>
   <x:si>
-    <x:t>8.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brand-new-milano-porta-ticinese-70.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1351224001_408190950_1_0_0&amp;highlighted_blocks=1351224001_408190950_1_0_0&amp;matching_block_id=1351224001_408190950_1_0_0&amp;sr_pri_blocks=1351224001_408190950_1_0_0__50105&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/brand-new-milano-porta-ticinese-70.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1351224001_408190950_1_0_0&amp;highlighted_blocks=1351224001_408190950_1_0_0&amp;matching_block_id=1351224001_408190950_1_0_0&amp;sr_pri_blocks=1351224001_408190950_1_0_0__50105&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chichouse Maderno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/chichouse-maderno.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=26&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1274893601_400341987_1_0_0&amp;highlighted_blocks=1274893601_400341987_1_0_0&amp;matching_block_id=1274893601_400341987_1_0_0&amp;sr_pri_blocks=1274893601_400341987_1_0_0__49225&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe King Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hbhall Residenze Darsena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/blu-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=27&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=101681818_88400138_2_0_0&amp;highlighted_blocks=101681818_88400138_2_0_0&amp;matching_block_id=101681818_88400138_2_0_0&amp;sr_pri_blocks=101681818_88400138_2_0_0__46699&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment with City View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Garibaldi 59 apartments in Brera district by Rentopolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>145.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/corso-garibaldi-modern-cozy-suite-by-rentopolis.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=28&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1307085603_403526015_1_0_0&amp;highlighted_blocks=1307085603_403526015_1_0_0&amp;matching_block_id=1307085603_403526015_1_0_0&amp;sr_pri_blocks=1307085603_403526015_1_0_0__72652&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Elite apartments in Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elite-apartments-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=29&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1402940003_412109324_2_0_0&amp;highlighted_blocks=1402940003_412109324_2_0_0&amp;matching_block_id=1402940003_412109324_2_0_0&amp;sr_pri_blocks=1402940003_412109324_2_0_0__47171&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nolo 5 - Apartment Milano - Leia Hospitality</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nolo-5-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=30&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1392076801_411171430_1_0_0&amp;highlighted_blocks=1392076801_411171430_1_0_0&amp;matching_block_id=1392076801_411171430_1_0_0&amp;sr_pri_blocks=1392076801_411171430_1_0_0__50635&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartment - Ground Floor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Villa Massari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/italian-residencies-villa-massari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=31&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=970311603_369428409_2_0_0&amp;highlighted_blocks=970311603_369428409_2_0_0&amp;matching_block_id=970311603_369428409_2_0_0&amp;sr_pri_blocks=970311603_369428409_2_0_0__51145&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Carducci 22 - Sant Ambrogio</x:t>
@@ -127,25 +412,43 @@
     <x:t>124.8</x:t>
   </x:si>
   <x:si>
-    <x:t>9.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-comoda-residenza-con-terrazzino-abitabile-in-zona-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=983710002_370801600_2_0_0&amp;highlighted_blocks=983710002_370801600_2_0_0&amp;matching_block_id=983710002_370801600_2_0_0&amp;sr_pri_blocks=983710002_370801600_2_0_0__62437&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Apartment with Terrace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Collection CityLife Suites with Terrace - Top Collection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/collection-city-life-suites-with-terrace-1-top-collection.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1020022002_374798637_1_0_0&amp;highlighted_blocks=1020022002_374798637_1_0_0&amp;matching_block_id=1020022002_374798637_1_0_0&amp;sr_pri_blocks=1020022002_374798637_1_0_0__47518&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-comoda-residenza-con-terrazzino-abitabile-in-zona-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=32&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=983710002_370801600_2_0_0&amp;highlighted_blocks=983710002_370801600_2_0_0&amp;matching_block_id=983710002_370801600_2_0_0&amp;sr_pri_blocks=983710002_370801600_2_0_0__62437&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milan Downtown Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>181.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-cozy-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=33&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=832001102_348396804_1_0_0&amp;highlighted_blocks=832001102_348396804_1_0_0&amp;matching_block_id=832001102_348396804_1_0_0&amp;sr_pri_blocks=832001102_348396804_1_0_0__90788&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luxury Apartments Fioravanti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>182.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/luxury-apartment-fioravanti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=34&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=321708604_380687466_1_0_0_663512&amp;highlighted_blocks=321708604_380687466_1_0_0_663512&amp;matching_block_id=321708604_380687466_1_0_0_663512&amp;sr_pri_blocks=321708604_380687466_1_0_0_663512_91087&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marco Polo Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>148.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/marco-polo-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=36&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=772964101_335686385_1_0_0_704773&amp;highlighted_blocks=772964101_335686385_1_0_0_704773&amp;matching_block_id=772964101_335686385_1_0_0_704773&amp;sr_pri_blocks=772964101_335686385_1_0_0_704773_74250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Dugnani 4 - Sant' Ambrogio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-comfortable-apartment-in-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=39&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1240198501_395931229_2_0_0&amp;highlighted_blocks=1240198501_395931229_2_0_0&amp;matching_block_id=1240198501_395931229_2_0_0&amp;sr_pri_blocks=1240198501_395931229_2_0_0__45841&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Magenta 83D - Magenta</x:t>
@@ -154,16 +457,97 @@
     <x:t>99.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-monolocale-in-corso-magenta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=955454602_368326497_2_0_0&amp;highlighted_blocks=955454602_368326497_2_0_0&amp;matching_block_id=955454602_368326497_2_0_0&amp;sr_pri_blocks=955454602_368326497_2_0_0__49770&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easystudio Milan - Solari</x:t>
-  </x:si>
-  <x:si>
-    <x:t>69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easystudio-milan-solari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1057394804_377969332_0_0_0&amp;highlighted_blocks=1057394804_377969332_0_0_0&amp;matching_block_id=1057394804_377969332_0_0_0&amp;sr_pri_blocks=1057394804_377969332_0_0_0__34523&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-monolocale-in-corso-magenta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=40&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=955454602_368326497_2_0_0&amp;highlighted_blocks=955454602_368326497_2_0_0&amp;matching_block_id=955454602_368326497_2_0_0&amp;sr_pri_blocks=955454602_368326497_2_0_0__49770&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano- Privata Angera 10S - Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-appartamento-di-design-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=41&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1069179902_379418625_2_0_0&amp;highlighted_blocks=1069179902_379418625_2_0_0&amp;matching_block_id=1069179902_379418625_2_0_0&amp;sr_pri_blocks=1069179902_379418625_2_0_0__47859&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Villa Aida</x:t>
+  </x:si>
+  <x:si>
+    <x:t>199.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/villa-aida.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=42&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=150415805_91955825_1_2_0_743654&amp;highlighted_blocks=150415805_91955825_1_2_0_743654&amp;matching_block_id=150415805_91955825_1_2_0_743654&amp;sr_pri_blocks=150415805_91955825_1_2_0_743654_99819&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Golden Prestige</x:t>
+  </x:si>
+  <x:si>
+    <x:t>184.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/luxury-flat-repubblica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=43&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=332276103_115726847_1_0_0&amp;highlighted_blocks=332276103_115726847_1_0_0&amp;matching_block_id=332276103_115726847_1_0_0&amp;sr_pri_blocks=332276103_115726847_1_0_0__92333&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frisi 3 City Center Suite - B Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/frisi-3-city-center-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=45&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1347983901_407144368_2_0_0&amp;highlighted_blocks=1347983901_407144368_2_0_0&amp;matching_block_id=1347983901_407144368_2_0_0&amp;sr_pri_blocks=1347983901_407144368_2_0_0__57485&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bramante Luxury Apartments by InnStay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bramante-luxury-apartments-by-innstay.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=46&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1392064301_411170762_1_0_0&amp;highlighted_blocks=1392064301_411170762_1_0_0&amp;matching_block_id=1392064301_411170762_1_0_0&amp;sr_pri_blocks=1392064301_411170762_1_0_0__66017&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ca Foscari Pop Naviglio ,2 camere 2 bagni</x:t>
+  </x:si>
+  <x:si>
+    <x:t>154.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ca-foscari-pop-naviglio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=47&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1167981801_389372607_1_0_0_295248&amp;highlighted_blocks=1167981801_389372607_1_0_0_295248&amp;matching_block_id=1167981801_389372607_1_0_0_295248&amp;sr_pri_blocks=1167981801_389372607_1_0_0_295248_77323&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUOMO VIEW - 2 min from Duomo Amazing location</x:t>
+  </x:si>
+  <x:si>
+    <x:t>173.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/duomo-view-2-min-from-duomo-amazing-location.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=49&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1132300201_385862129_2_0_0&amp;highlighted_blocks=1132300201_385862129_2_0_0&amp;matching_block_id=1132300201_385862129_2_0_0&amp;sr_pri_blocks=1132300201_385862129_2_0_0__86612&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUOMO - The Warm Maison - EXCLUSIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>154.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-warm-maison-duomo-700m.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=50&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=947727801_367351474_2_0_0&amp;highlighted_blocks=947727801_367351474_2_0_0&amp;matching_block_id=947727801_367351474_2_0_0&amp;sr_pri_blocks=947727801_367351474_2_0_0__77062&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Garden Lofts by Blue Velvet Livings</x:t>
+  </x:si>
+  <x:si>
+    <x:t>141.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/homie-urbangarden.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=51&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1105689204_383384584_1_0_0&amp;highlighted_blocks=1105689204_383384584_1_0_0&amp;matching_block_id=1105689204_383384584_1_0_0&amp;sr_pri_blocks=1105689204_383384584_1_0_0__70758&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>One-Bedroom Apartment (2 Adults)</x:t>
@@ -175,19 +559,58 @@
     <x:t>90.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/bb-hotels-aparthotel-visconti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=175892501_362128576_2_0_0&amp;highlighted_blocks=175892501_362128576_2_0_0&amp;matching_block_id=175892501_362128576_2_0_0&amp;sr_pri_blocks=175892501_362128576_2_0_0__45250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cozy Studio in Porta Genova - Via Vigevano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/cozy-studio-in-porta-genova-via-vigevano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1465916401_417912633_1_0_0&amp;highlighted_blocks=1465916401_417912633_1_0_0&amp;matching_block_id=1465916401_417912633_1_0_0&amp;sr_pri_blocks=1465916401_417912633_1_0_0__39805&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/bb-hotels-aparthotel-visconti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=52&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=175892501_362128576_2_0_0&amp;highlighted_blocks=175892501_362128576_2_0_0&amp;matching_block_id=175892501_362128576_2_0_0&amp;sr_pri_blocks=175892501_362128576_2_0_0__45250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - G Emiliani 1 114 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/114-amazing-flat-fully-furnished-in-pta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=53&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=414189201_126132005_2_0_0&amp;highlighted_blocks=414189201_126132005_2_0_0&amp;matching_block_id=414189201_126132005_2_0_0&amp;sr_pri_blocks=414189201_126132005_2_0_0__48297&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Duomo Deluxe Apartments #5-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-duomo-deluxe-apartments-5-11.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=54&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1389031004_410897819_2_0_0&amp;highlighted_blocks=1389031004_410897819_2_0_0&amp;matching_block_id=1389031004_410897819_2_0_0&amp;sr_pri_blocks=1389031004_410897819_2_0_0__57954&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milano Citylife Suites - Fully equipped apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-citylife-suites-fully-equipped-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=55&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1343072003_406686920_2_0_0&amp;highlighted_blocks=1343072003_406686920_2_0_0&amp;matching_block_id=1343072003_406686920_2_0_0&amp;sr_pri_blocks=1343072003_406686920_2_0_0__62487&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUVI - Savona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/luvi-savona.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=56&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1499858701_421654746_2_0_0&amp;highlighted_blocks=1499858701_421654746_2_0_0&amp;matching_block_id=1499858701_421654746_2_0_0&amp;sr_pri_blocks=1499858701_421654746_2_0_0__59520&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bellevue Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>198.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bellevue-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=57&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=866211901_354824185_1_0_0_263875&amp;highlighted_blocks=866211901_354824185_1_0_0_263875&amp;matching_block_id=866211901_354824185_1_0_0_263875&amp;sr_pri_blocks=866211901_354824185_1_0_0_263875_99174&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Medium Studio with Kitchenette and Balcony</x:t>
@@ -199,46 +622,52 @@
     <x:t>106.4</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/numa-milan-sempione.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1244681402_396582596_1_0_0_1190352&amp;highlighted_blocks=1244681402_396582596_1_0_0_1190352&amp;matching_block_id=1244681402_396582596_1_0_0_1190352&amp;sr_pri_blocks=1244681402_396582596_1_0_0_1190352_53200&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio with Balcony</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio 1 Milano Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/studio-1-milano-navigli-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1043157301_376704345_1_1_0_554495&amp;highlighted_blocks=1043157301_376704345_1_1_0_554495&amp;matching_block_id=1043157301_376704345_1_1_0_554495&amp;sr_pri_blocks=1043157301_376704345_1_1_0_554495_42550&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - MonteNero 29 D - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beautiful-studio-at-10-mins-from-duomo-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=819226901_344556970_0_0_0&amp;highlighted_blocks=819226901_344556970_0_0_0&amp;matching_block_id=819226901_344556970_0_0_0&amp;sr_pri_blocks=819226901_344556970_0_0_0__39590&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RRRapido apartment - Corso San Gottardo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/rrrapido-apartment-in-corso-san-gottardo-4-people.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1256639301_398209075_1_0_0_568384&amp;highlighted_blocks=1256639301_398209075_1_0_0_568384&amp;matching_block_id=1256639301_398209075_1_0_0_568384&amp;sr_pri_blocks=1256639301_398209075_1_0_0_568384_47250&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/numa-milan-sempione.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=59&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1244681402_396582596_1_0_0_1190352&amp;highlighted_blocks=1244681402_396582596_1_0_0_1190352&amp;matching_block_id=1244681402_396582596_1_0_0_1190352&amp;sr_pri_blocks=1244681402_396582596_1_0_0_1190352_53200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Game On Apt - Corso Vercelli by InnStay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/game-on-apt-corso-vercelli-by-innstay.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=61&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1344161301_406785908_2_0_0&amp;highlighted_blocks=1344161301_406785908_2_0_0&amp;matching_block_id=1344161301_406785908_2_0_0&amp;sr_pri_blocks=1344161301_406785908_2_0_0__92270&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESIGN APARTMENT - Spadolini, Campus Bocconi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>136.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/design-apartment-spadolini-campus-bocconi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=62&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=974140201_369797365_2_0_0&amp;highlighted_blocks=974140201_369797365_2_0_0&amp;matching_block_id=974140201_369797365_2_0_0&amp;sr_pri_blocks=974140201_369797365_2_0_0__68055&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Teodosio 15 - Lambrate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-colorato-studio-con-terrazzo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=63&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1025164002_411297676_2_0_0&amp;highlighted_blocks=1025164002_411297676_2_0_0&amp;matching_block_id=1025164002_411297676_2_0_0&amp;sr_pri_blocks=1025164002_411297676_2_0_0__41685&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe One-Bedroom Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Central Station Design Suites - B Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/central-station-design-suites-b-home-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=65&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1444849001_415905141_2_0_0&amp;highlighted_blocks=1444849001_415905141_2_0_0&amp;matching_block_id=1444849001_415905141_2_0_0&amp;sr_pri_blocks=1444849001_415905141_2_0_0__51560&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Navigli Cozy Corner - La Vista Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>104.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/navigli-cozy-corner-la-vista-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=66&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1538125001_425343543_2_0_0&amp;highlighted_blocks=1538125001_425343543_2_0_0&amp;matching_block_id=1538125001_425343543_2_0_0&amp;sr_pri_blocks=1538125001_425343543_2_0_0__52446&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Friuli 15 - Porta Romana</x:t>
@@ -247,22 +676,49 @@
     <x:t>94</x:t>
   </x:si>
   <x:si>
-    <x:t>8.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/stupendo-e-accogliente-apt-15-min-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=609060802_277504331_2_0_0&amp;highlighted_blocks=609060802_277504331_2_0_0&amp;matching_block_id=609060802_277504331_2_0_0&amp;sr_pri_blocks=609060802_277504331_2_0_0__46959&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Deluxe Double Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Palazzo Quantum 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/palazzo-quantum-1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1187317004_391089422_1_0_0&amp;highlighted_blocks=1187317004_391089422_1_0_0&amp;matching_block_id=1187317004_391089422_1_0_0&amp;sr_pri_blocks=1187317004_391089422_1_0_0__44660&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/stupendo-e-accogliente-apt-15-min-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=70&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=609060802_277504331_2_0_0&amp;highlighted_blocks=609060802_277504331_2_0_0&amp;matching_block_id=609060802_277504331_2_0_0&amp;sr_pri_blocks=609060802_277504331_2_0_0__46959&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eleven Suites - Cozy apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>111.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/eleven-suites-cozy-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=72&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1226394103_395701254_2_0_0&amp;highlighted_blocks=1226394103_395701254_2_0_0&amp;matching_block_id=1226394103_395701254_2_0_0&amp;sr_pri_blocks=1226394103_395701254_2_0_0__55806&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Bixio 17 - Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>137.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-milano-bixio-17-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=73&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1500100301_421675795_0_0_0&amp;highlighted_blocks=1500100301_421675795_0_0_0&amp;matching_block_id=1500100301_421675795_0_0_0&amp;sr_pri_blocks=1500100301_421675795_0_0_0__68768&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appartamento delizioso, vicino a Fiera, Duomo, San Siro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/casa-andry-vicino-a-fiera-duomo-san-siro.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=74&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1341018101_406509649_1_0_0&amp;highlighted_blocks=1341018101_406509649_1_0_0&amp;matching_block_id=1341018101_406509649_1_0_0&amp;sr_pri_blocks=1341018101_406509649_1_0_0__45815&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Navigli Design Apartment with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/navigli-comfy-location.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=75&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1042185701_376636488_1_0_0_586913&amp;highlighted_blocks=1042185701_376636488_1_0_0_586913&amp;matching_block_id=1042185701_376636488_1_0_0_586913&amp;sr_pri_blocks=1042185701_376636488_1_0_0_586913_45750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior One-Bedroom Apartment with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cefalonia Garden with Terrace &amp; Garage by NDP rent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>157.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cefalonia-garden-with-terrace-amp-garage-by-ndp-rent.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=76&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1384074410_423109409_1_0_0_1234024&amp;highlighted_blocks=1384074410_423109409_1_0_0_1234024&amp;matching_block_id=1384074410_423109409_1_0_0_1234024&amp;sr_pri_blocks=1384074410_423109409_1_0_0_1234024_78736&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Michelangelo Navigli Loft Experience - Via Magolfa</x:t>
@@ -271,16 +727,25 @@
     <x:t>75.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/michelangelo-navigli-loft-experience-via-magolfa.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1049649204_377218682_1_0_0&amp;highlighted_blocks=1049649204_377218682_1_0_0&amp;matching_block_id=1049649204_377218682_1_0_0&amp;sr_pri_blocks=1049649204_377218682_1_0_0__37750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Smart Apartment - Milan Downtown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/smart-apartment-milan-downtown.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=479462701_152647240_1_0_0&amp;highlighted_blocks=479462701_152647240_1_0_0&amp;matching_block_id=479462701_152647240_1_0_0&amp;sr_pri_blocks=479462701_152647240_1_0_0__37430&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/michelangelo-navigli-loft-experience-via-magolfa.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=77&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1049649204_377218682_1_0_0&amp;highlighted_blocks=1049649204_377218682_1_0_0&amp;matching_block_id=1049649204_377218682_1_0_0&amp;sr_pri_blocks=1049649204_377218682_1_0_0__37750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RRRapido Apartment - Via Casale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/rrrapido-apartment-in-via-casale-2-people.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=80&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1296030901_402510903_1_0_0_697918&amp;highlighted_blocks=1296030901_402510903_1_0_0_697918&amp;matching_block_id=1296030901_402510903_1_0_0_697918&amp;sr_pri_blocks=1296030901_402510903_1_0_0_697918_40425&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kaizen House - Bilocale De Angeli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/kaizen-house-bilocale-de-angeli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=81&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1047836101_377067817_2_0_0_666063&amp;highlighted_blocks=1047836101_377067817_2_0_0_666063&amp;matching_block_id=1047836101_377067817_2_0_0_666063&amp;sr_pri_blocks=1047836101_377067817_2_0_0_666063_50969&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Crema 23 - Porta Romana</x:t>
@@ -289,7 +754,52 @@
     <x:t>92.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/modern-and-central-apt-in-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=395164201_122892247_2_0_0&amp;highlighted_blocks=395164201_122892247_2_0_0&amp;matching_block_id=395164201_122892247_2_0_0&amp;sr_pri_blocks=395164201_122892247_2_0_0__46266&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/modern-and-central-apt-in-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=82&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=395164201_122892247_2_0_0&amp;highlighted_blocks=395164201_122892247_2_0_0&amp;matching_block_id=395164201_122892247_2_0_0&amp;sr_pri_blocks=395164201_122892247_2_0_0__46266&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Red Dragon Suite - Via Paolo Sarpi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/red-dragon-suite-via-paolo-sarpi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=83&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1328161501_405402817_1_0_0&amp;highlighted_blocks=1328161501_405402817_1_0_0&amp;matching_block_id=1328161501_405402817_1_0_0&amp;sr_pri_blocks=1328161501_405402817_1_0_0__40800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Queen Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Orti House Apartments - total renovation on Apr 2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bright-flat-in-via-orti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=84&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=312357902_113322890_2_0_0&amp;highlighted_blocks=312357902_113322890_2_0_0&amp;matching_block_id=312357902_113322890_2_0_0&amp;sr_pri_blocks=312357902_113322890_2_0_0__67493&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Suite Central Station</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/suite-central-station.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=85&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=607045011_326885500_1_0_0&amp;highlighted_blocks=607045011_326885500_1_0_0&amp;matching_block_id=607045011_326885500_1_0_0&amp;sr_pri_blocks=607045011_326885500_1_0_0__43500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment with Terrace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Buenos Aires 77 A-Buenos Aires</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-appartamento-con-terrazzo-buenos-aires.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=88&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1271585902_399928876_2_0_0&amp;highlighted_blocks=1271585902_399928876_2_0_0&amp;matching_block_id=1271585902_399928876_2_0_0&amp;sr_pri_blocks=1271585902_399928876_2_0_0__54837&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Pier Lombardo 16 - Porta Romana</x:t>
@@ -301,7 +811,7 @@
     <x:t>6.8</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/nice-and-cozy-studio-in-porta-romana-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=794224002_342458649_0_0_0&amp;highlighted_blocks=794224002_342458649_0_0_0&amp;matching_block_id=794224002_342458649_0_0_0&amp;sr_pri_blocks=794224002_342458649_0_0_0__43178&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/nice-and-cozy-studio-in-porta-romana-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=89&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=794224002_342458649_0_0_0&amp;highlighted_blocks=794224002_342458649_0_0_0&amp;matching_block_id=794224002_342458649_0_0_0&amp;sr_pri_blocks=794224002_342458649_0_0_0__43178&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Lecco 11P3 - Porta Venezia</x:t>
@@ -310,16 +820,154 @@
     <x:t>113.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/tropical-and-new-flat-in-porta-venezia-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=881074302_411297533_2_0_0&amp;highlighted_blocks=881074302_411297533_2_0_0&amp;matching_block_id=881074302_411297533_2_0_0&amp;sr_pri_blocks=881074302_411297533_2_0_0__56758&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Urban Lounge Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/urban-lounge-apartments-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1398661303_411733212_1_0_0&amp;highlighted_blocks=1398661303_411733212_1_0_0&amp;matching_block_id=1398661303_411733212_1_0_0&amp;sr_pri_blocks=1398661303_411733212_1_0_0__58983&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/tropical-and-new-flat-in-porta-venezia-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=90&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=881074302_411297533_2_0_0&amp;highlighted_blocks=881074302_411297533_2_0_0&amp;matching_block_id=881074302_411297533_2_0_0&amp;sr_pri_blocks=881074302_411297533_2_0_0__56758&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Mercato 5 - Brera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>105.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-monolocale-di-lusso-in-brera.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=91&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1354728302_407797656_2_0_0&amp;highlighted_blocks=1354728302_407797656_2_0_0&amp;matching_block_id=1354728302_407797656_2_0_0&amp;sr_pri_blocks=1354728302_407797656_2_0_0__52764&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BasicVillage Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>192.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/basicvillage-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=92&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=974823202_369858095_0_0_0&amp;highlighted_blocks=974823202_369858095_0_0_0&amp;matching_block_id=974823202_369858095_0_0_0&amp;sr_pri_blocks=974823202_369858095_0_0_0__96250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elegant Design Apartment[Duomo-Navigli]A/C e WI-FI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>142.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/elegant-design-apartment-duomo-navigli-a-c-e-wi-fi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=94&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1099984901_382857779_2_0_0&amp;highlighted_blocks=1099984901_382857779_2_0_0&amp;matching_block_id=1099984901_382857779_2_0_0&amp;sr_pri_blocks=1099984901_382857779_2_0_0__71050&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - MonteNero 62 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-appartamento-in-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=95&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1010173502_411297344_2_0_0&amp;highlighted_blocks=1010173502_411297344_2_0_0&amp;matching_block_id=1010173502_411297344_2_0_0&amp;sr_pri_blocks=1010173502_411297344_2_0_0__53018&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Nest Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/new-studio-apartment-sauro-orange.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=97&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=708995001_295734320_1_0_0&amp;highlighted_blocks=708995001_295734320_1_0_0&amp;matching_block_id=708995001_295734320_1_0_0&amp;sr_pri_blocks=708995001_295734320_1_0_0__49789&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Casati 2 - Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/stylish-and-new-apt-in-buenos-aires.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=99&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=414868501_126399064_2_0_0&amp;highlighted_blocks=414868501_126399064_2_0_0&amp;matching_block_id=414868501_126399064_2_0_0&amp;sr_pri_blocks=414868501_126399064_2_0_0__51018&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rifugio di Stile tra Tortona e Navigli a pochi passi da M4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/navigli-porta-genova-suite-eleganza-e-comfort-nel-cuore-di-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=100&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1375179401_409666188_2_0_0&amp;highlighted_blocks=1375179401_409666188_2_0_0&amp;matching_block_id=1375179401_409666188_2_0_0&amp;sr_pri_blocks=1375179401_409666188_2_0_0__52950&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EasyTopStay - Sempione Cozy Flat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/sempione-accogliente-appartamento.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=101&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1231700301_395142529_2_0_0_852707&amp;highlighted_blocks=1231700301_395142529_2_0_0_852707&amp;matching_block_id=1231700301_395142529_2_0_0_852707&amp;sr_pri_blocks=1231700301_395142529_2_0_0_852707_48956&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRESTIGE BOUTIQUE HOMES - Arco della Pace 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/prestige-boutique-homes-via-rosmini-11.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=103&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=873812901_356198202_2_0_0_1241765&amp;highlighted_blocks=873812901_356198202_2_0_0_1241765&amp;matching_block_id=873812901_356198202_2_0_0_1241765&amp;sr_pri_blocks=873812901_356198202_2_0_0_1241765_46781&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEA DREAMS - Amendola Fiera near San Siro Stadium</x:t>
+  </x:si>
+  <x:si>
+    <x:t>163.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/dea-dreams-amendola-fiera-apartment-free-wi-fi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=104&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1131107502_385767618_2_0_0&amp;highlighted_blocks=1131107502_385767618_2_0_0&amp;matching_block_id=1131107502_385767618_2_0_0&amp;sr_pri_blocks=1131107502_385767618_2_0_0__81570&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residenza Arcimboldi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>117.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-arcimboldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=105&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1467284602_418048755_2_0_0&amp;highlighted_blocks=1467284602_418048755_2_0_0&amp;matching_block_id=1467284602_418048755_2_0_0&amp;sr_pri_blocks=1467284602_418048755_2_0_0__58550&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Moscati 9A - Sarpi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-moderno-apt-con-terrazzo-in-paolo-sarpi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=106&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=984198602_411297670_2_0_0&amp;highlighted_blocks=984198602_411297670_2_0_0&amp;matching_block_id=984198602_411297670_2_0_0&amp;sr_pri_blocks=984198602_411297670_2_0_0__51397&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Coni Zugna 27 - Solari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-nuovo-bilocale-con-balcone-sagostino.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=108&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1179690302_390440949_2_0_0&amp;highlighted_blocks=1179690302_390440949_2_0_0&amp;matching_block_id=1179690302_390440949_2_0_0&amp;sr_pri_blocks=1179690302_390440949_2_0_0__53118&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luminoso bilocale in Porta Garibaldi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>150.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/luminoso-bilocale-in-porta-garibaldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=111&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1474758001_418880118_2_0_0&amp;highlighted_blocks=1474758001_418880118_2_0_0&amp;matching_block_id=1474758001_418880118_2_0_0&amp;sr_pri_blocks=1474758001_418880118_2_0_0__75378&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Ripa Ticinese 69 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/lovely-apartment-on-the-navigli-river-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=112&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=849768102_411297141_2_0_0&amp;highlighted_blocks=849768102_411297141_2_0_0&amp;matching_block_id=849768102_411297141_2_0_0&amp;sr_pri_blocks=849768102_411297141_2_0_0__53318&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Two-Bedroom Suite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>La Villa bed &amp; breakfast</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/la-villa-bed-amp-breakfast.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=114&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=774698003_404327984_2_1_0&amp;highlighted_blocks=774698003_404327984_2_1_0&amp;matching_block_id=774698003_404327984_2_1_0&amp;sr_pri_blocks=774698003_404327984_2_1_0__81587&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Bike Garage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-bike-garage.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=115&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=495282901_166389842_2_0_0&amp;highlighted_blocks=495282901_166389842_2_0_0&amp;matching_block_id=495282901_166389842_2_0_0&amp;sr_pri_blocks=495282901_166389842_2_0_0__87004&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Standard Triple Studio</x:t>
@@ -331,10 +979,58 @@
     <x:t>97.6</x:t>
   </x:si>
   <x:si>
-    <x:t>9.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/loreto-prestige.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=26&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1239873204_395916420_3_0_0&amp;highlighted_blocks=1239873204_395916420_3_0_0&amp;matching_block_id=1239873204_395916420_3_0_0&amp;sr_pri_blocks=1239873204_395916420_3_0_0__48750&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/loreto-prestige.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=116&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1239873204_395916420_3_0_0&amp;highlighted_blocks=1239873204_395916420_3_0_0&amp;matching_block_id=1239873204_395916420_3_0_0&amp;sr_pri_blocks=1239873204_395916420_3_0_0__48750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Duomo Deluxe Apartments #1-4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-duomo-deluxe-apartments-1-4.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=117&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1388996102_410894722_2_0_0&amp;highlighted_blocks=1388996102_410894722_2_0_0&amp;matching_block_id=1388996102_410894722_2_0_0&amp;sr_pri_blocks=1388996102_410894722_2_0_0__64637&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aprica16 Loft House Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>129.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aprica-16-loft-house-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=118&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=770008001_334792646_1_0_0&amp;highlighted_blocks=770008001_334792646_1_0_0&amp;matching_block_id=770008001_334792646_1_0_0&amp;sr_pri_blocks=770008001_334792646_1_0_0__64779&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Xenia Apartments - Quiet and cozy two-room apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>117.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/quiet-and-cozy-two-room-apartment-20-min-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=119&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1152156201_388008256_2_0_0&amp;highlighted_blocks=1152156201_388008256_2_0_0&amp;matching_block_id=1152156201_388008256_2_0_0&amp;sr_pri_blocks=1152156201_388008256_2_0_0__58676&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano- Vetere 10 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>105.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-appartamento-elegante-moderno-e-accogliente-la-tua-oasi-in-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=120&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=983129002_411297608_2_0_0&amp;highlighted_blocks=983129002_411297608_2_0_0&amp;matching_block_id=983129002_411297608_2_0_0&amp;sr_pri_blocks=983129002_411297608_2_0_0__52737&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUVI - Misurata</x:t>
+  </x:si>
+  <x:si>
+    <x:t>122.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/casa-carmen-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=124&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=974749401_369851095_2_0_0&amp;highlighted_blocks=974749401_369851095_2_0_0&amp;matching_block_id=974749401_369851095_2_0_0&amp;sr_pri_blocks=974749401_369851095_2_0_0__61334&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RRRapido Home in Brera - Via Mercato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/rrrapido-home-in-brera-via-mercato.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=125&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1360208804_408327303_0_0_0&amp;highlighted_blocks=1360208804_408327303_0_0_0&amp;matching_block_id=1360208804_408327303_0_0_0&amp;sr_pri_blocks=1360208804_408327303_0_0_0__48750&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Crocetta 2 P1S - Porta Romana</x:t>
@@ -343,10 +1039,7 @@
     <x:t>108</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-moderno-bilocale-in-zona-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=27&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=913089902_411297669_2_0_0&amp;highlighted_blocks=913089902_411297669_2_0_0&amp;matching_block_id=913089902_411297669_2_0_0&amp;sr_pri_blocks=913089902_411297669_2_0_0__54018&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Superior Studio</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-moderno-bilocale-in-zona-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=126&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=913089902_411297669_2_0_0&amp;highlighted_blocks=913089902_411297669_2_0_0&amp;matching_block_id=913089902_411297669_2_0_0&amp;sr_pri_blocks=913089902_411297669_2_0_0__54018&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Residence 2Gi</x:t>
@@ -355,13 +1048,7 @@
     <x:t>131.4</x:t>
   </x:si>
   <x:si>
-    <x:t>8.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/ajraghi-halldis-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=28&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=122518401_98061898_1_0_0&amp;highlighted_blocks=122518401_98061898_1_0_0&amp;matching_block_id=122518401_98061898_1_0_0&amp;sr_pri_blocks=122518401_98061898_1_0_0__65650&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio</x:t>
+    <x:t>https://www.booking.com/hotel/it/ajraghi-halldis-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=128&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=122518401_98061898_1_0_0&amp;highlighted_blocks=122518401_98061898_1_0_0&amp;matching_block_id=122518401_98061898_1_0_0&amp;sr_pri_blocks=122518401_98061898_1_0_0__65650&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Residenza Cenisio</x:t>
@@ -370,10 +1057,16 @@
     <x:t>83.8</x:t>
   </x:si>
   <x:si>
-    <x:t>7.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/residenza-cenisio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=29&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=28567108_88453047_0_0_0&amp;highlighted_blocks=28567108_88453047_0_0_0&amp;matching_block_id=28567108_88453047_0_0_0&amp;sr_pri_blocks=28567108_88453047_0_0_0__41865&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/residenza-cenisio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=130&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=28567108_88453047_0_0_0&amp;highlighted_blocks=28567108_88453047_0_0_0&amp;matching_block_id=28567108_88453047_0_0_0&amp;sr_pri_blocks=28567108_88453047_0_0_0__41865&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eaylife - Milano - Corso Italia 68P4 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-comfort-e-armonia-sui-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=131&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1391470602_411119641_2_0_0&amp;highlighted_blocks=1391470602_411119641_2_0_0&amp;matching_block_id=1391470602_411119641_2_0_0&amp;sr_pri_blocks=1391470602_411119641_2_0_0__54737&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Urban Hub Apartments</x:t>
@@ -382,7 +1075,7 @@
     <x:t>91.8</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/urban-hub-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=30&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1379458101_410069510_1_0_0&amp;highlighted_blocks=1379458101_410069510_1_0_0&amp;matching_block_id=1379458101_410069510_1_0_0&amp;sr_pri_blocks=1379458101_410069510_1_0_0__45916&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/urban-hub-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=132&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1379458101_410069510_1_0_0&amp;highlighted_blocks=1379458101_410069510_1_0_0&amp;matching_block_id=1379458101_410069510_1_0_0&amp;sr_pri_blocks=1379458101_410069510_1_0_0__45916&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Modrone 28 S1 - Duomo</x:t>
@@ -391,10 +1084,7 @@
     <x:t>114.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/cityscape-milan-design-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=31&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1122526001_385012587_1_0_0&amp;highlighted_blocks=1122526001_385012587_1_0_0&amp;matching_block_id=1122526001_385012587_1_0_0&amp;sr_pri_blocks=1122526001_385012587_1_0_0__57277&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio Apartment</x:t>
+    <x:t>https://www.booking.com/hotel/it/cityscape-milan-design-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=134&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1122526001_385012587_1_0_0&amp;highlighted_blocks=1122526001_385012587_1_0_0&amp;matching_block_id=1122526001_385012587_1_0_0&amp;sr_pri_blocks=1122526001_385012587_1_0_0__57277&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Piranesi 246</x:t>
@@ -403,25 +1093,55 @@
     <x:t>177.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/piranesi-246.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=32&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=340652502_384712436_2_0_0&amp;highlighted_blocks=340652502_384712436_2_0_0&amp;matching_block_id=340652502_384712436_2_0_0&amp;sr_pri_blocks=340652502_384712436_2_0_0__88750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milano Apartments Lombardini 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>159.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milano-apartments-lombardini-1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=33&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1222632502_423019779_1_0_0&amp;highlighted_blocks=1222632502_423019779_1_0_0&amp;matching_block_id=1222632502_423019779_1_0_0&amp;sr_pri_blocks=1222632502_423019779_1_0_0__79750&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/piranesi-246.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=135&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=340652508_384712436_2_0_0&amp;highlighted_blocks=340652508_384712436_2_0_0&amp;matching_block_id=340652508_384712436_2_0_0&amp;sr_pri_blocks=340652508_384712436_2_0_0__88750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piazza Gramsci Amazing Apartment with Balcony - Top Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/piazza-gramsci-amazing-apartment-with-balcony-top-collection.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=136&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1235737801_395512689_1_0_0&amp;highlighted_blocks=1235737801_395512689_1_0_0&amp;matching_block_id=1235737801_395512689_1_0_0&amp;sr_pri_blocks=1235737801_395512689_1_0_0__56520&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mora 9 - The Boutique Suite - B Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mora-9-the-boutique-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=137&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1495046101_421170065_2_0_0&amp;highlighted_blocks=1495046101_421170065_2_0_0&amp;matching_block_id=1495046101_421170065_2_0_0&amp;sr_pri_blocks=1495046101_421170065_2_0_0__64595&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Garibaldi's Gem - La Vista Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/garibaldis-gem-milanos-heart-la-vista-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=138&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1460732202_417378635_2_0_0&amp;highlighted_blocks=1460732202_417378635_2_0_0&amp;matching_block_id=1460732202_417378635_2_0_0&amp;sr_pri_blocks=1460732202_417378635_2_0_0__55543&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Suites in Porta Garibaldi &amp; Chinatown - City Center well connected</x:t>
+  </x:si>
+  <x:si>
+    <x:t>133.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/suites-in-porta-garibaldi-amp-chinatown-city-center-well-connected.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=139&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1249886302_397450220_2_0_0&amp;highlighted_blocks=1249886302_397450220_2_0_0&amp;matching_block_id=1249886302_397450220_2_0_0&amp;sr_pri_blocks=1249886302_397450220_2_0_0__66731&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Podgora 7 - Porta Vittoria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-rifugio-nel-cuore-del-centro-storico-milanese-in-zona-piazz.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=141&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=950694002_411297560_2_0_0&amp;highlighted_blocks=950694002_411297560_2_0_0&amp;matching_block_id=950694002_411297560_2_0_0&amp;sr_pri_blocks=950694002_411297560_2_0_0__51263&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Correnti 24 - Duomo</x:t>
   </x:si>
   <x:si>
-    <x:t>129.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/elegante-e-completamente-arredato-apt-in-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=34&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=414851001_126389632_2_0_0&amp;highlighted_blocks=414851001_126389632_2_0_0&amp;matching_block_id=414851001_126389632_2_0_0&amp;sr_pri_blocks=414851001_126389632_2_0_0__64837&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/elegante-e-completamente-arredato-apt-in-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=144&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=414851001_126389632_2_0_0&amp;highlighted_blocks=414851001_126389632_2_0_0&amp;matching_block_id=414851001_126389632_2_0_0&amp;sr_pri_blocks=414851001_126389632_2_0_0__64837&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Albani 20 - City Life</x:t>
@@ -430,52 +1150,34 @@
     <x:t>138.4</x:t>
   </x:si>
   <x:si>
-    <x:t>9.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-modern-and-spacious-apt-in-fiera-city-life.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=35&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=753188602_342458560_2_0_0&amp;highlighted_blocks=753188602_342458560_2_0_0&amp;matching_block_id=753188602_342458560_2_0_0&amp;sr_pri_blocks=753188602_342458560_2_0_0__69164&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Cerano 6 - Tortona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-il-tuo-spazio-ideale-a-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=36&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1391665202_411134582_2_0_0&amp;highlighted_blocks=1391665202_411134582_2_0_0&amp;matching_block_id=1391665202_411134582_2_0_0&amp;sr_pri_blocks=1391665202_411134582_2_0_0__53018&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loft</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milan Royal Suites - Centro Cadorna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>161.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-magenta-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=37&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=86366116_88472507_2_0_0&amp;highlighted_blocks=86366116_88472507_2_0_0&amp;matching_block_id=86366116_88472507_2_0_0&amp;sr_pri_blocks=86366116_88472507_2_0_0__80926&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[City life-Milano]Bright suite - Relax&amp;Deluxe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/city-life-milano-bright-suite-relax-amp-deluxe.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=38&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=957195001_368340079_2_0_0&amp;highlighted_blocks=957195001_368340079_2_0_0&amp;matching_block_id=957195001_368340079_2_0_0&amp;sr_pri_blocks=957195001_368340079_2_0_0__45800&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Residenza delle Città</x:t>
-  </x:si>
-  <x:si>
-    <x:t>136.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/residenza-delle-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=39&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=4270803_381695069_2_0_0&amp;highlighted_blocks=4270803_381695069_2_0_0&amp;matching_block_id=4270803_381695069_2_0_0&amp;sr_pri_blocks=4270803_381695069_2_0_0__68301&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-modern-and-spacious-apt-in-fiera-city-life.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=146&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=753188602_342458560_2_0_0&amp;highlighted_blocks=753188602_342458560_2_0_0&amp;matching_block_id=753188602_342458560_2_0_0&amp;sr_pri_blocks=753188602_342458560_2_0_0__69164&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Kramer 13 D - Risorgimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-monolocale-con-balcone-in-risorgimento.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=148&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1184377902_390811285_2_0_0&amp;highlighted_blocks=1184377902_390811285_2_0_0&amp;matching_block_id=1184377902_390811285_2_0_0&amp;sr_pri_blocks=1184377902_390811285_2_0_0__46771&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Paoli 6 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-modern-studio-in-the-heart-of-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=149&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1301789401_403060367_2_0_0&amp;highlighted_blocks=1301789401_403060367_2_0_0&amp;matching_block_id=1301789401_403060367_2_0_0&amp;sr_pri_blocks=1301789401_403060367_2_0_0__50368&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aria di Casa - Navigli Darsena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>153.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aria-di-casa-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=150&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=308977902_112593482_1_0_0&amp;highlighted_blocks=308977902_112593482_1_0_0&amp;matching_block_id=308977902_112593482_1_0_0&amp;sr_pri_blocks=308977902_112593482_1_0_0__76560&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Landscape Flats</x:t>
@@ -484,7 +1186,16 @@
     <x:t>115.2</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/landscape-flats.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=40&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1250259201_397504852_1_0_0&amp;highlighted_blocks=1250259201_397504852_1_0_0&amp;matching_block_id=1250259201_397504852_1_0_0&amp;sr_pri_blocks=1250259201_397504852_1_0_0__57554&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/landscape-flats.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=151&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1250259201_397504852_1_0_0&amp;highlighted_blocks=1250259201_397504852_1_0_0&amp;matching_block_id=1250259201_397504852_1_0_0&amp;sr_pri_blocks=1250259201_397504852_1_0_0__57554&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MiaHome43 - Cozy Milan Apartment Near Loreto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>108.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/new-charming-milanese-apartment-near-loreto-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=152&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1402908301_420762435_1_0_0&amp;highlighted_blocks=1402908301_420762435_1_0_0&amp;matching_block_id=1402908301_420762435_1_0_0&amp;sr_pri_blocks=1402908301_420762435_1_0_0__54160&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Elegante bilocale San Calocero</x:t>
@@ -493,7 +1204,7 @@
     <x:t>147.8</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/elegante-bilocale-san-calocero.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=41&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1075591401_402147700_2_0_0&amp;highlighted_blocks=1075591401_402147700_2_0_0&amp;matching_block_id=1075591401_402147700_2_0_0&amp;sr_pri_blocks=1075591401_402147700_2_0_0__73887&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/elegante-bilocale-san-calocero.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=153&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1075591401_402147700_2_0_0&amp;highlighted_blocks=1075591401_402147700_2_0_0&amp;matching_block_id=1075591401_402147700_2_0_0&amp;sr_pri_blocks=1075591401_402147700_2_0_0__73887&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Appartamento con 1 Camera da Letto – Via della Spiga 46</x:t>
@@ -505,40 +1216,73 @@
     <x:t>170.8</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/spiga-46-suites-by-brera-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=42&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=989858402_371633451_2_0_0&amp;highlighted_blocks=989858402_371633451_2_0_0&amp;matching_block_id=989858402_371633451_2_0_0&amp;sr_pri_blocks=989858402_371633451_2_0_0__85415&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>King Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Collection Moscova Suites 8 - Top Collection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/via-volta-apartment-moscova.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=43&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=643475901_403644755_2_0_0&amp;highlighted_blocks=643475901_403644755_2_0_0&amp;matching_block_id=643475901_403644755_2_0_0&amp;sr_pri_blocks=643475901_403644755_2_0_0__72370&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom House</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASATI CENTRAL STATION Metro M1, M2, M3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>146.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/casati-central-station-metro-m1-m2-m3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=44&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1366308501_408912923_2_0_0&amp;highlighted_blocks=1366308501_408912923_2_0_0&amp;matching_block_id=1366308501_408912923_2_0_0&amp;sr_pri_blocks=1366308501_408912923_2_0_0__73056&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/spiga-46-suites-by-brera-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=154&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=989858402_371633451_2_0_0&amp;highlighted_blocks=989858402_371633451_2_0_0&amp;matching_block_id=989858402_371633451_2_0_0&amp;sr_pri_blocks=989858402_371633451_2_0_0__85415&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amazing Studio in Corso Como next Brera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/amazing-studio-in-corso-como-next-brera.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=155&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1510791401_422835329_1_0_0&amp;highlighted_blocks=1510791401_422835329_1_0_0&amp;matching_block_id=1510791401_422835329_1_0_0&amp;sr_pri_blocks=1510791401_422835329_1_0_0__51969&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skyline Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bilocale-6degp-con-wi-fi-ac-posto-auto-a-30-mt-da-m3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=156&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=677119601_276398597_4_0_0&amp;highlighted_blocks=677119601_276398597_4_0_0&amp;matching_block_id=677119601_276398597_4_0_0&amp;sr_pri_blocks=677119601_276398597_4_0_0__55750&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>APARTHOTEL CASA MIA</x:t>
   </x:si>
   <x:si>
-    <x:t>9.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/aparthotel-casa-mia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=45&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=481374404_361771404_0_0_0&amp;highlighted_blocks=481374404_361771404_0_0_0&amp;matching_block_id=481374404_361771404_0_0_0&amp;sr_pri_blocks=481374404_361771404_0_0_0__79750&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/aparthotel-casa-mia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=157&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=481374401_361771404_0_0_0&amp;highlighted_blocks=481374401_361771404_0_0_0&amp;matching_block_id=481374401_361771404_0_0_0&amp;sr_pri_blocks=481374401_361771404_0_0_0__79750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Centrale Suite with Balcony - Top Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>130</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/centrale-suite-with-balcony-top-collection.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=159&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1043242001_376708779_1_0_0&amp;highlighted_blocks=1043242001_376708779_1_0_0&amp;matching_block_id=1043242001_376708779_1_0_0&amp;sr_pri_blocks=1043242001_376708779_1_0_0__65020&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alta Vista Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/alta-vista-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=161&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1503671601_422083140_1_0_0&amp;highlighted_blocks=1503671601_422083140_1_0_0&amp;matching_block_id=1503671601_422083140_1_0_0&amp;sr_pri_blocks=1503671601_422083140_1_0_0__47610&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fabbri Palace - B Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>138.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/fabbri-palace-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=162&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1491884508_420837644_2_0_0&amp;highlighted_blocks=1491884508_420837644_2_0_0&amp;matching_block_id=1491884508_420837644_2_0_0&amp;sr_pri_blocks=1491884508_420837644_2_0_0__69274&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Gregorio 43 A - Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-the-magnificent-flat-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=163&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=688652402_295393454_2_0_0&amp;highlighted_blocks=688652402_295393454_2_0_0&amp;matching_block_id=688652402_295393454_2_0_0&amp;sr_pri_blocks=688652402_295393454_2_0_0__50397&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Calco 2P3 - Sant'Agostino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-mono-con-balcone-in-sant-agostino.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=164&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1342493002_406630968_2_0_0&amp;highlighted_blocks=1342493002_406630968_2_0_0&amp;matching_block_id=1342493002_406630968_2_0_0&amp;sr_pri_blocks=1342493002_406630968_2_0_0__46771&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Orti 4 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-splendido-bilocale-in-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=165&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=925804302_411297180_2_0_0&amp;highlighted_blocks=925804302_411297180_2_0_0&amp;matching_block_id=925804302_411297180_2_0_0&amp;sr_pri_blocks=925804302_411297180_2_0_0__51018&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Garigliano 10 - Isola</x:t>
@@ -547,10 +1291,46 @@
     <x:t>128.2</x:t>
   </x:si>
   <x:si>
-    <x:t>7.9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-unita-su-due-livelli-a-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=46&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1179646202_390438749_2_0_0&amp;highlighted_blocks=1179646202_390438749_2_0_0&amp;matching_block_id=1179646202_390438749_2_0_0&amp;sr_pri_blocks=1179646202_390438749_2_0_0__64110&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-unita-su-due-livelli-a-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=166&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1179646202_390438749_2_0_0&amp;highlighted_blocks=1179646202_390438749_2_0_0&amp;matching_block_id=1179646202_390438749_2_0_0&amp;sr_pri_blocks=1179646202_390438749_2_0_0__64110&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schiaparelli4 - Central Station Suite - B Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>119.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/schiaparelli4-central-station-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=167&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1490630401_420726927_2_0_0&amp;highlighted_blocks=1490630401_420726927_2_0_0&amp;matching_block_id=1490630401_420726927_2_0_0&amp;sr_pri_blocks=1490630401_420726927_2_0_0__59855&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Santa Sofia House - Duomo Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>154.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/santa-sofia-house.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=168&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=920028002_363620357_0_0_0&amp;highlighted_blocks=920028002_363620357_0_0_0&amp;matching_block_id=920028002_363620357_0_0_0&amp;sr_pri_blocks=920028002_363620357_0_0_0__77374&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Central Station Milano Room - 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/central-station-milano-room-3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=169&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=779843701_337790221_1_0_0_587702&amp;highlighted_blocks=779843701_337790221_1_0_0_587702&amp;matching_block_id=779843701_337790221_1_0_0_587702&amp;sr_pri_blocks=779843701_337790221_1_0_0_587702_35975&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - G Emiliani 1 115 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beautiful-flat-fully-furnished-in-pta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=170&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=414216301_126143408_2_0_0&amp;highlighted_blocks=414216301_126143408_2_0_0&amp;matching_block_id=414216301_126143408_2_0_0&amp;sr_pri_blocks=414216301_126143408_2_0_0__48297&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Lecco 5 P2 - in Porta Venezia</x:t>
@@ -559,7 +1339,16 @@
     <x:t>107.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-comodo-appartamento-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=47&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1154859902_388280300_2_0_0&amp;highlighted_blocks=1154859902_388280300_2_0_0&amp;matching_block_id=1154859902_388280300_2_0_0&amp;sr_pri_blocks=1154859902_388280300_2_0_0__53837&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-comodo-appartamento-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=171&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1154859902_388280300_2_0_0&amp;highlighted_blocks=1154859902_388280300_2_0_0&amp;matching_block_id=1154859902_388280300_2_0_0&amp;sr_pri_blocks=1154859902_388280300_2_0_0__53837&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duomo Suite - B Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>167.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/duomo-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=172&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1378811801_410003981_2_0_0&amp;highlighted_blocks=1378811801_410003981_2_0_0&amp;matching_block_id=1378811801_410003981_2_0_0&amp;sr_pri_blocks=1378811801_410003981_2_0_0__83555&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Velasca Tower Apartments</x:t>
@@ -568,7 +1357,16 @@
     <x:t>155.4</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/velasca-tower-apartments-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=48&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=1275181361_400377746_1_0_0&amp;highlighted_blocks=1275181361_400377746_1_0_0&amp;matching_block_id=1275181361_400377746_1_0_0&amp;sr_pri_blocks=1275181361_400377746_1_0_0__77730&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/velasca-tower-apartments-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=173&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1275181361_400377746_1_0_0&amp;highlighted_blocks=1275181361_400377746_1_0_0&amp;matching_block_id=1275181361_400377746_1_0_0&amp;sr_pri_blocks=1275181361_400377746_1_0_0__77730&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luminoso Piano Alto con Terrazzo - Mirable PM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>113.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bright-loft-with-terrace-mirable-pm.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=174&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1443250601_415766843_0_0_0&amp;highlighted_blocks=1443250601_415766843_0_0_0&amp;matching_block_id=1443250601_415766843_0_0_0&amp;sr_pri_blocks=1443250601_415766843_0_0_0__56600&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Maffucci 53 - Dergano</x:t>
@@ -577,82 +1375,85 @@
     <x:t>96.2</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-dimora-con-balcone.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=49&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=987239102_411297538_2_0_0&amp;highlighted_blocks=987239102_411297538_2_0_0&amp;matching_block_id=987239102_411297538_2_0_0&amp;sr_pri_blocks=987239102_411297538_2_0_0__48141&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-dimora-con-balcone.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=175&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=987239102_411297538_2_0_0&amp;highlighted_blocks=987239102_411297538_2_0_0&amp;matching_block_id=987239102_411297538_2_0_0&amp;sr_pri_blocks=987239102_411297538_2_0_0__48141&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>EasyTopStay - Moscova Modern Apartment</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/moscova-modern-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=50&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129480&amp;all_sr_blocks=905968401_361678059_2_0_0_852695&amp;highlighted_blocks=905968401_361678059_2_0_0_852695&amp;matching_block_id=905968401_361678059_2_0_0_852695&amp;sr_pri_blocks=905968401_361678059_2_0_0_852695_73086&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/moscova-modern-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=176&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=905968401_361678059_2_0_0_852695&amp;highlighted_blocks=905968401_361678059_2_0_0_852695&amp;matching_block_id=905968401_361678059_2_0_0_852695&amp;sr_pri_blocks=905968401_361678059_2_0_0_852695_73086&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Penthouse Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hosting Dreams Attics - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>177.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hosting-dreams-attics-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=177&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1088925913_381812816_1_0_0_338935&amp;highlighted_blocks=1088925913_381812816_1_0_0_338935&amp;matching_block_id=1088925913_381812816_1_0_0_338935&amp;sr_pri_blocks=1088925913_381812816_1_0_0_338935_88852&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loft Moderno in Dateo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>107.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/modern-loft-in-dateo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=179&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=800171601_340971950_1_0_0&amp;highlighted_blocks=800171601_340971950_1_0_0&amp;matching_block_id=800171601_340971950_1_0_0&amp;sr_pri_blocks=800171601_340971950_1_0_0__53602&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>BnButler - Archimede 53 - Bright Studio</x:t>
   </x:si>
   <x:si>
-    <x:t>106.6</x:t>
-  </x:si>
-  <x:si>
     <x:t>7.2</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/monolocale-con-spazio-esterno.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=51&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=968435001_369272242_2_0_0&amp;highlighted_blocks=968435001_369272242_2_0_0&amp;matching_block_id=968435001_369272242_2_0_0&amp;sr_pri_blocks=968435001_369272242_2_0_0__53278&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Chichouse Maderno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/chichouse-maderno.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=52&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1274893601_400341987_1_0_0&amp;highlighted_blocks=1274893601_400341987_1_0_0&amp;matching_block_id=1274893601_400341987_1_0_0&amp;sr_pri_blocks=1274893601_400341987_1_0_0__49225&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/monolocale-con-spazio-esterno.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=180&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=968435001_369272242_2_0_0&amp;highlighted_blocks=968435001_369272242_2_0_0&amp;matching_block_id=968435001_369272242_2_0_0&amp;sr_pri_blocks=968435001_369272242_2_0_0__53278&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ComeCasa modern Terraced &amp; Palestra Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>172.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/comecasa-porta-romana-terraced-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=181&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1220752801_394226527_2_0_0&amp;highlighted_blocks=1220752801_394226527_2_0_0&amp;matching_block_id=1220752801_394226527_2_0_0&amp;sr_pri_blocks=1220752801_394226527_2_0_0__86200&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Washington 91 p7 - Solari</x:t>
   </x:si>
   <x:si>
-    <x:t>109.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-appartamento-in-solari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=53&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1085204302_381393382_2_0_0&amp;highlighted_blocks=1085204302_381393382_2_0_0&amp;matching_block_id=1085204302_381393382_2_0_0&amp;sr_pri_blocks=1085204302_381393382_2_0_0__54814&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Deluxe King Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hbhall Residenze Darsena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/blu-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=54&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=101681818_88400138_2_0_0&amp;highlighted_blocks=101681818_88400138_2_0_0&amp;matching_block_id=101681818_88400138_2_0_0&amp;sr_pri_blocks=101681818_88400138_2_0_0__46699&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-appartamento-in-solari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=183&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1085204302_381393382_2_0_0&amp;highlighted_blocks=1085204302_381393382_2_0_0&amp;matching_block_id=1085204302_381393382_2_0_0&amp;sr_pri_blocks=1085204302_381393382_2_0_0__54814&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Lovelyloft - Alzaia Naviglio</x:t>
   </x:si>
   <x:si>
-    <x:t>7.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/lovelyloft-alzaia-naviglio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=55&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=211441401_96023455_2_0_0&amp;highlighted_blocks=211441401_96023455_2_0_0&amp;matching_block_id=211441401_96023455_2_0_0&amp;sr_pri_blocks=211441401_96023455_2_0_0__39801&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment with City View</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Garibaldi 59 apartments in Brera district by Rentopolis</x:t>
-  </x:si>
-  <x:si>
-    <x:t>145.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/corso-garibaldi-modern-cozy-suite-by-rentopolis.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=56&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1307085603_403526015_1_0_0&amp;highlighted_blocks=1307085603_403526015_1_0_0&amp;matching_block_id=1307085603_403526015_1_0_0&amp;sr_pri_blocks=1307085603_403526015_1_0_0__72652&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/lovelyloft-alzaia-naviglio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=184&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=211441401_96023455_2_0_0&amp;highlighted_blocks=211441401_96023455_2_0_0&amp;matching_block_id=211441401_96023455_2_0_0&amp;sr_pri_blocks=211441401_96023455_2_0_0__39801&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Maroncelli 14 - Garibaldi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>111.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-luminoso-bilocale-in-zona-garibaldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=185&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=920802502_411297558_2_0_0&amp;highlighted_blocks=920802502_411297558_2_0_0&amp;matching_block_id=920802502_411297558_2_0_0&amp;sr_pri_blocks=920802502_411297558_2_0_0__55737&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 Pax Luxury Milano Duomo San Babila</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/4-pax-luxury-milano-duomo-san-babila.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=186&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1500952001_421765283_1_0_0&amp;highlighted_blocks=1500952001_421765283_1_0_0&amp;matching_block_id=1500952001_421765283_1_0_0&amp;sr_pri_blocks=1500952001_421765283_1_0_0__85412&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAR RIBBON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/star-ribbon.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=187&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=794654902_339549249_2_2_0&amp;highlighted_blocks=794654902_339549249_2_2_0&amp;matching_block_id=794654902_339549249_2_2_0&amp;sr_pri_blocks=794654902_339549249_2_2_0__57985&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Studio - Annex</x:t>
@@ -664,7 +1465,7 @@
     <x:t>139.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/andreolacentralhotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=57&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=8078766_88153824_0_33_0&amp;highlighted_blocks=8078766_88153824_0_33_0&amp;matching_block_id=8078766_88153824_0_33_0&amp;sr_pri_blocks=8078766_88153824_0_33_0__69800&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/andreolacentralhotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=189&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=8078766_88153824_0_33_0&amp;highlighted_blocks=8078766_88153824_0_33_0&amp;matching_block_id=8078766_88153824_0_33_0&amp;sr_pri_blocks=8078766_88153824_0_33_0__69800&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - DellaChiusa 8 - Porta Ticinese</x:t>
@@ -673,16 +1474,34 @@
     <x:t>153.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-pearl-with-balcony-on-ticinese-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=58&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1311590301_403939277_2_0_0&amp;highlighted_blocks=1311590301_403939277_2_0_0&amp;matching_block_id=1311590301_403939277_2_0_0&amp;sr_pri_blocks=1311590301_403939277_2_0_0__76798&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Elite apartments in Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elite-apartments-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=59&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1402940003_412109324_2_0_0&amp;highlighted_blocks=1402940003_412109324_2_0_0&amp;matching_block_id=1402940003_412109324_2_0_0&amp;sr_pri_blocks=1402940003_412109324_2_0_0__47171&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-pearl-with-balcony-on-ticinese-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=190&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1311590301_403939277_2_0_0&amp;highlighted_blocks=1311590301_403939277_2_0_0&amp;matching_block_id=1311590301_403939277_2_0_0&amp;sr_pri_blocks=1311590301_403939277_2_0_0__76798&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EasyTopStay - Porta Garibaldi Cozy Flat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/porta-garibaldi-grazioso-bilocale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=191&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1138260701_386545476_1_0_0_852718&amp;highlighted_blocks=1138260701_386545476_1_0_0_852718&amp;matching_block_id=1138260701_386545476_1_0_0_852718&amp;sr_pri_blocks=1138260701_386545476_1_0_0_852718_53237&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Living La Corte Segreta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>156.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/buonarroti-la-corte-segreta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=193&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1451587401_416516876_1_0_0&amp;highlighted_blocks=1451587401_416516876_1_0_0&amp;matching_block_id=1451587401_416516876_1_0_0&amp;sr_pri_blocks=1451587401_416516876_1_0_0__78358&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maisonette</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mi casa Cesalpino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>117.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mi-casa-cesalpino.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=196&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1454210002_416749810_1_0_0&amp;highlighted_blocks=1454210002_416749810_1_0_0&amp;matching_block_id=1454210002_416749810_1_0_0&amp;sr_pri_blocks=1454210002_416749810_1_0_0__58777&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>EasyTopStay - Porta Romana Lovely Apartment</x:t>
@@ -691,13 +1510,16 @@
     <x:t>118.8</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/porta-romana-lovely-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=60&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1186688801_391031971_2_0_0_852711&amp;highlighted_blocks=1186688801_391031971_2_0_0_852711&amp;matching_block_id=1186688801_391031971_2_0_0_852711&amp;sr_pri_blocks=1186688801_391031971_2_0_0_852711_59358&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nolo 5 - Apartment Milano - Leia Hospitality</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/nolo-5-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=61&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1392076801_411171430_1_0_0&amp;highlighted_blocks=1392076801_411171430_1_0_0&amp;matching_block_id=1392076801_411171430_1_0_0&amp;sr_pri_blocks=1392076801_411171430_1_0_0__50635&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/porta-romana-lovely-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=197&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1186688801_391031971_2_0_0_852711&amp;highlighted_blocks=1186688801_391031971_2_0_0_852711&amp;matching_block_id=1186688801_391031971_2_0_0_852711&amp;sr_pri_blocks=1186688801_391031971_2_0_0_852711_59358&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luxurious Designer Studio - Centrale Station</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/luxurious-designer-studio-centrale-station.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=198&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1492391701_420884423_2_0_0&amp;highlighted_blocks=1492391701_420884423_2_0_0&amp;matching_block_id=1492391701_420884423_2_0_0&amp;sr_pri_blocks=1492391701_420884423_2_0_0__56410&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Pisacane 19 - Porta Venezia</x:t>
@@ -706,1051 +1528,7 @@
     <x:t>121.4</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easy-life-elegante-trilocale-in-zona-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=62&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=952472502_411297279_2_0_0&amp;highlighted_blocks=952472502_411297279_2_0_0&amp;matching_block_id=952472502_411297279_2_0_0&amp;sr_pri_blocks=952472502_411297279_2_0_0__60745&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Apartment - Ground Floor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Villa Massari</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/italian-residencies-villa-massari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=63&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=970311603_369428409_2_0_0&amp;highlighted_blocks=970311603_369428409_2_0_0&amp;matching_block_id=970311603_369428409_2_0_0&amp;sr_pri_blocks=970311603_369428409_2_0_0__51145&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment with Terrace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toiletpaper Living</x:t>
-  </x:si>
-  <x:si>
-    <x:t>172.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/toiletpaper-living.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=64&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1184641401_390835896_2_0_0&amp;highlighted_blocks=1184641401_390835896_2_0_0&amp;matching_block_id=1184641401_390835896_2_0_0&amp;sr_pri_blocks=1184641401_390835896_2_0_0__86223&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Deluxe Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Broggi 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>146.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/b-family.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=65&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1136928703_386305137_2_0_0&amp;highlighted_blocks=1136928703_386305137_2_0_0&amp;matching_block_id=1136928703_386305137_2_0_0&amp;sr_pri_blocks=1136928703_386305137_2_0_0__73350&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Ferrari 9 - Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-e-moderno-bilocale-in-zona-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=66&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=941565102_411297408_2_0_0&amp;highlighted_blocks=941565102_411297408_2_0_0&amp;matching_block_id=941565102_411297408_2_0_0&amp;sr_pri_blocks=941565102_411297408_2_0_0__53318&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Borgonuovo 4D - Centro Storico</x:t>
-  </x:si>
-  <x:si>
-    <x:t>142.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/stylish-and-fancy-flat-close-to-montenapoleone-brera-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=67&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=801095402_342458597_0_0_0&amp;highlighted_blocks=801095402_342458597_0_0_0&amp;matching_block_id=801095402_342458597_0_0_0&amp;sr_pri_blocks=801095402_342458597_0_0_0__71326&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Recanate 5 - Centrale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>104.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-bello-e-luminoso-flat-in-zona-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=68&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=715255402_342454734_2_0_0&amp;highlighted_blocks=715255402_342454734_2_0_0&amp;matching_block_id=715255402_342454734_2_0_0&amp;sr_pri_blocks=715255402_342454734_2_0_0__52118&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ht maison montenero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>126.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/ht-maison-montenero.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=69&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1455900401_416890977_2_0_0&amp;highlighted_blocks=1455900401_416890977_2_0_0&amp;matching_block_id=1455900401_416890977_2_0_0&amp;sr_pri_blocks=1455900401_416890977_2_0_0__63255&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Gregorio 17 P2 - Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>140.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-confortevola-dimora-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=70&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1010372102_411297589_2_0_0&amp;highlighted_blocks=1010372102_411297589_2_0_0&amp;matching_block_id=1010372102_411297589_2_0_0&amp;sr_pri_blocks=1010372102_411297589_2_0_0__70168&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Torino 34S - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>164.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-dimora-a-due-minuti-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=71&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=996494102_411297086_2_0_0&amp;highlighted_blocks=996494102_411297086_2_0_0&amp;matching_block_id=996494102_411297086_2_0_0&amp;sr_pri_blocks=996494102_411297086_2_0_0__82052&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Apartment with Balcony</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Downtown Apartments Merlo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>164</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/downtown-apartment-merlo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=72&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=389558701_122225007_0_0_0&amp;highlighted_blocks=389558701_122225007_0_0_0&amp;matching_block_id=389558701_122225007_0_0_0&amp;sr_pri_blocks=389558701_122225007_0_0_0__81998&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BB Hotels Aparthotel Isola</x:t>
-  </x:si>
-  <x:si>
-    <x:t>110.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bb-hotels-aparthotel-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=73&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=274589509_362128569_2_0_0&amp;highlighted_blocks=274589509_362128569_2_0_0&amp;matching_block_id=274589509_362128569_2_0_0&amp;sr_pri_blocks=274589509_362128569_2_0_0__55250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELIO, 11 – Appartamento con terrazzo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>129</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/celio-11-appartamento-con-terrazzo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=74&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=1100915201_382929317_2_0_0&amp;highlighted_blocks=1100915201_382929317_2_0_0&amp;matching_block_id=1100915201_382929317_2_0_0&amp;sr_pri_blocks=1100915201_382929317_2_0_0__64462&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milan Downtown Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>181.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milano-cozy-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=75&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129481&amp;all_sr_blocks=832001102_348396804_1_0_0&amp;highlighted_blocks=832001102_348396804_1_0_0&amp;matching_block_id=832001102_348396804_1_0_0&amp;sr_pri_blocks=832001102_348396804_1_0_0__90788&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Cola Montano 3 - Isola</x:t>
-  </x:si>
-  <x:si>
-    <x:t>113</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-incantevole-abitazione-in-zona-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=76&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1064246102_378783331_2_0_0&amp;highlighted_blocks=1064246102_378783331_2_0_0&amp;matching_block_id=1064246102_378783331_2_0_0&amp;sr_pri_blocks=1064246102_378783331_2_0_0__56458&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - San Marco 1 - Brera</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/wonderful-brera-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=77&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=483462501_157562430_2_0_0&amp;highlighted_blocks=483462501_157562430_2_0_0&amp;matching_block_id=483462501_157562430_2_0_0&amp;sr_pri_blocks=483462501_157562430_2_0_0__64772&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Amedei 6 - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>195.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-dimora-a-due-passi-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=78&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1026106302_411297428_2_0_0&amp;highlighted_blocks=1026106302_411297428_2_0_0&amp;matching_block_id=1026106302_411297428_2_0_0&amp;sr_pri_blocks=1026106302_411297428_2_0_0__97577&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Luxury Apartments Fioravanti</x:t>
-  </x:si>
-  <x:si>
-    <x:t>182.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luxury-apartment-fioravanti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=79&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=321708604_380687466_1_0_0_663512&amp;highlighted_blocks=321708604_380687466_1_0_0_663512&amp;matching_block_id=321708604_380687466_1_0_0_663512&amp;sr_pri_blocks=321708604_380687466_1_0_0_663512_91087&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brembo House</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brembo-house.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=81&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=501165301_169592778_2_0_0&amp;highlighted_blocks=501165301_169592778_2_0_0&amp;matching_block_id=501165301_169592778_2_0_0&amp;sr_pri_blocks=501165301_169592778_2_0_0__42050&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Three-Bedroom Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BeCO Sempione Luxury Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beco-sempione-luxury-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=82&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1377862001_410273239_4_0_0&amp;highlighted_blocks=1377862001_410273239_4_0_0&amp;matching_block_id=1377862001_410273239_4_0_0&amp;sr_pri_blocks=1377862001_410273239_4_0_0__91003&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN RIBBON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/green-ribbon.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=83&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=643672411_263835080_2_2_0&amp;highlighted_blocks=643672411_263835080_2_2_0&amp;matching_block_id=643672411_263835080_2_2_0&amp;sr_pri_blocks=643672411_263835080_2_2_0__57985&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>easyhomes - Repubblica</x:t>
-  </x:si>
-  <x:si>
-    <x:t>167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easyhomes-repubblica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=84&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1377078001_409835078_2_0_0&amp;highlighted_blocks=1377078001_409835078_2_0_0&amp;matching_block_id=1377078001_409835078_2_0_0&amp;sr_pri_blocks=1377078001_409835078_2_0_0__83500&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boccaccio's Flats</x:t>
-  </x:si>
-  <x:si>
-    <x:t>142.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/boccaccios-flats.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=85&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1042477701_376658104_2_0_0&amp;highlighted_blocks=1042477701_376658104_2_0_0&amp;matching_block_id=1042477701_376658104_2_0_0&amp;sr_pri_blocks=1042477701_376658104_2_0_0__71421&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milano - Brand New 4 PAX Life &amp; The City Giulio Cesare 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>161</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milano-brand-new-4-pax-life-amp-the-city-giulio-cesare-5.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=86&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1145904001_408191012_1_0_0&amp;highlighted_blocks=1145904001_408191012_1_0_0&amp;matching_block_id=1145904001_408191012_1_0_0&amp;sr_pri_blocks=1145904001_408191012_1_0_0__80483&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Cherubini 6 - City Life</x:t>
-  </x:si>
-  <x:si>
-    <x:t>181.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegance-a-few-steps-from-citylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=87&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1256161501_398156122_2_0_0&amp;highlighted_blocks=1256161501_398156122_2_0_0&amp;matching_block_id=1256161501_398156122_2_0_0&amp;sr_pri_blocks=1256161501_398156122_2_0_0__90582&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Casa Buenos Aires</x:t>
-  </x:si>
-  <x:si>
-    <x:t>137.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/casa-buenos-aires.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=88&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1338765801_406815097_2_0_0&amp;highlighted_blocks=1338765801_406815097_2_0_0&amp;matching_block_id=1338765801_406815097_2_0_0&amp;sr_pri_blocks=1338765801_406815097_2_0_0__68750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Modrone 8-1 - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>119.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-san-babila-elegante-e-rifinito-bilocale-nel-cuore-della-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=90&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=971442802_411297516_2_0_0&amp;highlighted_blocks=971442802_411297516_2_0_0&amp;matching_block_id=971442802_411297516_2_0_0&amp;sr_pri_blocks=971442802_411297516_2_0_0__59896&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Dugnani 4 - Sant' Ambrogio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-comfortable-apartment-in-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=91&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1240198501_395931229_2_0_0&amp;highlighted_blocks=1240198501_395931229_2_0_0&amp;matching_block_id=1240198501_395931229_2_0_0&amp;sr_pri_blocks=1240198501_395931229_2_0_0__45841&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Algarotti 4 - Porta Nuova</x:t>
-  </x:si>
-  <x:si>
-    <x:t>121.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-moderno-e-fresco-trilocale-in-uno-dei-quartieri-piu-moderni-della-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=92&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=924822002_411297083_2_0_0&amp;highlighted_blocks=924822002_411297083_2_0_0&amp;matching_block_id=924822002_411297083_2_0_0&amp;sr_pri_blocks=924822002_411297083_2_0_0__60560&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUVI - Adda</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/cozy-apartments-near-central-station.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=93&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1302638302_403134808_2_0_0&amp;highlighted_blocks=1302638302_403134808_2_0_0&amp;matching_block_id=1302638302_403134808_2_0_0&amp;sr_pri_blocks=1302638302_403134808_2_0_0__58990&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Galleria Buenos Aires 11- Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>159.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/splendid-house-buenos-aires-piazza-lima.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=94&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=453008101_137552007_2_0_0&amp;highlighted_blocks=453008101_137552007_2_0_0&amp;matching_block_id=453008101_137552007_2_0_0&amp;sr_pri_blocks=453008101_137552007_2_0_0__79552&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano- Privata Angera 10S - Centrale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-appartamento-di-design-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=95&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=1069179902_379418625_2_0_0&amp;highlighted_blocks=1069179902_379418625_2_0_0&amp;matching_block_id=1069179902_379418625_2_0_0&amp;sr_pri_blocks=1069179902_379418625_2_0_0__47859&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment - Piazza Monte Falterona 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BePlace Apartments in Fiera</x:t>
-  </x:si>
-  <x:si>
-    <x:t>119</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-fiera.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=96&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=948093101_367386831_2_0_0&amp;highlighted_blocks=948093101_367386831_2_0_0&amp;matching_block_id=948093101_367386831_2_0_0&amp;sr_pri_blocks=948093101_367386831_2_0_0__59470&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Villa Aida</x:t>
-  </x:si>
-  <x:si>
-    <x:t>199.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/villa-aida.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=97&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=150415805_91955825_1_2_0_743654&amp;highlighted_blocks=150415805_91955825_1_2_0_743654&amp;matching_block_id=150415805_91955825_1_2_0_743654&amp;sr_pri_blocks=150415805_91955825_1_2_0_743654_99819&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Golden Prestige</x:t>
-  </x:si>
-  <x:si>
-    <x:t>184.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luxury-flat-repubblica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=98&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=332276103_115726847_1_0_0&amp;highlighted_blocks=332276103_115726847_1_0_0&amp;matching_block_id=332276103_115726847_1_0_0&amp;sr_pri_blocks=332276103_115726847_1_0_0__92333&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Le scuderie di Sant'Ambrogio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>166.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/terraggio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=99&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129483&amp;all_sr_blocks=253069601_103872408_2_0_0_666040&amp;highlighted_blocks=253069601_103872408_2_0_0_666040&amp;matching_block_id=253069601_103872408_2_0_0_666040&amp;sr_pri_blocks=253069601_103872408_2_0_0_666040_83060&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Frisi 3 City Center Suite - B Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>115</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/frisi-3-city-center-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=101&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1347983901_407144368_2_0_0&amp;highlighted_blocks=1347983901_407144368_2_0_0&amp;matching_block_id=1347983901_407144368_2_0_0&amp;sr_pri_blocks=1347983901_407144368_2_0_0__57485&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Torino 34D - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>141.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/amazing-new-amp-fully-furnished-studio-in-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=102&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=414193401_126133859_2_0_0&amp;highlighted_blocks=414193401_126133859_2_0_0&amp;matching_block_id=414193401_126133859_2_0_0&amp;sr_pri_blocks=414193401_126133859_2_0_0__70726&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ca Foscari Pop Naviglio ,2 camere 2 bagni</x:t>
-  </x:si>
-  <x:si>
-    <x:t>154.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/ca-foscari-pop-naviglio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=103&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1167981801_389372607_1_0_0_295248&amp;highlighted_blocks=1167981801_389372607_1_0_0_295248&amp;matching_block_id=1167981801_389372607_1_0_0_295248&amp;sr_pri_blocks=1167981801_389372607_1_0_0_295248_77323&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Podgora 5 - Porta Vittoria</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-dimora-con-balcone-in-porta-vittoria.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=104&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1185527402_390923589_2_0_0&amp;highlighted_blocks=1185527402_390923589_2_0_0&amp;matching_block_id=1185527402_390923589_2_0_0&amp;sr_pri_blocks=1185527402_390923589_2_0_0__79772&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RED RIBBON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/red-ribbon.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=106&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=643669302_263831163_2_2_0&amp;highlighted_blocks=643669302_263831163_2_2_0&amp;matching_block_id=643669302_263831163_2_2_0&amp;sr_pri_blocks=643669302_263831163_2_2_0__50345&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUOMO VIEW - 2 min from Duomo Amazing location</x:t>
-  </x:si>
-  <x:si>
-    <x:t>173.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/duomo-view-2-min-from-duomo-amazing-location.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=107&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1132300201_385862129_2_0_0&amp;highlighted_blocks=1132300201_385862129_2_0_0&amp;matching_block_id=1132300201_385862129_2_0_0&amp;sr_pri_blocks=1132300201_385862129_2_0_0__86612&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Modrone 28 PT - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-moderno-rifugio-a-due-passi-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=108&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1065754302_411297157_2_0_0&amp;highlighted_blocks=1065754302_411297157_2_0_0&amp;matching_block_id=1065754302_411297157_2_0_0&amp;sr_pri_blocks=1065754302_411297157_2_0_0__59896&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUOMO - The Warm Maison - EXCLUSIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>154.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/the-warm-maison-duomo-700m.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=109&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=947727801_367351474_2_0_0&amp;highlighted_blocks=947727801_367351474_2_0_0&amp;matching_block_id=947727801_367351474_2_0_0&amp;sr_pri_blocks=947727801_367351474_2_0_0__77062&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio Upper Floor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milan Eleven by Brera Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milan-eleven-by-brera-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=110&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=694969603_285647587_1_0_0&amp;highlighted_blocks=694969603_285647587_1_0_0&amp;matching_block_id=694969603_285647587_1_0_0&amp;sr_pri_blocks=694969603_285647587_1_0_0__95530&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment - Annex</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hotel Lido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/hotellidomilano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=111&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=8084515_88153892_0_1_0&amp;highlighted_blocks=8084515_88153892_0_1_0&amp;matching_block_id=8084515_88153892_0_1_0&amp;sr_pri_blocks=8084515_88153892_0_1_0__79750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milan Royal Suites - Duomo Santo Stefano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-duomo-santo-stefano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=112&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1203600902_392602555_2_0_0&amp;highlighted_blocks=1203600902_392602555_2_0_0&amp;matching_block_id=1203600902_392602555_2_0_0&amp;sr_pri_blocks=1203600902_392602555_2_0_0__90770&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Suffragio 3 - Fashion District</x:t>
-  </x:si>
-  <x:si>
-    <x:t>145.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-stylish-design-apartment-in-fashion-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=113&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1312097201_403984239_2_0_0&amp;highlighted_blocks=1312097201_403984239_2_0_0&amp;matching_block_id=1312097201_403984239_2_0_0&amp;sr_pri_blocks=1312097201_403984239_2_0_0__72940&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife Milano - Santa Maria Valle 4 - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>164.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/spacious-comfortable-apartment-in-duomo-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=115&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=801094902_342458644_2_0_0&amp;highlighted_blocks=801094902_342458644_2_0_0&amp;matching_block_id=801094902_342458644_2_0_0&amp;sr_pri_blocks=801094902_342458644_2_0_0__82152&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Lecco 18D - Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/nice-apartment-in-the-heart-of-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=116&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=889046702_411297401_2_0_0&amp;highlighted_blocks=889046702_411297401_2_0_0&amp;matching_block_id=889046702_411297401_2_0_0&amp;sr_pri_blocks=889046702_411297401_2_0_0__54458&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Settembrini 7 - Centrale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-monolocale-con-arredamento-minimal-in-zona-stazione-central.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=117&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=941285802_411297087_2_0_0&amp;highlighted_blocks=941285802_411297087_2_0_0&amp;matching_block_id=941285802_411297087_2_0_0&amp;sr_pri_blocks=941285802_411297087_2_0_0__45276&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Kramer 29 - Risorgimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>143.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-trilocale-in-zona-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=118&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=927040702_411297578_2_0_0&amp;highlighted_blocks=927040702_411297578_2_0_0&amp;matching_block_id=927040702_411297578_2_0_0&amp;sr_pri_blocks=927040702_411297578_2_0_0__71940&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ampi monolocali in Via Pirandello - Washington</x:t>
-  </x:si>
-  <x:si>
-    <x:t>151.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/pirandello-4.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=121&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1290498304_402004962_2_0_0&amp;highlighted_blocks=1290498304_402004962_2_0_0&amp;matching_block_id=1290498304_402004962_2_0_0&amp;sr_pri_blocks=1290498304_402004962_2_0_0__75550&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Urban Garden Lofts by Blue Velvet Livings</x:t>
-  </x:si>
-  <x:si>
-    <x:t>141.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/homie-urbangarden.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=122&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1105689204_383384584_1_0_0&amp;highlighted_blocks=1105689204_383384584_1_0_0&amp;matching_block_id=1105689204_383384584_1_0_0&amp;sr_pri_blocks=1105689204_383384584_1_0_0__70758&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - G Emiliani 1 114 - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/114-amazing-flat-fully-furnished-in-pta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=123&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=414189201_126132005_2_0_0&amp;highlighted_blocks=414189201_126132005_2_0_0&amp;matching_block_id=414189201_126132005_2_0_0&amp;sr_pri_blocks=414189201_126132005_2_0_0__48297&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio - Via San Calocero 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BePlace Apartments in De Amicis</x:t>
-  </x:si>
-  <x:si>
-    <x:t>134.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-de-amicis.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=124&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1296552601_402558435_2_0_0&amp;highlighted_blocks=1296552601_402558435_2_0_0&amp;matching_block_id=1296552601_402558435_2_0_0&amp;sr_pri_blocks=1296552601_402558435_2_0_0__67070&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Garigliano 8 - Isola</x:t>
-  </x:si>
-  <x:si>
-    <x:t>118.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-coccole-e-relax-nel-cuore-di-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=125&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129494&amp;all_sr_blocks=1066167102_411297075_2_0_0&amp;highlighted_blocks=1066167102_411297075_2_0_0&amp;matching_block_id=1066167102_411297075_2_0_0&amp;sr_pri_blocks=1066167102_411297075_2_0_0__59282&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Residenza Porta Volta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>174.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/residenza-porta-volta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=126&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=106625301_91899460_2_0_0&amp;highlighted_blocks=106625301_91899460_2_0_0&amp;matching_block_id=106625301_91899460_2_0_0&amp;sr_pri_blocks=106625301_91899460_2_0_0__87250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sweett - Luxury Velasca</x:t>
-  </x:si>
-  <x:si>
-    <x:t>184.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/sweet-inn-luxury-velasca.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=127&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=1117509506_384613446_0_0_0&amp;highlighted_blocks=1117509506_384613446_0_0_0&amp;matching_block_id=1117509506_384613446_0_0_0&amp;sr_pri_blocks=1117509506_384613446_0_0_0__92236&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Santa Sofia 29 - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>115.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/modern-and-new-flat-in-duomo-area.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=128&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=609071102_242160742_2_0_0&amp;highlighted_blocks=609071102_242160742_2_0_0&amp;matching_block_id=609071102_242160742_2_0_0&amp;sr_pri_blocks=609071102_242160742_2_0_0__57896&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio Apartment - Via Romagnosi 4 B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milan Royal Suites - Centro Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>197.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=129&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=130695902_202239866_2_0_0&amp;highlighted_blocks=130695902_202239866_2_0_0&amp;matching_block_id=130695902_202239866_2_0_0&amp;sr_pri_blocks=130695902_202239866_2_0_0__98590&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Appartamento con 1 Camera da Letto - Via Pioppette 8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brera Apartments in Porta Ticinese</x:t>
-  </x:si>
-  <x:si>
-    <x:t>148.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brera-apartments-in-porta-ticinese.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=130&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=210794101_95900308_2_0_0&amp;highlighted_blocks=210794101_95900308_2_0_0&amp;matching_block_id=210794101_95900308_2_0_0&amp;sr_pri_blocks=210794101_95900308_2_0_0__74110&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Duomo Deluxe Apartments #5-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-duomo-deluxe-apartments-5-11.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=131&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=1389031004_410897819_2_0_0&amp;highlighted_blocks=1389031004_410897819_2_0_0&amp;matching_block_id=1389031004_410897819_2_0_0&amp;sr_pri_blocks=1389031004_410897819_2_0_0__57954&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BePlace Bocconi Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>138.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beplace-bocconi-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=132&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=772869501_335238850_2_0_0&amp;highlighted_blocks=772869501_335238850_2_0_0&amp;matching_block_id=772869501_335238850_2_0_0&amp;sr_pri_blocks=772869501_335238850_2_0_0__69070&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Porta Venezia Luxe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>175.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/porta-venezia-luxe.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=133&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=1417265401_413402093_2_0_0&amp;highlighted_blocks=1417265401_413402093_2_0_0&amp;matching_block_id=1417265401_413402093_2_0_0&amp;sr_pri_blocks=1417265401_413402093_2_0_0__87935&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Savoia Central Milan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>169.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/savoia-central-milan.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=134&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=1076314502_402221173_1_0_0&amp;highlighted_blocks=1076314502_402221173_1_0_0&amp;matching_block_id=1076314502_402221173_1_0_0&amp;sr_pri_blocks=1076314502_402221173_1_0_0__84750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top Accommodations in the Heart of Milano!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/roomy-apts-in-the-heart-of-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=135&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=896647102_360273517_1_0_0&amp;highlighted_blocks=896647102_360273517_1_0_0&amp;matching_block_id=896647102_360273517_1_0_0&amp;sr_pri_blocks=896647102_360273517_1_0_0__54837&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Santa Sofia 18 - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-annydi-art-home-in-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=136&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=911484302_411297152_2_0_0&amp;highlighted_blocks=911484302_411297152_2_0_0&amp;matching_block_id=911484302_411297152_2_0_0&amp;sr_pri_blocks=911484302_411297152_2_0_0__82052&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUVI - Savona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luvi-savona.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=138&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=1499858701_421654746_2_0_0&amp;highlighted_blocks=1499858701_421654746_2_0_0&amp;matching_block_id=1499858701_421654746_2_0_0&amp;sr_pri_blocks=1499858701_421654746_2_0_0__59520&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Appartamento con 1 Camera da Letto - Corso Garibaldi 127</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brera Apartments in Garibaldi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>155.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brera-apartments-in-garibaldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=139&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=77197815_88389966_2_0_0&amp;highlighted_blocks=77197815_88389966_2_0_0&amp;matching_block_id=77197815_88389966_2_0_0&amp;sr_pri_blocks=77197815_88389966_2_0_0__77595&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milan - Disciplini 17 - Historic Center</x:t>
-  </x:si>
-  <x:si>
-    <x:t>157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-comfort-and-style-in-the-heart-of-milan.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=140&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=1329196201_405478950_2_0_0&amp;highlighted_blocks=1329196201_405478950_2_0_0&amp;matching_block_id=1329196201_405478950_2_0_0&amp;sr_pri_blocks=1329196201_405478950_2_0_0__78498&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Darsena Flat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>125.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/darsena-flat-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=141&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=879179401_394181088_2_0_0&amp;highlighted_blocks=879179401_394181088_2_0_0&amp;matching_block_id=879179401_394181088_2_0_0&amp;sr_pri_blocks=879179401_394181088_2_0_0__62753&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Twin Room with Kitchenette</x:t>
-  </x:si>
-  <x:si>
-    <x:t>iH Hotels Milano ApartHotel Argonne Park</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/biancacroce.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=142&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=23691704_88162793_1_0_0&amp;highlighted_blocks=23691704_88162793_1_0_0&amp;matching_block_id=23691704_88162793_1_0_0&amp;sr_pri_blocks=23691704_88162793_1_0_0__38635&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bellevue Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>198.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bellevue-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=143&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=866211901_354824185_1_0_0_263875&amp;highlighted_blocks=866211901_354824185_1_0_0_263875&amp;matching_block_id=866211901_354824185_1_0_0_263875&amp;sr_pri_blocks=866211901_354824185_1_0_0_263875_99174&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BB Hotels Aparthotel Arcimboldi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bb-hotels-residenza-arcimboldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=144&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=115910705_362128522_2_0_0&amp;highlighted_blocks=115910705_362128522_2_0_0&amp;matching_block_id=115910705_362128522_2_0_0&amp;sr_pri_blocks=115910705_362128522_2_0_0__47250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio - Via Confalonieri 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BePlace Apartments in Gae Aulenti</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=147&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=554243403_204765162_2_0_0&amp;highlighted_blocks=554243403_204765162_2_0_0&amp;matching_block_id=554243403_204765162_2_0_0&amp;sr_pri_blocks=554243403_204765162_2_0_0__67070&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Genova 22 - Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>128.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/colored-and-spacious-flat-close-to-navigli-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=148&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=891711202_411297609_2_0_0&amp;highlighted_blocks=891711202_411297609_2_0_0&amp;matching_block_id=891711202_411297609_2_0_0&amp;sr_pri_blocks=891711202_411297609_2_0_0__64410&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ComeCasa 3 Bedrooms Apartment near Bocconi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>167.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/comecasa-3-bedrooms-apartment-near-bocconi-milano1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=149&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=1373698901_409520909_2_0_0&amp;highlighted_blocks=1373698901_409520909_2_0_0&amp;matching_block_id=1373698901_409520909_2_0_0&amp;sr_pri_blocks=1373698901_409520909_2_0_0__83650&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Luxury Apartment - Near Stazione Centrale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bilocale-luxury-near-stazione-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=150&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129505&amp;all_sr_blocks=1176794301_390205150_1_0_0&amp;highlighted_blocks=1176794301_390205150_1_0_0&amp;matching_block_id=1176794301_390205150_1_0_0&amp;sr_pri_blocks=1176794301_390205150_1_0_0__75586&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stylish Flat Near San Siro - Metro WiFi &amp; AC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>127.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/ideal-rent-albertinelli-9.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=153&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1331133402_405649003_2_0_0&amp;highlighted_blocks=1331133402_405649003_2_0_0&amp;matching_block_id=1331133402_405649003_2_0_0&amp;sr_pri_blocks=1331133402_405649003_2_0_0__63750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Deluxe One-Bedroom Apartment with City View</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Maggi Milano - New beautiful apartments in the city center</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/new-beautiful-two-apartments-in-the-city-center.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=154&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1222105404_412190978_2_0_0&amp;highlighted_blocks=1222105404_412190978_2_0_0&amp;matching_block_id=1222105404_412190978_2_0_0&amp;sr_pri_blocks=1222105404_412190978_2_0_0__90610&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio with Terrace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BePlace Apartments in Scalo Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>130.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beplace-apartments-at-fondazione-prada.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=156&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1064660701_378853338_2_0_0&amp;highlighted_blocks=1064660701_378853338_2_0_0&amp;matching_block_id=1064660701_378853338_2_0_0&amp;sr_pri_blocks=1064660701_378853338_2_0_0__65070&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exquisite Stay Bocconi - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>149.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/lovely-stay-vannucci-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=157&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=900610701_360735586_1_0_0&amp;highlighted_blocks=900610701_360735586_1_0_0&amp;matching_block_id=900610701_360735586_1_0_0&amp;sr_pri_blocks=900610701_360735586_1_0_0__74750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LaFilo Apartment 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>146.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/solution-home-porta-romana-3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=158&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1181103901_390553415_1_0_0&amp;highlighted_blocks=1181103901_390553415_1_0_0&amp;matching_block_id=1181103901_390553415_1_0_0&amp;sr_pri_blocks=1181103901_390553415_1_0_0__73250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Game On Apt - Corso Vercelli by InnStay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/game-on-apt-corso-vercelli-by-innstay.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=159&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1344161301_406785908_2_0_0&amp;highlighted_blocks=1344161301_406785908_2_0_0&amp;matching_block_id=1344161301_406785908_2_0_0&amp;sr_pri_blocks=1344161301_406785908_2_0_0__92270&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESIGN APARTMENT - Spadolini, Campus Bocconi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>136.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/design-apartment-spadolini-campus-bocconi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=160&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=974140201_369797365_2_0_0&amp;highlighted_blocks=974140201_369797365_2_0_0&amp;matching_block_id=974140201_369797365_2_0_0&amp;sr_pri_blocks=974140201_369797365_2_0_0__68055&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment with View</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RELSTAY - Tortona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>192.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/relstay-tortona-1br.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=161&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1107508801_383531966_0_0_0&amp;highlighted_blocks=1107508801_383531966_0_0_0&amp;matching_block_id=1107508801_383531966_0_0_0&amp;sr_pri_blocks=1107508801_383531966_0_0_0__96200&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BnButler - Pergolesi, 6 - Accogliente e Moderno a Due Passi da Tutto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>119.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/pergolesi-6-accogliente-e-moderno-a-due-passi-da-tutto.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=162&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=873063102_356089594_2_0_0&amp;highlighted_blocks=873063102_356089594_2_0_0&amp;matching_block_id=873063102_356089594_2_0_0&amp;sr_pri_blocks=873063102_356089594_2_0_0__59691&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Teodosio 15 - Lambrate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-colorato-studio-con-terrazzo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=163&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1025164002_411297676_2_0_0&amp;highlighted_blocks=1025164002_411297676_2_0_0&amp;matching_block_id=1025164002_411297676_2_0_0&amp;sr_pri_blocks=1025164002_411297676_2_0_0__41685&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>I-Host Apartment - Maffei 20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>160.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/i-host-apartment-maffei-20.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=164&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1487736801_420243981_1_0_0&amp;highlighted_blocks=1487736801_420243981_1_0_0&amp;matching_block_id=1487736801_420243981_1_0_0&amp;sr_pri_blocks=1487736801_420243981_1_0_0__80183&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment - Largo Treves 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brera Apartments in San Marco</x:t>
-  </x:si>
-  <x:si>
-    <x:t>163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brera-apartments-in-san-marco.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=165&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=309666304_112718597_2_0_0&amp;highlighted_blocks=309666304_112718597_2_0_0&amp;matching_block_id=309666304_112718597_2_0_0&amp;sr_pri_blocks=309666304_112718597_2_0_0__81505&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOIVY Boutique Apartments Farneti</x:t>
-  </x:si>
-  <x:si>
-    <x:t>160.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/aria-boutique-apartments-farneti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=166&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=594316101_233175898_0_0_0&amp;highlighted_blocks=594316101_233175898_0_0_0&amp;matching_block_id=594316101_233175898_0_0_0&amp;sr_pri_blocks=594316101_233175898_0_0_0__80362&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Deluxe One-Bedroom Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Central Station Design Suites - B Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>103.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/central-station-design-suites-b-home-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=169&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1444849001_415905141_2_0_0&amp;highlighted_blocks=1444849001_415905141_2_0_0&amp;matching_block_id=1444849001_415905141_2_0_0&amp;sr_pri_blocks=1444849001_415905141_2_0_0__51560&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brera Apartments in San Fermo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brera-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=170&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=18725213_88388315_2_0_0&amp;highlighted_blocks=18725213_88388315_2_0_0&amp;matching_block_id=18725213_88388315_2_0_0&amp;sr_pri_blocks=18725213_88388315_2_0_0__81505&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Navigli Cozy Corner - La Vista Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>104.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/navigli-cozy-corner-la-vista-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=171&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1538125001_425343543_2_0_0&amp;highlighted_blocks=1538125001_425343543_2_0_0&amp;matching_block_id=1538125001_425343543_2_0_0&amp;sr_pri_blocks=1538125001_425343543_2_0_0__52446&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vanilla Rosemary House</x:t>
-  </x:si>
-  <x:si>
-    <x:t>147.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/vanilla-rosemary-house.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=172&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1496574801_421334125_1_0_0&amp;highlighted_blocks=1496574801_421334125_1_0_0&amp;matching_block_id=1496574801_421334125_1_0_0&amp;sr_pri_blocks=1496574801_421334125_1_0_0__73600&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BnButler - Verona 12, Porta Romana District</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/verona-12-porta-romana-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=174&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=975304901_369904033_2_0_0&amp;highlighted_blocks=975304901_369904033_2_0_0&amp;matching_block_id=975304901_369904033_2_0_0&amp;sr_pri_blocks=975304901_369904033_2_0_0__80877&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Xenia Apartments - Luminous Suite in Citylife</x:t>
-  </x:si>
-  <x:si>
-    <x:t>139.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luminous-suite-in-citylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=175&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129516&amp;all_sr_blocks=1215699501_416285264_2_0_0&amp;highlighted_blocks=1215699501_416285264_2_0_0&amp;matching_block_id=1215699501_416285264_2_0_0&amp;sr_pri_blocks=1215699501_416285264_2_0_0__69566&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Giacosa, 71 – Comodo appartamento per 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>197.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/giacosa-71-comodo-appartamento-per-6.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=177&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1183246701_390727905_4_0_0&amp;highlighted_blocks=1183246701_390727905_4_0_0&amp;matching_block_id=1183246701_390727905_4_0_0&amp;sr_pri_blocks=1183246701_390727905_4_0_0__98728&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Ascanio Sforza 53 - Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-romantico-appartamento-sui-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=178&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1015534602_411297596_2_0_0&amp;highlighted_blocks=1015534602_411297596_2_0_0&amp;matching_block_id=1015534602_411297596_2_0_0&amp;sr_pri_blocks=1015534602_411297596_2_0_0__53018&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>La casa di Tessa - Navigli Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>157.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/la-casa-di-tessa-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=180&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1054980201_377688966_1_0_0&amp;highlighted_blocks=1054980201_377688966_1_0_0&amp;matching_block_id=1054980201_377688966_1_0_0&amp;sr_pri_blocks=1054980201_377688966_1_0_0__78775&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loft Budget</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BB Hotels Aparthotel Città Studi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bb-hotels-residenza-giulia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=181&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=38781210_362089897_2_0_0&amp;highlighted_blocks=38781210_362089897_2_0_0&amp;matching_block_id=38781210_362089897_2_0_0&amp;sr_pri_blocks=38781210_362089897_2_0_0__54250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aparthotel Isola</x:t>
-  </x:si>
-  <x:si>
-    <x:t>132.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/aparthotel-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=183&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=225027101_98891649_1_0_0&amp;highlighted_blocks=225027101_98891649_1_0_0&amp;matching_block_id=225027101_98891649_1_0_0&amp;sr_pri_blocks=225027101_98891649_1_0_0__66400&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Il Melograno sul Naviglio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>138.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/il-melograno-sul-naviglio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=184&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1178347601_390390159_1_0_0&amp;highlighted_blocks=1178347601_390390159_1_0_0&amp;matching_block_id=1178347601_390390159_1_0_0&amp;sr_pri_blocks=1178347601_390390159_1_0_0__69250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sant' Ambrogio Flat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/sant-39-ambrogio-flat.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=185&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=305047102_394181144_2_0_0&amp;highlighted_blocks=305047102_394181144_2_0_0&amp;matching_block_id=305047102_394181144_2_0_0&amp;sr_pri_blocks=305047102_394181144_2_0_0__68530&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio - Via Passarella 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brera Apartments in San Babila</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brera-apartments-in-san-babila.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=188&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=106267107_88400509_2_0_0&amp;highlighted_blocks=106267107_88400509_2_0_0&amp;matching_block_id=106267107_88400509_2_0_0&amp;sr_pri_blocks=106267107_88400509_2_0_0__81505&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Eleven Suites - Cozy apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>111.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/eleven-suites-cozy-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=189&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1226394103_395701254_2_0_0&amp;highlighted_blocks=1226394103_395701254_2_0_0&amp;matching_block_id=1226394103_395701254_2_0_0&amp;sr_pri_blocks=1226394103_395701254_2_0_0__55806&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Bixio 17 - Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-milano-bixio-17-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=190&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1500100301_421675795_0_0_0&amp;highlighted_blocks=1500100301_421675795_0_0_0&amp;matching_block_id=1500100301_421675795_0_0_0&amp;sr_pri_blocks=1500100301_421675795_0_0_0__68768&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Rontgen 24D - Bocconi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>112.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-appartamento-in-bocconi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=191&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=993685902_411297557_2_0_0&amp;highlighted_blocks=993685902_411297557_2_0_0&amp;matching_block_id=993685902_411297557_2_0_0&amp;sr_pri_blocks=993685902_411297557_2_0_0__56177&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Appartamento delizioso, vicino a Fiera, Duomo, San Siro</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/casa-andry-vicino-a-fiera-duomo-san-siro.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=192&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1341018101_406509649_1_0_0&amp;highlighted_blocks=1341018101_406509649_1_0_0&amp;matching_block_id=1341018101_406509649_1_0_0&amp;sr_pri_blocks=1341018101_406509649_1_0_0__45815&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Charming &amp; Bright Apartment near Milan's Fashion District</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/charming-bright-apartment-near-milans-fashion-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=193&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1354104402_407740427_2_0_0&amp;highlighted_blocks=1354104402_407740427_2_0_0&amp;matching_block_id=1354104402_407740427_2_0_0&amp;sr_pri_blocks=1354104402_407740427_2_0_0__90556&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Navigli Design Apartment with Balcony</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/navigli-comfy-location.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=195&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1042185701_376636488_1_0_0_586913&amp;highlighted_blocks=1042185701_376636488_1_0_0_586913&amp;matching_block_id=1042185701_376636488_1_0_0_586913&amp;sr_pri_blocks=1042185701_376636488_1_0_0_586913_45750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Superior One-Bedroom Apartment with Balcony</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cefalonia Garden with Terrace &amp; Garage by NDP rent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>157.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/cefalonia-garden-with-terrace-amp-garage-by-ndp-rent.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=196&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1384074410_423109409_1_0_0_1234024&amp;highlighted_blocks=1384074410_423109409_1_0_0_1234024&amp;matching_block_id=1384074410_423109409_1_0_0_1234024&amp;sr_pri_blocks=1384074410_423109409_1_0_0_1234024_78736&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Relais Milano Suite 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>187.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/relais-milano-suite-2.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=197&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1029878701_375677568_2_0_0&amp;highlighted_blocks=1029878701_375677568_2_0_0&amp;matching_block_id=1029878701_375677568_2_0_0&amp;sr_pri_blocks=1029878701_375677568_2_0_0__93875&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elegant Sempione Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/elegant-sempione-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=198&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=931010601_365440874_2_0_0&amp;highlighted_blocks=931010601_365440874_2_0_0&amp;matching_block_id=931010601_365440874_2_0_0&amp;sr_pri_blocks=931010601_365440874_2_0_0__85415&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exclusive rooftop apartment with large terrace in Solari/Tortona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>150.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/exclusive-rooftop-apartment-with-large-terrace-in-solari-tortona.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=199&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=480965001_154784694_2_0_0&amp;highlighted_blocks=480965001_154784694_2_0_0&amp;matching_block_id=480965001_154784694_2_0_0&amp;sr_pri_blocks=480965001_154784694_2_0_0__75222&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milano Apartments Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>147.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milano-apartments-vigevano-41.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAKvh47LBsACAdICJGQ4MDlhZjBlLTliMjQtNDU5Ni1hZDY2LWM3ZGMxODc3NzZkMdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=200&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=6fa42e2a1248579330a9829a725e28a1&amp;srepoch=1768129527&amp;all_sr_blocks=1290699607_423019782_2_0_0&amp;highlighted_blocks=1290699607_423019782_2_0_0&amp;matching_block_id=1290699607_423019782_2_0_0&amp;sr_pri_blocks=1290699607_423019782_2_0_0__73750&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easy-life-elegante-trilocale-in-zona-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=199&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=952472502_411297279_2_0_0&amp;highlighted_blocks=952472502_411297279_2_0_0&amp;matching_block_id=952472502_411297279_2_0_0&amp;sr_pri_blocks=952472502_411297279_2_0_0__60745&amp;from=searchresults</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2101,7 +1879,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F178"/>
+  <x:dimension ref="A1:F156"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:6">
@@ -2169,19 +1947,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="D4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -2189,19 +1967,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="D5" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="E5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="s">
+      <x:c r="F5" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -2209,19 +1987,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="E6" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
+      <x:c r="F6" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -2229,19 +2007,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="D7" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
+      <x:c r="F7" s="0" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -2249,7 +2027,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>35</x:v>
@@ -2269,19 +2047,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="D9" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="E9" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="s">
+      <x:c r="F9" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -2289,7 +2067,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>44</x:v>
@@ -2298,7 +2076,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>46</x:v>
@@ -2309,7 +2087,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>47</x:v>
@@ -2318,10 +2096,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -2329,19 +2107,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -2349,16 +2127,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>57</x:v>
@@ -2378,10 +2156,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -2389,7 +2167,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>63</x:v>
@@ -2409,19 +2187,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C16" s="0" t="s">
+      <x:c r="D16" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D16" s="0" t="s">
+      <x:c r="E16" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -2429,19 +2207,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D17" s="0" t="s">
+      <x:c r="F17" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -2449,7 +2227,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>75</x:v>
@@ -2458,10 +2236,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
@@ -2469,16 +2247,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C19" s="0" t="s">
+      <x:c r="D19" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D19" s="0" t="s">
+      <x:c r="E19" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>82</x:v>
@@ -2489,7 +2267,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>83</x:v>
@@ -2498,10 +2276,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -2509,19 +2287,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -2529,19 +2307,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -2549,19 +2327,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -2569,19 +2347,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -2589,19 +2367,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -2609,19 +2387,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
@@ -2629,19 +2407,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
@@ -2649,19 +2427,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -2669,19 +2447,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -2689,19 +2467,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -2709,19 +2487,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
@@ -2729,19 +2507,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
@@ -2749,19 +2527,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
@@ -2769,19 +2547,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
@@ -2789,19 +2567,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
@@ -2809,19 +2587,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -2829,7 +2607,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>145</x:v>
@@ -2838,7 +2616,7 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>147</x:v>
@@ -2849,7 +2627,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>148</x:v>
@@ -2858,7 +2636,7 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>150</x:v>
@@ -2869,7 +2647,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>151</x:v>
@@ -2878,10 +2656,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
@@ -2889,19 +2667,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
@@ -2909,19 +2687,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
@@ -2929,19 +2707,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6">
@@ -2949,7 +2727,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>165</x:v>
@@ -2958,7 +2736,7 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
         <x:v>167</x:v>
@@ -2969,19 +2747,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C44" s="0" t="s">
+      <x:c r="D44" s="0" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="D44" s="0" t="s">
+      <x:c r="E44" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -2989,13 +2767,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>173</x:v>
@@ -3009,7 +2787,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>175</x:v>
@@ -3018,10 +2796,10 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:6">
@@ -3029,7 +2807,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>179</x:v>
@@ -3038,7 +2816,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>181</x:v>
@@ -3049,7 +2827,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>182</x:v>
@@ -3058,10 +2836,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -3069,19 +2847,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6">
@@ -3089,19 +2867,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:6">
@@ -3109,19 +2887,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -3129,19 +2907,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -3149,19 +2927,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -3169,16 +2947,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
         <x:v>204</x:v>
@@ -3189,16 +2967,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
         <x:v>207</x:v>
@@ -3209,19 +2987,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="C56" s="0" t="s">
+      <x:c r="D56" s="0" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="D56" s="0" t="s">
+      <x:c r="E56" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="E56" s="0" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F56" s="0" t="s">
-        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:6">
@@ -3229,19 +3007,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="C57" s="0" t="s">
+      <x:c r="E57" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F57" s="0" t="s">
-        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:6">
@@ -3249,19 +3027,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="E58" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F58" s="0" t="s">
-        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -3269,19 +3047,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="E59" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F59" s="0" t="s">
-        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -3289,19 +3067,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F60" s="0" t="s">
-        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -3309,19 +3087,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F61" s="0" t="s">
-        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -3329,19 +3107,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="D62" s="0" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F62" s="0" t="s">
-        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -3349,19 +3127,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6">
@@ -3369,19 +3147,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:6">
@@ -3389,19 +3167,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -3409,19 +3187,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -3429,19 +3207,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -3449,19 +3227,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6">
@@ -3469,19 +3247,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:6">
@@ -3489,19 +3267,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:6">
@@ -3509,19 +3287,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
@@ -3529,19 +3307,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:6">
@@ -3549,19 +3327,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:6">
@@ -3569,19 +3347,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -3589,19 +3367,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
@@ -3609,19 +3387,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:6">
@@ -3629,19 +3407,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:6">
@@ -3649,19 +3427,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:6">
@@ -3669,19 +3447,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:6">
@@ -3689,19 +3467,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:6">
@@ -3709,19 +3487,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:6">
@@ -3729,19 +3507,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:6">
@@ -3749,19 +3527,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:6">
@@ -3769,19 +3547,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:6">
@@ -3789,19 +3567,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:6">
@@ -3809,19 +3587,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:6">
@@ -3829,19 +3607,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:6">
@@ -3849,19 +3627,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:6">
@@ -3869,19 +3647,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:6">
@@ -3889,19 +3667,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:6">
@@ -3909,19 +3687,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:6">
@@ -3929,19 +3707,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
         <x:v>321</x:v>
-      </x:c>
-      <x:c r="D92" s="0" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="E92" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F92" s="0" t="s">
-        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:6">
@@ -3949,19 +3727,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:6">
@@ -3969,19 +3747,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:6">
@@ -3989,19 +3767,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:6">
@@ -4009,19 +3787,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:6">
@@ -4029,19 +3807,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:6">
@@ -4049,19 +3827,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:6">
@@ -4069,19 +3847,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:6">
@@ -4089,19 +3867,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:6">
@@ -4109,19 +3887,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>347</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:6">
@@ -4129,19 +3907,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:6">
@@ -4149,19 +3927,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:6">
@@ -4169,19 +3947,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:6">
@@ -4189,19 +3967,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F105" s="0" t="s">
         <x:v>359</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F105" s="0" t="s">
-        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:6">
@@ -4209,19 +3987,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="E106" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
         <x:v>362</x:v>
-      </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="E106" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F106" s="0" t="s">
-        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:6">
@@ -4229,19 +4007,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>364</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:6">
@@ -4249,19 +4027,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:6">
@@ -4269,19 +4047,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:6">
@@ -4289,19 +4067,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:6">
@@ -4309,19 +4087,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:6">
@@ -4329,19 +4107,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>378</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:6">
@@ -4349,19 +4127,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:6">
@@ -4369,19 +4147,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:6">
@@ -4389,19 +4167,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:6">
@@ -4409,19 +4187,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:6">
@@ -4429,19 +4207,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>393</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:6">
@@ -4449,19 +4227,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:6">
@@ -4469,19 +4247,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:6">
@@ -4489,19 +4267,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:6">
@@ -4509,19 +4287,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:6">
@@ -4529,19 +4307,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:6">
@@ -4549,19 +4327,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:6">
@@ -4569,19 +4347,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:6">
@@ -4589,19 +4367,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>416</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:6">
@@ -4609,19 +4387,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>418</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:6">
@@ -4629,19 +4407,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:6">
@@ -4649,19 +4427,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:6">
@@ -4669,19 +4447,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:6">
@@ -4689,19 +4467,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:6">
@@ -4709,19 +4487,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>433</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:6">
@@ -4729,19 +4507,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:6">
@@ -4749,19 +4527,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>438</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:6">
@@ -4769,19 +4547,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:6">
@@ -4789,19 +4567,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>444</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:6">
@@ -4809,19 +4587,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>447</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:6">
@@ -4829,19 +4607,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:6">
@@ -4849,19 +4627,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>453</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:6">
@@ -4869,19 +4647,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:6">
@@ -4889,19 +4667,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:6">
@@ -4909,19 +4687,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>462</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:6">
@@ -4929,19 +4707,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:6">
@@ -4949,19 +4727,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>468</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:6">
@@ -4969,19 +4747,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:6">
@@ -4989,19 +4767,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
         <x:v>173</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:6">
@@ -5009,19 +4787,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:6">
@@ -5029,19 +4807,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>477</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:6">
@@ -5049,19 +4827,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:6">
@@ -5069,19 +4847,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>483</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:6">
@@ -5089,19 +4867,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:6">
@@ -5109,19 +4887,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:6">
@@ -5129,19 +4907,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>491</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:6">
@@ -5149,19 +4927,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:6">
@@ -5169,19 +4947,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:6">
@@ -5189,19 +4967,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:6">
@@ -5209,459 +4987,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>517</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" spans="1:6">
-      <x:c r="A157" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="D157" s="0" t="s">
-        <x:v>519</x:v>
-      </x:c>
-      <x:c r="E157" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F157" s="0" t="s">
-        <x:v>520</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" spans="1:6">
-      <x:c r="A158" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>521</x:v>
-      </x:c>
-      <x:c r="D158" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="E158" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F158" s="0" t="s">
-        <x:v>522</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" spans="1:6">
-      <x:c r="A159" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C159" s="0" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="D159" s="0" t="s">
-        <x:v>524</x:v>
-      </x:c>
-      <x:c r="E159" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F159" s="0" t="s">
-        <x:v>525</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" spans="1:6">
-      <x:c r="A160" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="C160" s="0" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="D160" s="0" t="s">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="E160" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F160" s="0" t="s">
-        <x:v>528</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:6">
-      <x:c r="A161" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>529</x:v>
-      </x:c>
-      <x:c r="D161" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E161" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F161" s="0" t="s">
-        <x:v>530</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" spans="1:6">
-      <x:c r="A162" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C162" s="0" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="D162" s="0" t="s">
-        <x:v>532</x:v>
-      </x:c>
-      <x:c r="E162" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F162" s="0" t="s">
-        <x:v>533</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" spans="1:6">
-      <x:c r="A163" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>534</x:v>
-      </x:c>
-      <x:c r="C163" s="0" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="D163" s="0" t="s">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c r="E163" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F163" s="0" t="s">
-        <x:v>537</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" spans="1:6">
-      <x:c r="A164" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C164" s="0" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D164" s="0" t="s">
-        <x:v>539</x:v>
-      </x:c>
-      <x:c r="E164" s="0" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F164" s="0" t="s">
-        <x:v>540</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" spans="1:6">
-      <x:c r="A165" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C165" s="0" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="D165" s="0" t="s">
-        <x:v>542</x:v>
-      </x:c>
-      <x:c r="E165" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F165" s="0" t="s">
-        <x:v>543</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" spans="1:6">
-      <x:c r="A166" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C166" s="0" t="s">
-        <x:v>544</x:v>
-      </x:c>
-      <x:c r="D166" s="0" t="s">
-        <x:v>545</x:v>
-      </x:c>
-      <x:c r="E166" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F166" s="0" t="s">
-        <x:v>546</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:6">
-      <x:c r="A167" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>547</x:v>
-      </x:c>
-      <x:c r="C167" s="0" t="s">
-        <x:v>548</x:v>
-      </x:c>
-      <x:c r="D167" s="0" t="s">
         <x:v>504</x:v>
-      </x:c>
-      <x:c r="E167" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F167" s="0" t="s">
-        <x:v>549</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:6">
-      <x:c r="A168" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="D168" s="0" t="s">
-        <x:v>551</x:v>
-      </x:c>
-      <x:c r="E168" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F168" s="0" t="s">
-        <x:v>552</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:6">
-      <x:c r="A169" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="E169" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F169" s="0" t="s">
-        <x:v>554</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:6">
-      <x:c r="A170" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="D170" s="0" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="E170" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F170" s="0" t="s">
-        <x:v>557</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:6">
-      <x:c r="A171" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C171" s="0" t="s">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="D171" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="E171" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F171" s="0" t="s">
-        <x:v>559</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:6">
-      <x:c r="A172" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C172" s="0" t="s">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="D172" s="0" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="E172" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F172" s="0" t="s">
-        <x:v>561</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:6">
-      <x:c r="A173" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B173" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C173" s="0" t="s">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="D173" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="E173" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F173" s="0" t="s">
-        <x:v>563</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:6">
-      <x:c r="A174" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B174" s="0" t="s">
-        <x:v>564</x:v>
-      </x:c>
-      <x:c r="C174" s="0" t="s">
-        <x:v>565</x:v>
-      </x:c>
-      <x:c r="D174" s="0" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="E174" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F174" s="0" t="s">
-        <x:v>567</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:6">
-      <x:c r="A175" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B175" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C175" s="0" t="s">
-        <x:v>568</x:v>
-      </x:c>
-      <x:c r="D175" s="0" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="E175" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F175" s="0" t="s">
-        <x:v>570</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:6">
-      <x:c r="A176" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B176" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C176" s="0" t="s">
-        <x:v>571</x:v>
-      </x:c>
-      <x:c r="D176" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="E176" s="0" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F176" s="0" t="s">
-        <x:v>572</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:6">
-      <x:c r="A177" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B177" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C177" s="0" t="s">
-        <x:v>573</x:v>
-      </x:c>
-      <x:c r="D177" s="0" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="E177" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F177" s="0" t="s">
-        <x:v>575</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:6">
-      <x:c r="A178" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B178" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C178" s="0" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="D178" s="0" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="E178" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F178" s="0" t="s">
-        <x:v>578</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/BOOKING_RESULT_Milan_10_August_2026_15_August_2026_1_guests.xlsx
+++ b/BOOKING_RESULT_Milan_10_August_2026_15_August_2026_1_guests.xlsx
@@ -49,7 +49,88 @@
     <x:t>8.7</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/aiello-hotels-aparthotel-citylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1331556901_405682550_1_2_0&amp;highlighted_blocks=1331556901_405682550_1_2_0&amp;matching_block_id=1331556901_405682550_1_2_0&amp;sr_pri_blocks=1331556901_405682550_1_2_0__96490&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/aiello-hotels-aparthotel-citylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1331556901_405682550_1_2_0&amp;highlighted_blocks=1331556901_405682550_1_2_0&amp;matching_block_id=1331556901_405682550_1_2_0&amp;sr_pri_blocks=1331556901_405682550_1_2_0__96490&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Taddei 14C - Washington</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-monolocale-zona-washington.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=727243102_342454710_0_0_0&amp;highlighted_blocks=727243102_342454710_0_0_0&amp;matching_block_id=727243102_342454710_0_0_0&amp;sr_pri_blocks=727243102_342454710_0_0_0__38690&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Nasco</x:t>
+  </x:si>
+  <x:si>
+    <x:t>143.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/qualys-hotel-nasco.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=8105810_92524515_1_1_0&amp;highlighted_blocks=8105810_92524515_1_1_0&amp;matching_block_id=8105810_92524515_1_1_0&amp;sr_pri_blocks=8105810_92524515_1_1_0__71760&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appartamento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Novi 2 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-penthouse-sui-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1073189802_379864802_2_0_0&amp;highlighted_blocks=1073189802_379864802_2_0_0&amp;matching_block_id=1073189802_379864802_2_0_0&amp;sr_pri_blocks=1073189802_379864802_2_0_0__97496&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Melchiorre Gioia 30 - Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>101.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-incantevole-abitazione-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1067604802_411297452_2_0_0&amp;highlighted_blocks=1067604802_411297452_2_0_0&amp;matching_block_id=1067604802_411297452_2_0_0&amp;sr_pri_blocks=1067604802_411297452_2_0_0__50615&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Two-Bedroom Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brand New Milano Porta Ticinese 70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brand-new-milano-porta-ticinese-70.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1351224001_408190950_1_0_0&amp;highlighted_blocks=1351224001_408190950_1_0_0&amp;matching_block_id=1351224001_408190950_1_0_0&amp;sr_pri_blocks=1351224001_408190950_1_0_0__50105&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Carducci 22 - Sant Ambrogio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>124.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-comoda-residenza-con-terrazzino-abitabile-in-zona-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=983710002_370801600_2_0_0&amp;highlighted_blocks=983710002_370801600_2_0_0&amp;matching_block_id=983710002_370801600_2_0_0&amp;sr_pri_blocks=983710002_370801600_2_0_0__62437&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Apartment with Terrace</x:t>
@@ -64,7 +145,16 @@
     <x:t>8.5</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/collection-city-life-suites-with-terrace-1-top-collection.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1020022002_374798637_1_0_0&amp;highlighted_blocks=1020022002_374798637_1_0_0&amp;matching_block_id=1020022002_374798637_1_0_0&amp;sr_pri_blocks=1020022002_374798637_1_0_0__47518&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/collection-city-life-suites-with-terrace-1-top-collection.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1020022002_374798637_1_0_0&amp;highlighted_blocks=1020022002_374798637_1_0_0&amp;matching_block_id=1020022002_374798637_1_0_0&amp;sr_pri_blocks=1020022002_374798637_1_0_0__47518&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Magenta 83D - Magenta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-monolocale-in-corso-magenta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=955454602_368326497_2_0_0&amp;highlighted_blocks=955454602_368326497_2_0_0&amp;matching_block_id=955454602_368326497_2_0_0&amp;sr_pri_blocks=955454602_368326497_2_0_0__49770&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easystudio Milan - Solari</x:t>
@@ -73,22 +163,7 @@
     <x:t>69</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easystudio-milan-solari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1057394804_377969332_0_0_0&amp;highlighted_blocks=1057394804_377969332_0_0_0&amp;matching_block_id=1057394804_377969332_0_0_0&amp;sr_pri_blocks=1057394804_377969332_0_0_0__34523&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Taddei 14C - Washington</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-monolocale-zona-washington.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=727243102_342454710_0_0_0&amp;highlighted_blocks=727243102_342454710_0_0_0&amp;matching_block_id=727243102_342454710_0_0_0&amp;sr_pri_blocks=727243102_342454710_0_0_0__38690&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easystudio-milan-solari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1057394804_377969332_0_0_0&amp;highlighted_blocks=1057394804_377969332_0_0_0&amp;matching_block_id=1057394804_377969332_0_0_0&amp;sr_pri_blocks=1057394804_377969332_0_0_0__34523&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Cozy Studio in Porta Genova - Via Vigevano</x:t>
@@ -100,7 +175,34 @@
     <x:t>8.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/cozy-studio-in-porta-genova-via-vigevano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1465916401_417912633_1_0_0&amp;highlighted_blocks=1465916401_417912633_1_0_0&amp;matching_block_id=1465916401_417912633_1_0_0&amp;sr_pri_blocks=1465916401_417912633_1_0_0__39805&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/cozy-studio-in-porta-genova-via-vigevano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1465916401_417912633_1_0_0&amp;highlighted_blocks=1465916401_417912633_1_0_0&amp;matching_block_id=1465916401_417912633_1_0_0&amp;sr_pri_blocks=1465916401_417912633_1_0_0__39805&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment (2 Adults)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BB Hotels Aparthotel Visconti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bb-hotels-aparthotel-visconti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=175892501_362128576_2_0_0&amp;highlighted_blocks=175892501_362128576_2_0_0&amp;matching_block_id=175892501_362128576_2_0_0&amp;sr_pri_blocks=175892501_362128576_2_0_0__45250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - MonteNero 29 D - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beautiful-studio-at-10-mins-from-duomo-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=819226901_344556970_0_0_0&amp;highlighted_blocks=819226901_344556970_0_0_0&amp;matching_block_id=819226901_344556970_0_0_0&amp;sr_pri_blocks=819226901_344556970_0_0_0__39590&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Studio with Balcony</x:t>
@@ -115,22 +217,19 @@
     <x:t>9.4</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/studio-1-milano-navigli-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1043157301_376704345_1_1_0_554495&amp;highlighted_blocks=1043157301_376704345_1_1_0_554495&amp;matching_block_id=1043157301_376704345_1_1_0_554495&amp;sr_pri_blocks=1043157301_376704345_1_1_0_554495_42550&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - MonteNero 29 D - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beautiful-studio-at-10-mins-from-duomo-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=819226901_344556970_0_0_0&amp;highlighted_blocks=819226901_344556970_0_0_0&amp;matching_block_id=819226901_344556970_0_0_0&amp;sr_pri_blocks=819226901_344556970_0_0_0__39590&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/studio-1-milano-navigli-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1043157301_376704345_1_1_0_554495&amp;highlighted_blocks=1043157301_376704345_1_1_0_554495&amp;matching_block_id=1043157301_376704345_1_1_0_554495&amp;sr_pri_blocks=1043157301_376704345_1_1_0_554495_42550&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Medium Studio with Kitchenette and Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Numa Milan Sempione</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/numa-milan-sempione.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1244681402_396582596_1_0_0_1190352&amp;highlighted_blocks=1244681402_396582596_1_0_0_1190352&amp;matching_block_id=1244681402_396582596_1_0_0_1190352&amp;sr_pri_blocks=1244681402_396582596_1_0_0_1190352_53200&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>RRRapido apartment - Corso San Gottardo</x:t>
@@ -139,10 +238,232 @@
     <x:t>94.6</x:t>
   </x:si>
   <x:si>
-    <x:t>9.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/rrrapido-apartment-in-corso-san-gottardo-4-people.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1256639301_398209075_1_0_0_568384&amp;highlighted_blocks=1256639301_398209075_1_0_0_568384&amp;matching_block_id=1256639301_398209075_1_0_0_568384&amp;sr_pri_blocks=1256639301_398209075_1_0_0_568384_47250&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/rrrapido-apartment-in-corso-san-gottardo-4-people.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1256639301_398209075_1_0_0_568384&amp;highlighted_blocks=1256639301_398209075_1_0_0_568384&amp;matching_block_id=1256639301_398209075_1_0_0_568384&amp;sr_pri_blocks=1256639301_398209075_1_0_0_568384_47250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Michelangelo Navigli Loft Experience - Via Magolfa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/michelangelo-navigli-loft-experience-via-magolfa.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1049649204_377218682_1_0_0&amp;highlighted_blocks=1049649204_377218682_1_0_0&amp;matching_block_id=1049649204_377218682_1_0_0&amp;sr_pri_blocks=1049649204_377218682_1_0_0__37750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Smart Apartment - Milan Downtown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/smart-apartment-milan-downtown.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=479462701_152647240_1_0_0&amp;highlighted_blocks=479462701_152647240_1_0_0&amp;matching_block_id=479462701_152647240_1_0_0&amp;sr_pri_blocks=479462701_152647240_1_0_0__37430&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Crema 23 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/modern-and-central-apt-in-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=395164201_122892247_2_0_0&amp;highlighted_blocks=395164201_122892247_2_0_0&amp;matching_block_id=395164201_122892247_2_0_0&amp;sr_pri_blocks=395164201_122892247_2_0_0__46266&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Pier Lombardo 16 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nice-and-cozy-studio-in-porta-romana-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=794224002_342458649_0_0_0&amp;highlighted_blocks=794224002_342458649_0_0_0&amp;matching_block_id=794224002_342458649_0_0_0&amp;sr_pri_blocks=794224002_342458649_0_0_0__43178&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Lecco 11P3 - Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>113.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/tropical-and-new-flat-in-porta-venezia-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=881074302_411297533_2_0_0&amp;highlighted_blocks=881074302_411297533_2_0_0&amp;matching_block_id=881074302_411297533_2_0_0&amp;sr_pri_blocks=881074302_411297533_2_0_0__56758&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Moscati 9A - Sarpi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-moderno-apt-con-terrazzo-in-paolo-sarpi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=984198602_411297670_2_0_0&amp;highlighted_blocks=984198602_411297670_2_0_0&amp;matching_block_id=984198602_411297670_2_0_0&amp;sr_pri_blocks=984198602_411297670_2_0_0__51397&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Lounge Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/urban-lounge-apartments-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1398661305_411733212_1_0_0&amp;highlighted_blocks=1398661305_411733212_1_0_0&amp;matching_block_id=1398661305_411733212_1_0_0&amp;sr_pri_blocks=1398661305_411733212_1_0_0__58983&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Triple Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loreto Prestige - Parking Free &amp; Bulb Gym</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/loreto-prestige.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1239873204_395916420_3_0_0&amp;highlighted_blocks=1239873204_395916420_3_0_0&amp;matching_block_id=1239873204_395916420_3_0_0&amp;sr_pri_blocks=1239873204_395916420_3_0_0__48750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Crocetta 2 P1S - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-moderno-bilocale-in-zona-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=26&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=913089902_411297669_2_0_0&amp;highlighted_blocks=913089902_411297669_2_0_0&amp;matching_block_id=913089902_411297669_2_0_0&amp;sr_pri_blocks=913089902_411297669_2_0_0__54018&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residenza Cenisio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-cenisio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=27&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=28567108_88453047_0_0_0&amp;highlighted_blocks=28567108_88453047_0_0_0&amp;matching_block_id=28567108_88453047_0_0_0&amp;sr_pri_blocks=28567108_88453047_0_0_0__41865&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Hub Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/urban-hub-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=28&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1379458101_410069510_1_0_0&amp;highlighted_blocks=1379458101_410069510_1_0_0&amp;matching_block_id=1379458101_410069510_1_0_0&amp;sr_pri_blocks=1379458101_410069510_1_0_0__45916&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Modrone 28 S1 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>114.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cityscape-milan-design-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=29&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1122526001_385012587_1_0_0&amp;highlighted_blocks=1122526001_385012587_1_0_0&amp;matching_block_id=1122526001_385012587_1_0_0&amp;sr_pri_blocks=1122526001_385012587_1_0_0__57277&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milano Apartments Lombardini 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>159.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-apartments-lombardini-1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=30&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1222632502_423019779_1_0_0&amp;highlighted_blocks=1222632502_423019779_1_0_0&amp;matching_block_id=1222632502_423019779_1_0_0&amp;sr_pri_blocks=1222632502_423019779_1_0_0__79750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piranesi 246</x:t>
+  </x:si>
+  <x:si>
+    <x:t>177.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/piranesi-246.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=31&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=340652502_384712436_2_0_0&amp;highlighted_blocks=340652502_384712436_2_0_0&amp;matching_block_id=340652502_384712436_2_0_0&amp;sr_pri_blocks=340652502_384712436_2_0_0__88750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loft</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milan Royal Suites - Centro Cadorna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>161.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-magenta-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=32&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=86366116_88472507_2_0_0&amp;highlighted_blocks=86366116_88472507_2_0_0&amp;matching_block_id=86366116_88472507_2_0_0&amp;sr_pri_blocks=86366116_88472507_2_0_0__80926&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Superior Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residenza delle Città</x:t>
+  </x:si>
+  <x:si>
+    <x:t>136.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-delle-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=33&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=4270803_381695069_2_0_0&amp;highlighted_blocks=4270803_381695069_2_0_0&amp;matching_block_id=4270803_381695069_2_0_0&amp;sr_pri_blocks=4270803_381695069_2_0_0__68301&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio Apartment with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Cloud Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/urban-cloud-by-blue-velvet-livings.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=34&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1283884502_401326573_1_0_0&amp;highlighted_blocks=1283884502_401326573_1_0_0&amp;matching_block_id=1283884502_401326573_1_0_0&amp;sr_pri_blocks=1283884502_401326573_1_0_0__46466&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Landscape Flats</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/landscape-flats.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=35&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1250259201_397504852_1_0_0&amp;highlighted_blocks=1250259201_397504852_1_0_0&amp;matching_block_id=1250259201_397504852_1_0_0&amp;sr_pri_blocks=1250259201_397504852_1_0_0__57554&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Cerano 6 - Tortona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-il-tuo-spazio-ideale-a-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=36&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1391665202_411134582_2_0_0&amp;highlighted_blocks=1391665202_411134582_2_0_0&amp;matching_block_id=1391665202_411134582_2_0_0&amp;sr_pri_blocks=1391665202_411134582_2_0_0__53018&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elegante bilocale San Calocero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>147.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/elegante-bilocale-san-calocero.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=37&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1075591401_402147700_2_0_0&amp;highlighted_blocks=1075591401_402147700_2_0_0&amp;matching_block_id=1075591401_402147700_2_0_0&amp;sr_pri_blocks=1075591401_402147700_2_0_0__73887&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appartamento con 1 Camera da Letto – Via della Spiga 46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments in Via della Spiga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>170.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/spiga-46-suites-by-brera-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=38&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=989858402_371633451_2_0_0&amp;highlighted_blocks=989858402_371633451_2_0_0&amp;matching_block_id=989858402_371633451_2_0_0&amp;sr_pri_blocks=989858402_371633451_2_0_0__85415&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Deluxe Double Studio</x:t>
@@ -151,118 +472,31 @@
     <x:t>Palazzo Quantum 1</x:t>
   </x:si>
   <x:si>
-    <x:t>89.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/palazzo-quantum-1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1187317004_391089422_1_0_0&amp;highlighted_blocks=1187317004_391089422_1_0_0&amp;matching_block_id=1187317004_391089422_1_0_0&amp;sr_pri_blocks=1187317004_391089422_1_0_0__44660&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Smart Apartment - Milan Downtown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/smart-apartment-milan-downtown.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=479462701_152647240_1_0_0&amp;highlighted_blocks=479462701_152647240_1_0_0&amp;matching_block_id=479462701_152647240_1_0_0&amp;sr_pri_blocks=479462701_152647240_1_0_0__37430&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Superior Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hotel Nasco</x:t>
-  </x:si>
-  <x:si>
-    <x:t>143.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/qualys-hotel-nasco.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=8105810_92524515_1_1_0&amp;highlighted_blocks=8105810_92524515_1_1_0&amp;matching_block_id=8105810_92524515_1_1_0&amp;sr_pri_blocks=8105810_92524515_1_1_0__71760&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Urban Lounge Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/urban-lounge-apartments-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1398661303_411733212_1_0_0&amp;highlighted_blocks=1398661303_411733212_1_0_0&amp;matching_block_id=1398661303_411733212_1_0_0&amp;sr_pri_blocks=1398661303_411733212_1_0_0__58983&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Appartamento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Novi 2 - Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-penthouse-sui-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1073189802_379864802_2_0_0&amp;highlighted_blocks=1073189802_379864802_2_0_0&amp;matching_block_id=1073189802_379864802_2_0_0&amp;sr_pri_blocks=1073189802_379864802_2_0_0__97496&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Melchiorre Gioia 30 - Centrale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>101.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-incantevole-abitazione-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1067604802_411297452_2_0_0&amp;highlighted_blocks=1067604802_411297452_2_0_0&amp;matching_block_id=1067604802_411297452_2_0_0&amp;sr_pri_blocks=1067604802_411297452_2_0_0__50615&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milano Apartments Lombardini 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>159.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milano-apartments-lombardini-1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1222632502_423019779_1_0_0&amp;highlighted_blocks=1222632502_423019779_1_0_0&amp;matching_block_id=1222632502_423019779_1_0_0&amp;sr_pri_blocks=1222632502_423019779_1_0_0__79750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Cerano 6 - Tortona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-il-tuo-spazio-ideale-a-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1391665202_411134582_2_0_0&amp;highlighted_blocks=1391665202_411134582_2_0_0&amp;matching_block_id=1391665202_411134582_2_0_0&amp;sr_pri_blocks=1391665202_411134582_2_0_0__53018&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loft</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milan Royal Suites - Centro Cadorna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>161.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-magenta-palace.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=86366116_88472507_2_0_0&amp;highlighted_blocks=86366116_88472507_2_0_0&amp;matching_block_id=86366116_88472507_2_0_0&amp;sr_pri_blocks=86366116_88472507_2_0_0__80926&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio Apartment with Balcony</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Urban Cloud Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/urban-cloud-by-blue-velvet-livings.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1283884502_401326573_1_0_0&amp;highlighted_blocks=1283884502_401326573_1_0_0&amp;matching_block_id=1283884502_401326573_1_0_0&amp;sr_pri_blocks=1283884502_401326573_1_0_0__46466&amp;from=searchresults</x:t>
+    <x:t>99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/palazzo-quantum-1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=39&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1187317004_391089422_1_0_0&amp;highlighted_blocks=1187317004_391089422_1_0_0&amp;matching_block_id=1187317004_391089422_1_0_0&amp;sr_pri_blocks=1187317004_391089422_1_0_0__49502&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>King Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Collection Moscova Suites 8 - Top Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/via-volta-apartment-moscova.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=40&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=643475901_403644755_2_0_0&amp;highlighted_blocks=643475901_403644755_2_0_0&amp;matching_block_id=643475901_403644755_2_0_0&amp;sr_pri_blocks=643475901_403644755_2_0_0__72370&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APARTHOTEL CASA MIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aparthotel-casa-mia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=41&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=481374404_361771404_0_0_0&amp;highlighted_blocks=481374404_361771404_0_0_0&amp;matching_block_id=481374404_361771404_0_0_0&amp;sr_pri_blocks=481374404_361771404_0_0_0__79750&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>[City life-Milano]Bright suite - Relax&amp;Deluxe</x:t>
@@ -271,223 +505,862 @@
     <x:t>91.6</x:t>
   </x:si>
   <x:si>
-    <x:t>9.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/city-life-milano-bright-suite-relax-amp-deluxe.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=957195001_368340079_2_0_0&amp;highlighted_blocks=957195001_368340079_2_0_0&amp;matching_block_id=957195001_368340079_2_0_0&amp;sr_pri_blocks=957195001_368340079_2_0_0__45800&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Superior Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Residenza delle Città</x:t>
-  </x:si>
-  <x:si>
-    <x:t>136.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/residenza-delle-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=4270803_381695069_2_0_0&amp;highlighted_blocks=4270803_381695069_2_0_0&amp;matching_block_id=4270803_381695069_2_0_0&amp;sr_pri_blocks=4270803_381695069_2_0_0__68301&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>King Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Collection Moscova Suites 8 - Top Collection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/via-volta-apartment-moscova.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=643475901_403644755_2_0_0&amp;highlighted_blocks=643475901_403644755_2_0_0&amp;matching_block_id=643475901_403644755_2_0_0&amp;sr_pri_blocks=643475901_403644755_2_0_0__72370&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom House</x:t>
+    <x:t>https://www.booking.com/hotel/it/city-life-milano-bright-suite-relax-amp-deluxe.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=42&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=957195001_368340079_2_0_0&amp;highlighted_blocks=957195001_368340079_2_0_0&amp;matching_block_id=957195001_368340079_2_0_0&amp;sr_pri_blocks=957195001_368340079_2_0_0__45800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Garigliano 10 - Isola</x:t>
+  </x:si>
+  <x:si>
+    <x:t>128.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-unita-su-due-livelli-a-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=43&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1179646202_390438749_2_0_0&amp;highlighted_blocks=1179646202_390438749_2_0_0&amp;matching_block_id=1179646202_390438749_2_0_0&amp;sr_pri_blocks=1179646202_390438749_2_0_0__64110&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agave in Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>198</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/agave-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=44&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1358611104_408185144_1_2_0&amp;highlighted_blocks=1358611104_408185144_1_2_0&amp;matching_block_id=1358611104_408185144_1_2_0&amp;sr_pri_blocks=1358611104_408185144_1_2_0__99003&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Lecco 5 P2 - in Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>107.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-comodo-appartamento-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=45&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1154859902_388280300_2_0_0&amp;highlighted_blocks=1154859902_388280300_2_0_0&amp;matching_block_id=1154859902_388280300_2_0_0&amp;sr_pri_blocks=1154859902_388280300_2_0_0__53837&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Velasca Tower Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>155.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/velasca-tower-apartments-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=46&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=1275181361_400377746_1_0_0&amp;highlighted_blocks=1275181361_400377746_1_0_0&amp;matching_block_id=1275181361_400377746_1_0_0&amp;sr_pri_blocks=1275181361_400377746_1_0_0__77730&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EasyTopStay - Moscova Modern Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/moscova-modern-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=47&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=905968401_361678059_2_0_0_852695&amp;highlighted_blocks=905968401_361678059_2_0_0_852695&amp;matching_block_id=905968401_361678059_2_0_0_852695&amp;sr_pri_blocks=905968401_361678059_2_0_0_852695_73086&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Maffucci 53 - Dergano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-dimora-con-balcone.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=48&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=987239102_411297538_2_0_0&amp;highlighted_blocks=987239102_411297538_2_0_0&amp;matching_block_id=987239102_411297538_2_0_0&amp;sr_pri_blocks=987239102_411297538_2_0_0__48141&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hbhall Residenze Darsena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/blu-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=49&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=101681804_88400138_2_0_0&amp;highlighted_blocks=101681804_88400138_2_0_0&amp;matching_block_id=101681804_88400138_2_0_0&amp;sr_pri_blocks=101681804_88400138_2_0_0__46699&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Friuli 15 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/stupendo-e-accogliente-apt-15-min-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=50&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134630&amp;all_sr_blocks=609060802_277504331_2_0_0&amp;highlighted_blocks=609060802_277504331_2_0_0&amp;matching_block_id=609060802_277504331_2_0_0&amp;sr_pri_blocks=609060802_277504331_2_0_0__50971&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BnButler - Archimede 53 - Bright Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/monolocale-con-spazio-esterno.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=51&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=968435001_369272242_2_0_0&amp;highlighted_blocks=968435001_369272242_2_0_0&amp;matching_block_id=968435001_369272242_2_0_0&amp;sr_pri_blocks=968435001_369272242_2_0_0__53278&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Washington 91 p7 - Solari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-appartamento-in-solari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=52&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1085204302_381393382_2_0_0&amp;highlighted_blocks=1085204302_381393382_2_0_0&amp;matching_block_id=1085204302_381393382_2_0_0&amp;sr_pri_blocks=1085204302_381393382_2_0_0__54814&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment with City View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Garibaldi 59 apartments in Brera district by Rentopolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>145.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/corso-garibaldi-modern-cozy-suite-by-rentopolis.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=53&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1307085603_403526015_1_0_0&amp;highlighted_blocks=1307085603_403526015_1_0_0&amp;matching_block_id=1307085603_403526015_1_0_0&amp;sr_pri_blocks=1307085603_403526015_1_0_0__72652&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAR RIBBON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/star-ribbon.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=54&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=794654902_339549249_2_2_0&amp;highlighted_blocks=794654902_339549249_2_2_0&amp;matching_block_id=794654902_339549249_2_2_0&amp;sr_pri_blocks=794654902_339549249_2_2_0__57985&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - DellaChiusa 8 - Porta Ticinese</x:t>
+  </x:si>
+  <x:si>
+    <x:t>153.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-pearl-with-balcony-on-ticinese-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=55&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1311590301_403939277_2_0_0&amp;highlighted_blocks=1311590301_403939277_2_0_0&amp;matching_block_id=1311590301_403939277_2_0_0&amp;sr_pri_blocks=1311590301_403939277_2_0_0__76798&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio - Annex</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Andreola Central Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>139.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/andreolacentralhotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=56&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=8078766_88153824_0_33_0&amp;highlighted_blocks=8078766_88153824_0_33_0&amp;matching_block_id=8078766_88153824_0_33_0&amp;sr_pri_blocks=8078766_88153824_0_33_0__69800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residence 2Gi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ajraghi-halldis-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=57&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=122518401_98061898_1_0_0&amp;highlighted_blocks=122518401_98061898_1_0_0&amp;matching_block_id=122518401_98061898_1_0_0&amp;sr_pri_blocks=122518401_98061898_1_0_0__69000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EasyTopStay - Porta Romana Lovely Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>118.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/porta-romana-lovely-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=58&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1186688801_391031971_2_0_0_852711&amp;highlighted_blocks=1186688801_391031971_2_0_0_852711&amp;matching_block_id=1186688801_391031971_2_0_0_852711&amp;sr_pri_blocks=1186688801_391031971_2_0_0_852711_59358&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Pisacane 19 - Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>121.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easy-life-elegante-trilocale-in-zona-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=59&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=952472502_411297279_2_0_0&amp;highlighted_blocks=952472502_411297279_2_0_0&amp;matching_block_id=952472502_411297279_2_0_0&amp;sr_pri_blocks=952472502_411297279_2_0_0__60745&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartment - Ground Floor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Villa Massari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/italian-residencies-villa-massari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=60&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=970311603_369428409_2_0_0&amp;highlighted_blocks=970311603_369428409_2_0_0&amp;matching_block_id=970311603_369428409_2_0_0&amp;sr_pri_blocks=970311603_369428409_2_0_0__51145&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chichouse Maderno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/chichouse-maderno.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=61&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1274893601_400341987_1_0_0&amp;highlighted_blocks=1274893601_400341987_1_0_0&amp;matching_block_id=1274893601_400341987_1_0_0&amp;sr_pri_blocks=1274893601_400341987_1_0_0__49225&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Elite apartments in Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elite-apartments-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=62&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1402940003_412109324_2_0_0&amp;highlighted_blocks=1402940003_412109324_2_0_0&amp;matching_block_id=1402940003_412109324_2_0_0&amp;sr_pri_blocks=1402940003_412109324_2_0_0__47171&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Broggi 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/b-family.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=63&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1136928703_386305137_2_0_0&amp;highlighted_blocks=1136928703_386305137_2_0_0&amp;matching_block_id=1136928703_386305137_2_0_0&amp;sr_pri_blocks=1136928703_386305137_2_0_0__73350&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Albani 20 - City Life</x:t>
+  </x:si>
+  <x:si>
+    <x:t>150.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-modern-and-spacious-apt-in-fiera-city-life.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=64&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=753188602_342458560_2_0_0&amp;highlighted_blocks=753188602_342458560_2_0_0&amp;matching_block_id=753188602_342458560_2_0_0&amp;sr_pri_blocks=753188602_342458560_2_0_0__75321&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Borgonuovo 4D - Centro Storico</x:t>
+  </x:si>
+  <x:si>
+    <x:t>142.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/stylish-and-fancy-flat-close-to-montenapoleone-brera-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=65&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=801095402_342458597_0_0_0&amp;highlighted_blocks=801095402_342458597_0_0_0&amp;matching_block_id=801095402_342458597_0_0_0&amp;sr_pri_blocks=801095402_342458597_0_0_0__71326&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nolo 5 - Apartment Milano - Leia Hospitality</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nolo-5-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=66&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1392076801_411171430_1_0_0&amp;highlighted_blocks=1392076801_411171430_1_0_0&amp;matching_block_id=1392076801_411171430_1_0_0&amp;sr_pri_blocks=1392076801_411171430_1_0_0__50635&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Recanate 5 - Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>104.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-bello-e-luminoso-flat-in-zona-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=67&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=715255402_342454734_2_0_0&amp;highlighted_blocks=715255402_342454734_2_0_0&amp;matching_block_id=715255402_342454734_2_0_0&amp;sr_pri_blocks=715255402_342454734_2_0_0__52118&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ht maison montenero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ht-maison-montenero.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=68&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1455900401_416890977_2_0_0&amp;highlighted_blocks=1455900401_416890977_2_0_0&amp;matching_block_id=1455900401_416890977_2_0_0&amp;sr_pri_blocks=1455900401_416890977_2_0_0__63255&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Gregorio 17 P2 - Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>140.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-confortevola-dimora-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=69&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1010372102_411297589_2_0_0&amp;highlighted_blocks=1010372102_411297589_2_0_0&amp;matching_block_id=1010372102_411297589_2_0_0&amp;sr_pri_blocks=1010372102_411297589_2_0_0__70168&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BB Hotels Aparthotel Isola</x:t>
+  </x:si>
+  <x:si>
+    <x:t>110.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bb-hotels-aparthotel-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=70&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=274589509_362128569_2_0_0&amp;highlighted_blocks=274589509_362128569_2_0_0&amp;matching_block_id=274589509_362128569_2_0_0&amp;sr_pri_blocks=274589509_362128569_2_0_0__55250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartment with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Downtown Apartments Merlo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>164</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/downtown-apartment-merlo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=71&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=389558701_122225007_0_0_0&amp;highlighted_blocks=389558701_122225007_0_0_0&amp;matching_block_id=389558701_122225007_0_0_0&amp;sr_pri_blocks=389558701_122225007_0_0_0__81998&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - San Marco 1 - Brera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>129.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/wonderful-brera-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=72&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=483462501_157562430_2_0_0&amp;highlighted_blocks=483462501_157562430_2_0_0&amp;matching_block_id=483462501_157562430_2_0_0&amp;sr_pri_blocks=483462501_157562430_2_0_0__64772&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELIO, 11 – Appartamento con terrazzo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>129</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/celio-11-appartamento-con-terrazzo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=73&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=1100915201_382929317_2_0_0&amp;highlighted_blocks=1100915201_382929317_2_0_0&amp;matching_block_id=1100915201_382929317_2_0_0&amp;sr_pri_blocks=1100915201_382929317_2_0_0__64462&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe King Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milan Downtown Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>181.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-cozy-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=74&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=832001102_348396804_1_0_0&amp;highlighted_blocks=832001102_348396804_1_0_0&amp;matching_block_id=832001102_348396804_1_0_0&amp;sr_pri_blocks=832001102_348396804_1_0_0__90788&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BePlace Apartments in De Angeli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-de-angeli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=75&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134632&amp;all_sr_blocks=991814201_372153726_2_0_0&amp;highlighted_blocks=991814201_372153726_2_0_0&amp;matching_block_id=991814201_372153726_2_0_0&amp;sr_pri_blocks=991814201_372153726_2_0_0__72110&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Amedei 6 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>195.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-dimora-a-due-passi-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=76&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1026106302_411297428_2_0_0&amp;highlighted_blocks=1026106302_411297428_2_0_0&amp;matching_block_id=1026106302_411297428_2_0_0&amp;sr_pri_blocks=1026106302_411297428_2_0_0__97577&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Three-Bedroom Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BeCO Sempione Luxury Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beco-sempione-luxury-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=78&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1377862001_410273239_4_0_0&amp;highlighted_blocks=1377862001_410273239_4_0_0&amp;matching_block_id=1377862001_410273239_4_0_0&amp;sr_pri_blocks=1377862001_410273239_4_0_0__91003&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN RIBBON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/green-ribbon.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=79&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=643672411_263835080_2_2_0&amp;highlighted_blocks=643672411_263835080_2_2_0&amp;matching_block_id=643672411_263835080_2_2_0&amp;sr_pri_blocks=643672411_263835080_2_2_0__57985&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>easyhomes - Repubblica</x:t>
+  </x:si>
+  <x:si>
+    <x:t>167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easyhomes-repubblica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=80&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1377078001_409835078_2_0_0&amp;highlighted_blocks=1377078001_409835078_2_0_0&amp;matching_block_id=1377078001_409835078_2_0_0&amp;sr_pri_blocks=1377078001_409835078_2_0_0__83500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boccaccio's Flats</x:t>
+  </x:si>
+  <x:si>
+    <x:t>142.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/boccaccios-flats.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=81&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1042477701_376658104_2_0_0&amp;highlighted_blocks=1042477701_376658104_2_0_0&amp;matching_block_id=1042477701_376658104_2_0_0&amp;sr_pri_blocks=1042477701_376658104_2_0_0__71421&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marco Polo Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>148.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/marco-polo-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=82&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=772964101_335686385_1_0_0_704773&amp;highlighted_blocks=772964101_335686385_1_0_0_704773&amp;matching_block_id=772964101_335686385_1_0_0_704773&amp;sr_pri_blocks=772964101_335686385_1_0_0_704773_74250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Buenos Aires</x:t>
+  </x:si>
+  <x:si>
+    <x:t>137.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/casa-buenos-aires.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=83&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1338765801_406815097_2_0_0&amp;highlighted_blocks=1338765801_406815097_2_0_0&amp;matching_block_id=1338765801_406815097_2_0_0&amp;sr_pri_blocks=1338765801_406815097_2_0_0__68750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Modrone 8-1 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>119.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-san-babila-elegante-e-rifinito-bilocale-nel-cuore-della-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=84&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=971442802_411297516_2_0_0&amp;highlighted_blocks=971442802_411297516_2_0_0&amp;matching_block_id=971442802_411297516_2_0_0&amp;sr_pri_blocks=971442802_411297516_2_0_0__59896&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Correnti 24 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>141.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/elegante-e-completamente-arredato-apt-in-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=85&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=414851001_126389632_2_0_0&amp;highlighted_blocks=414851001_126389632_2_0_0&amp;matching_block_id=414851001_126389632_2_0_0&amp;sr_pri_blocks=414851001_126389632_2_0_0__70569&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Monolocale - Via San Carpoforo 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brera-23-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=86&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=211137009_95948739_0_0_0&amp;highlighted_blocks=211137009_95948739_0_0_0&amp;matching_block_id=211137009_95948739_0_0_0&amp;sr_pri_blocks=211137009_95948739_0_0_0__74332&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUVI - Adda</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cozy-apartments-near-central-station.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=87&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1302638301_403134808_2_0_0&amp;highlighted_blocks=1302638301_403134808_2_0_0&amp;matching_block_id=1302638301_403134808_2_0_0&amp;sr_pri_blocks=1302638301_403134808_2_0_0__58990&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment - Piazza Monte Falterona 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BePlace Apartments in Fiera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-fiera.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=88&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=948093101_367386831_2_0_0&amp;highlighted_blocks=948093101_367386831_2_0_0&amp;matching_block_id=948093101_367386831_2_0_0&amp;sr_pri_blocks=948093101_367386831_2_0_0__59470&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>CASATI CENTRAL STATION Metro M1, M2, M3</x:t>
   </x:si>
   <x:si>
-    <x:t>146.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/casati-central-station-metro-m1-m2-m3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1366308501_408912923_2_0_0&amp;highlighted_blocks=1366308501_408912923_2_0_0&amp;matching_block_id=1366308501_408912923_2_0_0&amp;sr_pri_blocks=1366308501_408912923_2_0_0__73056&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Two-Bedroom Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BnButler - Cesare Brivio, 21 - Ampio e Luminoso</x:t>
-  </x:si>
-  <x:si>
-    <x:t>129.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brivio-21-ampio-e-luminoso.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=979437801_370203701_2_0_0&amp;highlighted_blocks=979437801_370203701_2_0_0&amp;matching_block_id=979437801_370203701_2_0_0&amp;sr_pri_blocks=979437801_370203701_2_0_0__64568&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brand New Milano Porta Ticinese 70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/brand-new-milano-porta-ticinese-70.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1351224001_408190950_1_0_0&amp;highlighted_blocks=1351224001_408190950_1_0_0&amp;matching_block_id=1351224001_408190950_1_0_0&amp;sr_pri_blocks=1351224001_408190950_1_0_0__50105&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Chichouse Maderno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/chichouse-maderno.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=26&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1274893601_400341987_1_0_0&amp;highlighted_blocks=1274893601_400341987_1_0_0&amp;matching_block_id=1274893601_400341987_1_0_0&amp;sr_pri_blocks=1274893601_400341987_1_0_0__49225&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Deluxe King Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hbhall Residenze Darsena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/blu-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=27&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=101681818_88400138_2_0_0&amp;highlighted_blocks=101681818_88400138_2_0_0&amp;matching_block_id=101681818_88400138_2_0_0&amp;sr_pri_blocks=101681818_88400138_2_0_0__46699&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment with City View</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Garibaldi 59 apartments in Brera district by Rentopolis</x:t>
-  </x:si>
-  <x:si>
-    <x:t>145.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/corso-garibaldi-modern-cozy-suite-by-rentopolis.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=28&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1307085603_403526015_1_0_0&amp;highlighted_blocks=1307085603_403526015_1_0_0&amp;matching_block_id=1307085603_403526015_1_0_0&amp;sr_pri_blocks=1307085603_403526015_1_0_0__72652&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Elite apartments in Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elite-apartments-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=29&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1402940003_412109324_2_0_0&amp;highlighted_blocks=1402940003_412109324_2_0_0&amp;matching_block_id=1402940003_412109324_2_0_0&amp;sr_pri_blocks=1402940003_412109324_2_0_0__47171&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nolo 5 - Apartment Milano - Leia Hospitality</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/nolo-5-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=30&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1392076801_411171430_1_0_0&amp;highlighted_blocks=1392076801_411171430_1_0_0&amp;matching_block_id=1392076801_411171430_1_0_0&amp;sr_pri_blocks=1392076801_411171430_1_0_0__50635&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Apartment - Ground Floor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Villa Massari</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/italian-residencies-villa-massari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=31&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=970311603_369428409_2_0_0&amp;highlighted_blocks=970311603_369428409_2_0_0&amp;matching_block_id=970311603_369428409_2_0_0&amp;sr_pri_blocks=970311603_369428409_2_0_0__51145&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Carducci 22 - Sant Ambrogio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>124.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-comoda-residenza-con-terrazzino-abitabile-in-zona-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=32&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=983710002_370801600_2_0_0&amp;highlighted_blocks=983710002_370801600_2_0_0&amp;matching_block_id=983710002_370801600_2_0_0&amp;sr_pri_blocks=983710002_370801600_2_0_0__62437&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milan Downtown Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>181.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milano-cozy-apartment-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=33&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=832001102_348396804_1_0_0&amp;highlighted_blocks=832001102_348396804_1_0_0&amp;matching_block_id=832001102_348396804_1_0_0&amp;sr_pri_blocks=832001102_348396804_1_0_0__90788&amp;from=searchresults</x:t>
+    <x:t>156.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/casati-central-station-metro-m1-m2-m3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=89&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1366308502_408912923_2_0_0&amp;highlighted_blocks=1366308502_408912923_2_0_0&amp;matching_block_id=1366308502_408912923_2_0_0&amp;sr_pri_blocks=1366308502_408912923_2_0_0__78300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Villa Aida</x:t>
+  </x:si>
+  <x:si>
+    <x:t>199.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/villa-aida.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=90&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=150415805_91955825_1_2_0_743654&amp;highlighted_blocks=150415805_91955825_1_2_0_743654&amp;matching_block_id=150415805_91955825_1_2_0_743654&amp;sr_pri_blocks=150415805_91955825_1_2_0_743654_99819&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment with Terrace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toiletpaper Living</x:t>
+  </x:si>
+  <x:si>
+    <x:t>190.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/toiletpaper-living.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=92&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1184641401_390835896_2_0_0&amp;highlighted_blocks=1184641401_390835896_2_0_0&amp;matching_block_id=1184641401_390835896_2_0_0&amp;sr_pri_blocks=1184641401_390835896_2_0_0__95275&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Le scuderie di Sant'Ambrogio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>166.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/terraggio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=94&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=253069601_103872408_2_0_0_666040&amp;highlighted_blocks=253069601_103872408_2_0_0_666040&amp;matching_block_id=253069601_103872408_2_0_0_666040&amp;sr_pri_blocks=253069601_103872408_2_0_0_666040_83060&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Torino 34D - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>141.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/amazing-new-amp-fully-furnished-studio-in-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=95&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=414193401_126133859_2_0_0&amp;highlighted_blocks=414193401_126133859_2_0_0&amp;matching_block_id=414193401_126133859_2_0_0&amp;sr_pri_blocks=414193401_126133859_2_0_0__70726&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Golden Prestige</x:t>
+  </x:si>
+  <x:si>
+    <x:t>184.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/luxury-flat-repubblica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=96&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=332276103_115726847_1_0_0&amp;highlighted_blocks=332276103_115726847_1_0_0&amp;matching_block_id=332276103_115726847_1_0_0&amp;sr_pri_blocks=332276103_115726847_1_0_0__92333&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Dugnani 4 - Sant' Ambrogio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-comfortable-apartment-in-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=97&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1240198501_395931229_2_0_0&amp;highlighted_blocks=1240198501_395931229_2_0_0&amp;matching_block_id=1240198501_395931229_2_0_0&amp;sr_pri_blocks=1240198501_395931229_2_0_0__45841&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bramante Luxury Apartments by InnStay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bramante-luxury-apartments-by-innstay.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=98&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=1392064301_411170762_1_0_0&amp;highlighted_blocks=1392064301_411170762_1_0_0&amp;matching_block_id=1392064301_411170762_1_0_0&amp;sr_pri_blocks=1392064301_411170762_1_0_0__66017&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One Bedroom Apartment (Via Broletto 26)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments Alla Scala</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brera-apartments-alla-scala.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=99&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=197393703_93885030_2_0_0&amp;highlighted_blocks=197393703_93885030_2_0_0&amp;matching_block_id=197393703_93885030_2_0_0&amp;sr_pri_blocks=197393703_93885030_2_0_0__85415&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RED RIBBON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/red-ribbon.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=100&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134634&amp;all_sr_blocks=643669302_263831163_2_2_0&amp;highlighted_blocks=643669302_263831163_2_2_0&amp;matching_block_id=643669302_263831163_2_2_0&amp;sr_pri_blocks=643669302_263831163_2_2_0__50345&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUOMO VIEW - 2 min from Duomo Amazing location</x:t>
+  </x:si>
+  <x:si>
+    <x:t>173.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/duomo-view-2-min-from-duomo-amazing-location.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=101&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1132300201_385862129_2_0_0&amp;highlighted_blocks=1132300201_385862129_2_0_0&amp;matching_block_id=1132300201_385862129_2_0_0&amp;sr_pri_blocks=1132300201_385862129_2_0_0__86612&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Modrone 28 PT - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-moderno-rifugio-a-due-passi-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=103&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1065754302_411297157_2_0_0&amp;highlighted_blocks=1065754302_411297157_2_0_0&amp;matching_block_id=1065754302_411297157_2_0_0&amp;sr_pri_blocks=1065754302_411297157_2_0_0__59896&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUOMO - The Warm Maison - EXCLUSIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>154.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-warm-maison-duomo-700m.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=104&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=947727801_367351474_2_0_0&amp;highlighted_blocks=947727801_367351474_2_0_0&amp;matching_block_id=947727801_367351474_2_0_0&amp;sr_pri_blocks=947727801_367351474_2_0_0__77062&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio Upper Floor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milan Eleven by Brera Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milan-eleven-by-brera-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=105&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=694969603_285647587_1_0_0&amp;highlighted_blocks=694969603_285647587_1_0_0&amp;matching_block_id=694969603_285647587_1_0_0&amp;sr_pri_blocks=694969603_285647587_1_0_0__95530&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife Milano - Santa Maria Valle 4 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>164.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/spacious-comfortable-apartment-in-duomo-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=106&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=801094902_342458644_2_0_0&amp;highlighted_blocks=801094902_342458644_2_0_0&amp;matching_block_id=801094902_342458644_2_0_0&amp;sr_pri_blocks=801094902_342458644_2_0_0__82152&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Suffragio 3 - Fashion District</x:t>
+  </x:si>
+  <x:si>
+    <x:t>145.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-stylish-design-apartment-in-fashion-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=107&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1312097201_403984239_2_0_0&amp;highlighted_blocks=1312097201_403984239_2_0_0&amp;matching_block_id=1312097201_403984239_2_0_0&amp;sr_pri_blocks=1312097201_403984239_2_0_0__72940&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milan Royal Suites - Duomo Santo Stefano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-duomo-santo-stefano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=108&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1203600902_392602555_2_0_0&amp;highlighted_blocks=1203600902_392602555_2_0_0&amp;matching_block_id=1203600902_392602555_2_0_0&amp;sr_pri_blocks=1203600902_392602555_2_0_0__90770&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano- Privata Angera 10S - Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-appartamento-di-design-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=109&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1069179902_379418625_2_0_0&amp;highlighted_blocks=1069179902_379418625_2_0_0&amp;matching_block_id=1069179902_379418625_2_0_0&amp;sr_pri_blocks=1069179902_379418625_2_0_0__47859&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Luxury Apartments Fioravanti</x:t>
   </x:si>
   <x:si>
-    <x:t>182.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luxury-apartment-fioravanti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=34&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=321708604_380687466_1_0_0_663512&amp;highlighted_blocks=321708604_380687466_1_0_0_663512&amp;matching_block_id=321708604_380687466_1_0_0_663512&amp;sr_pri_blocks=321708604_380687466_1_0_0_663512_91087&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standard Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Marco Polo Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>148.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/marco-polo-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=36&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=772964101_335686385_1_0_0_704773&amp;highlighted_blocks=772964101_335686385_1_0_0_704773&amp;matching_block_id=772964101_335686385_1_0_0_704773&amp;sr_pri_blocks=772964101_335686385_1_0_0_704773_74250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Dugnani 4 - Sant' Ambrogio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-comfortable-apartment-in-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=39&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1240198501_395931229_2_0_0&amp;highlighted_blocks=1240198501_395931229_2_0_0&amp;matching_block_id=1240198501_395931229_2_0_0&amp;sr_pri_blocks=1240198501_395931229_2_0_0__45841&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Magenta 83D - Magenta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-monolocale-in-corso-magenta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=40&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=955454602_368326497_2_0_0&amp;highlighted_blocks=955454602_368326497_2_0_0&amp;matching_block_id=955454602_368326497_2_0_0&amp;sr_pri_blocks=955454602_368326497_2_0_0__49770&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano- Privata Angera 10S - Centrale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-appartamento-di-design-in-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=41&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1069179902_379418625_2_0_0&amp;highlighted_blocks=1069179902_379418625_2_0_0&amp;matching_block_id=1069179902_379418625_2_0_0&amp;sr_pri_blocks=1069179902_379418625_2_0_0__47859&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Villa Aida</x:t>
-  </x:si>
-  <x:si>
-    <x:t>199.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/villa-aida.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=42&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=150415805_91955825_1_2_0_743654&amp;highlighted_blocks=150415805_91955825_1_2_0_743654&amp;matching_block_id=150415805_91955825_1_2_0_743654&amp;sr_pri_blocks=150415805_91955825_1_2_0_743654_99819&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Golden Prestige</x:t>
-  </x:si>
-  <x:si>
-    <x:t>184.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luxury-flat-repubblica.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=43&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=332276103_115726847_1_0_0&amp;highlighted_blocks=332276103_115726847_1_0_0&amp;matching_block_id=332276103_115726847_1_0_0&amp;sr_pri_blocks=332276103_115726847_1_0_0__92333&amp;from=searchresults</x:t>
+    <x:t>195.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/luxury-apartment-fioravanti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=110&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=321708604_380687466_1_0_0_663512&amp;highlighted_blocks=321708604_380687466_1_0_0_663512&amp;matching_block_id=321708604_380687466_1_0_0_663512&amp;sr_pri_blocks=321708604_380687466_1_0_0_663512_97682&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment - Annex</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Lido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotellidomilano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=111&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=8084515_88153892_0_1_0&amp;highlighted_blocks=8084515_88153892_0_1_0&amp;matching_block_id=8084515_88153892_0_1_0&amp;sr_pri_blocks=8084515_88153892_0_1_0__79750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Lecco 18D - Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nice-apartment-in-the-heart-of-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=112&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=889046702_411297401_2_0_0&amp;highlighted_blocks=889046702_411297401_2_0_0&amp;matching_block_id=889046702_411297401_2_0_0&amp;sr_pri_blocks=889046702_411297401_2_0_0__54458&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Settembrini 7 - Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-monolocale-con-arredamento-minimal-in-zona-stazione-central.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=114&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=941285802_411297087_2_0_0&amp;highlighted_blocks=941285802_411297087_2_0_0&amp;matching_block_id=941285802_411297087_2_0_0&amp;sr_pri_blocks=941285802_411297087_2_0_0__45276&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milano - Brand New 4 PAX Life &amp; The City Giulio Cesare 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>175.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-brand-new-4-pax-life-amp-the-city-giulio-cesare-5.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=115&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1145904001_408191012_1_0_0&amp;highlighted_blocks=1145904001_408191012_1_0_0&amp;matching_block_id=1145904001_408191012_1_0_0&amp;sr_pri_blocks=1145904001_408191012_1_0_0__87786&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Garden Lofts by Blue Velvet Livings</x:t>
+  </x:si>
+  <x:si>
+    <x:t>141.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/homie-urbangarden.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=117&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1105689204_383384584_1_0_0&amp;highlighted_blocks=1105689204_383384584_1_0_0&amp;matching_block_id=1105689204_383384584_1_0_0&amp;sr_pri_blocks=1105689204_383384584_1_0_0__70758&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio - Via San Calocero 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BePlace Apartments in De Amicis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>134.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-de-amicis.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=119&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1296552601_402558435_2_0_0&amp;highlighted_blocks=1296552601_402558435_2_0_0&amp;matching_block_id=1296552601_402558435_2_0_0&amp;sr_pri_blocks=1296552601_402558435_2_0_0__67070&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ampi monolocali in Via Pirandello - Washington</x:t>
+  </x:si>
+  <x:si>
+    <x:t>151.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/pirandello-4.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=120&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1290498304_402004962_2_0_0&amp;highlighted_blocks=1290498304_402004962_2_0_0&amp;matching_block_id=1290498304_402004962_2_0_0&amp;sr_pri_blocks=1290498304_402004962_2_0_0__75550&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sweett - Luxury Velasca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>184.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/sweet-inn-luxury-velasca.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=121&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1117509506_384613446_0_0_0&amp;highlighted_blocks=1117509506_384613446_0_0_0&amp;matching_block_id=1117509506_384613446_0_0_0&amp;sr_pri_blocks=1117509506_384613446_0_0_0__92236&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Santa Sofia 29 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/modern-and-new-flat-in-duomo-area.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=122&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=609071102_242160742_2_0_0&amp;highlighted_blocks=609071102_242160742_2_0_0&amp;matching_block_id=609071102_242160742_2_0_0&amp;sr_pri_blocks=609071102_242160742_2_0_0__57896&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Garigliano 8 - Isola</x:t>
+  </x:si>
+  <x:si>
+    <x:t>118.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-coccole-e-relax-nel-cuore-di-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=123&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=1066167102_411297075_2_0_0&amp;highlighted_blocks=1066167102_411297075_2_0_0&amp;matching_block_id=1066167102_411297075_2_0_0&amp;sr_pri_blocks=1066167102_411297075_2_0_0__59282&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residenza Porta Volta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>174.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-porta-volta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=124&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=106625301_91899460_2_0_0&amp;highlighted_blocks=106625301_91899460_2_0_0&amp;matching_block_id=106625301_91899460_2_0_0&amp;sr_pri_blocks=106625301_91899460_2_0_0__87250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Studio - Via Romagnosi 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milan Royal Suites - Centro Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>197.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=125&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134645&amp;all_sr_blocks=130695912_202239866_2_0_0&amp;highlighted_blocks=130695912_202239866_2_0_0&amp;matching_block_id=130695912_202239866_2_0_0&amp;sr_pri_blocks=130695912_202239866_2_0_0__98590&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Cola Montano 3 - Isola</x:t>
+  </x:si>
+  <x:si>
+    <x:t>122.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-incantevole-abitazione-in-zona-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=126&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1064246102_378783331_2_0_0&amp;highlighted_blocks=1064246102_378783331_2_0_0&amp;matching_block_id=1064246102_378783331_2_0_0&amp;sr_pri_blocks=1064246102_378783331_2_0_0__61425&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BB Hotels Aparthotel Desuite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>120.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/desuite-lofts-milan.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=127&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=109749020_362128548_2_0_0&amp;highlighted_blocks=109749020_362128548_2_0_0&amp;matching_block_id=109749020_362128548_2_0_0&amp;sr_pri_blocks=109749020_362128548_2_0_0__60250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appartamento con 1 Camera da Letto - Via Pioppette 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments in Porta Ticinese</x:t>
+  </x:si>
+  <x:si>
+    <x:t>148.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brera-apartments-in-porta-ticinese.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=128&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=210794101_95900308_2_0_0&amp;highlighted_blocks=210794101_95900308_2_0_0&amp;matching_block_id=210794101_95900308_2_0_0&amp;sr_pri_blocks=210794101_95900308_2_0_0__74110&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Porta Venezia Luxe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>175.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/porta-venezia-luxe.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=129&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1417265401_413402093_2_0_0&amp;highlighted_blocks=1417265401_413402093_2_0_0&amp;matching_block_id=1417265401_413402093_2_0_0&amp;sr_pri_blocks=1417265401_413402093_2_0_0__87935&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Santa Sofia 18 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>164.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-annydi-art-home-in-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=130&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=911484302_411297152_2_0_0&amp;highlighted_blocks=911484302_411297152_2_0_0&amp;matching_block_id=911484302_411297152_2_0_0&amp;sr_pri_blocks=911484302_411297152_2_0_0__82052&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Ferrari 9 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-e-moderno-bilocale-in-zona-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=131&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=941565102_411297408_2_0_0&amp;highlighted_blocks=941565102_411297408_2_0_0&amp;matching_block_id=941565102_411297408_2_0_0&amp;sr_pri_blocks=941565102_411297408_2_0_0__57903&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top Accommodations in the Heart of Milano!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/roomy-apts-in-the-heart-of-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=132&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=896647102_360273517_1_0_0&amp;highlighted_blocks=896647102_360273517_1_0_0&amp;matching_block_id=896647102_360273517_1_0_0&amp;sr_pri_blocks=896647102_360273517_1_0_0__54837&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Twin Room with Kitchenette</x:t>
+  </x:si>
+  <x:si>
+    <x:t>iH Hotels Milano ApartHotel Argonne Park</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/biancacroce.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=133&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=23691704_88162793_1_0_0&amp;highlighted_blocks=23691704_88162793_1_0_0&amp;matching_block_id=23691704_88162793_1_0_0&amp;sr_pri_blocks=23691704_88162793_1_0_0__38635&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milano Citylife Suites - Fully equipped apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-citylife-suites-fully-equipped-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=134&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1343072003_406686920_2_0_0&amp;highlighted_blocks=1343072003_406686920_2_0_0&amp;matching_block_id=1343072003_406686920_2_0_0&amp;sr_pri_blocks=1343072003_406686920_2_0_0__62487&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BePlace Bocconi Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>138.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beplace-bocconi-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=135&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=772869501_335238850_2_0_0&amp;highlighted_blocks=772869501_335238850_2_0_0&amp;matching_block_id=772869501_335238850_2_0_0&amp;sr_pri_blocks=772869501_335238850_2_0_0__69070&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Savoia Central Milan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>169.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/savoia-central-milan.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=136&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1076314502_402221173_1_0_0&amp;highlighted_blocks=1076314502_402221173_1_0_0&amp;matching_block_id=1076314502_402221173_1_0_0&amp;sr_pri_blocks=1076314502_402221173_1_0_0__84750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maloja, 10 – Casa Maloja – ampio appartamento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/maloja-10-casa-maloja-ampio-appartamento.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=137&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1126339701_385290734_4_0_0&amp;highlighted_blocks=1126339701_385290734_4_0_0&amp;matching_block_id=1126339701_385290734_4_0_0&amp;sr_pri_blocks=1126339701_385290734_4_0_0__81472&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Darsena Flat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/darsena-flat-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=139&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=879179401_394181088_2_0_0&amp;highlighted_blocks=879179401_394181088_2_0_0&amp;matching_block_id=879179401_394181088_2_0_0&amp;sr_pri_blocks=879179401_394181088_2_0_0__62753&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Frisi 3 City Center Suite - B Home</x:t>
@@ -496,148 +1369,298 @@
     <x:t>115</x:t>
   </x:si>
   <x:si>
-    <x:t>7.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/frisi-3-city-center-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=45&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1347983901_407144368_2_0_0&amp;highlighted_blocks=1347983901_407144368_2_0_0&amp;matching_block_id=1347983901_407144368_2_0_0&amp;sr_pri_blocks=1347983901_407144368_2_0_0__57485&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bramante Luxury Apartments by InnStay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>132</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bramante-luxury-apartments-by-innstay.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=46&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1392064301_411170762_1_0_0&amp;highlighted_blocks=1392064301_411170762_1_0_0&amp;matching_block_id=1392064301_411170762_1_0_0&amp;sr_pri_blocks=1392064301_411170762_1_0_0__66017&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ca Foscari Pop Naviglio ,2 camere 2 bagni</x:t>
-  </x:si>
-  <x:si>
-    <x:t>154.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/ca-foscari-pop-naviglio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=47&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1167981801_389372607_1_0_0_295248&amp;highlighted_blocks=1167981801_389372607_1_0_0_295248&amp;matching_block_id=1167981801_389372607_1_0_0_295248&amp;sr_pri_blocks=1167981801_389372607_1_0_0_295248_77323&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUOMO VIEW - 2 min from Duomo Amazing location</x:t>
-  </x:si>
-  <x:si>
-    <x:t>173.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/duomo-view-2-min-from-duomo-amazing-location.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=49&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=1132300201_385862129_2_0_0&amp;highlighted_blocks=1132300201_385862129_2_0_0&amp;matching_block_id=1132300201_385862129_2_0_0&amp;sr_pri_blocks=1132300201_385862129_2_0_0__86612&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUOMO - The Warm Maison - EXCLUSIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>154.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/the-warm-maison-duomo-700m.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=50&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130902&amp;all_sr_blocks=947727801_367351474_2_0_0&amp;highlighted_blocks=947727801_367351474_2_0_0&amp;matching_block_id=947727801_367351474_2_0_0&amp;sr_pri_blocks=947727801_367351474_2_0_0__77062&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Urban Garden Lofts by Blue Velvet Livings</x:t>
-  </x:si>
-  <x:si>
-    <x:t>141.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/homie-urbangarden.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=51&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1105689204_383384584_1_0_0&amp;highlighted_blocks=1105689204_383384584_1_0_0&amp;matching_block_id=1105689204_383384584_1_0_0&amp;sr_pri_blocks=1105689204_383384584_1_0_0__70758&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment (2 Adults)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BB Hotels Aparthotel Visconti</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bb-hotels-aparthotel-visconti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=52&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=175892501_362128576_2_0_0&amp;highlighted_blocks=175892501_362128576_2_0_0&amp;matching_block_id=175892501_362128576_2_0_0&amp;sr_pri_blocks=175892501_362128576_2_0_0__45250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - G Emiliani 1 114 - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/114-amazing-flat-fully-furnished-in-pta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=53&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=414189201_126132005_2_0_0&amp;highlighted_blocks=414189201_126132005_2_0_0&amp;matching_block_id=414189201_126132005_2_0_0&amp;sr_pri_blocks=414189201_126132005_2_0_0__48297&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/frisi-3-city-center-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=140&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1347983901_407144368_2_0_0&amp;highlighted_blocks=1347983901_407144368_2_0_0&amp;matching_block_id=1347983901_407144368_2_0_0&amp;sr_pri_blocks=1347983901_407144368_2_0_0__57485&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appartamento con 1 Camera da Letto - Corso Garibaldi 127</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments in Garibaldi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>155.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brera-apartments-in-garibaldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=141&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=77197815_88389966_2_0_0&amp;highlighted_blocks=77197815_88389966_2_0_0&amp;matching_block_id=77197815_88389966_2_0_0&amp;sr_pri_blocks=77197815_88389966_2_0_0__77595&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BB Hotels Aparthotel Arcimboldi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bb-hotels-residenza-arcimboldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=142&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=115910705_362128522_2_0_0&amp;highlighted_blocks=115910705_362128522_2_0_0&amp;matching_block_id=115910705_362128522_2_0_0&amp;sr_pri_blocks=115910705_362128522_2_0_0__47250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bellevue Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>198.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bellevue-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=143&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=866211901_354824185_1_0_0_263875&amp;highlighted_blocks=866211901_354824185_1_0_0_263875&amp;matching_block_id=866211901_354824185_1_0_0_263875&amp;sr_pri_blocks=866211901_354824185_1_0_0_263875_99174&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Torino 34S - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>179.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-dimora-a-due-minuti-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=144&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=996494102_411297086_2_0_0&amp;highlighted_blocks=996494102_411297086_2_0_0&amp;matching_block_id=996494102_411297086_2_0_0&amp;sr_pri_blocks=996494102_411297086_2_0_0__89641&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio - Via Confalonieri 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BePlace Apartments in Gae Aulenti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=145&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=554243403_204765162_2_0_0&amp;highlighted_blocks=554243403_204765162_2_0_0&amp;matching_block_id=554243403_204765162_2_0_0&amp;sr_pri_blocks=554243403_204765162_2_0_0__67070&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Genova 22 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>128.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/colored-and-spacious-flat-close-to-navigli-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=147&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=891711202_411297609_2_0_0&amp;highlighted_blocks=891711202_411297609_2_0_0&amp;matching_block_id=891711202_411297609_2_0_0&amp;sr_pri_blocks=891711202_411297609_2_0_0__64410&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment with Balcony</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vigentina 80s Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-xxv-aprile.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=148&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1294749502_402400733_2_0_0&amp;highlighted_blocks=1294749502_402400733_2_0_0&amp;matching_block_id=1294749502_402400733_2_0_0&amp;sr_pri_blocks=1294749502_402400733_2_0_0__72110&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luxury Apartment - Near Stazione Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>149.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bilocale-luxury-near-stazione-centrale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=149&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1176794301_390205150_1_0_0&amp;highlighted_blocks=1176794301_390205150_1_0_0&amp;matching_block_id=1176794301_390205150_1_0_0&amp;sr_pri_blocks=1176794301_390205150_1_0_0__74650&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ComeCasa 3 Bedrooms Apartment near Bocconi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>167.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/comecasa-3-bedrooms-apartment-near-bocconi-milano1.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=150&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134656&amp;all_sr_blocks=1373698901_409520909_2_0_0&amp;highlighted_blocks=1373698901_409520909_2_0_0&amp;matching_block_id=1373698901_409520909_2_0_0&amp;sr_pri_blocks=1373698901_409520909_2_0_0__83650&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - De Amicis 36 - Sant' Ambrogio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-luminosa-dimora-in-sant-ambrogio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=152&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1084361902_411297548_2_0_0&amp;highlighted_blocks=1084361902_411297548_2_0_0&amp;matching_block_id=1084361902_411297548_2_0_0&amp;sr_pri_blocks=1084361902_411297548_2_0_0__83052&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BePlace Apartments in Pagano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beplace-apartments-in-pagano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=153&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1375273101_409672812_2_0_0&amp;highlighted_blocks=1375273101_409672812_2_0_0&amp;matching_block_id=1375273101_409672812_2_0_0&amp;sr_pri_blocks=1375273101_409672812_2_0_0__70190&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Duomo Deluxe Apartments #5-11</x:t>
   </x:si>
   <x:si>
-    <x:t>116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-duomo-deluxe-apartments-5-11.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=54&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1389031004_410897819_2_0_0&amp;highlighted_blocks=1389031004_410897819_2_0_0&amp;matching_block_id=1389031004_410897819_2_0_0&amp;sr_pri_blocks=1389031004_410897819_2_0_0__57954&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milano Citylife Suites - Fully equipped apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>125</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/milano-citylife-suites-fully-equipped-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=55&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1343072003_406686920_2_0_0&amp;highlighted_blocks=1343072003_406686920_2_0_0&amp;matching_block_id=1343072003_406686920_2_0_0&amp;sr_pri_blocks=1343072003_406686920_2_0_0__62487&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-duomo-deluxe-apartments-5-11.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=155&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1389031004_410897819_2_0_0&amp;highlighted_blocks=1389031004_410897819_2_0_0&amp;matching_block_id=1389031004_410897819_2_0_0&amp;sr_pri_blocks=1389031004_410897819_2_0_0__57954&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stylish Flat Near San Siro - Metro WiFi &amp; AC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>127.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ideal-rent-albertinelli-9.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=156&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1331133402_405649003_2_0_0&amp;highlighted_blocks=1331133402_405649003_2_0_0&amp;matching_block_id=1331133402_405649003_2_0_0&amp;sr_pri_blocks=1331133402_405649003_2_0_0__63750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe One-Bedroom Apartment with City View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maggi Milano - New beautiful apartments in the city center</x:t>
+  </x:si>
+  <x:si>
+    <x:t>181.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/new-beautiful-two-apartments-in-the-city-center.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=157&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1222105404_412190978_2_0_0&amp;highlighted_blocks=1222105404_412190978_2_0_0&amp;matching_block_id=1222105404_412190978_2_0_0&amp;sr_pri_blocks=1222105404_412190978_2_0_0__90610&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio with Terrace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BePlace Apartments in Scalo Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>130.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beplace-apartments-at-fondazione-prada.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=158&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1064660701_378853338_2_0_0&amp;highlighted_blocks=1064660701_378853338_2_0_0&amp;matching_block_id=1064660701_378853338_2_0_0&amp;sr_pri_blocks=1064660701_378853338_2_0_0__65070&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LaFilo Apartment 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/solution-home-porta-romana-3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=160&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1181103901_390553415_1_0_0&amp;highlighted_blocks=1181103901_390553415_1_0_0&amp;matching_block_id=1181103901_390553415_1_0_0&amp;sr_pri_blocks=1181103901_390553415_1_0_0__73250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exquisite Stay Bocconi - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>149.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/lovely-stay-vannucci-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=161&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=900610701_360735586_1_0_0&amp;highlighted_blocks=900610701_360735586_1_0_0&amp;matching_block_id=900610701_360735586_1_0_0&amp;sr_pri_blocks=900610701_360735586_1_0_0__74750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Game On Apt - Corso Vercelli by InnStay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/game-on-apt-corso-vercelli-by-innstay.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=162&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1344161301_406785908_2_0_0&amp;highlighted_blocks=1344161301_406785908_2_0_0&amp;matching_block_id=1344161301_406785908_2_0_0&amp;sr_pri_blocks=1344161301_406785908_2_0_0__92270&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment with View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RELSTAY - Tortona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>192.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/relstay-tortona-1br.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=163&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1107508801_383531966_0_0_0&amp;highlighted_blocks=1107508801_383531966_0_0_0&amp;matching_block_id=1107508801_383531966_0_0_0&amp;sr_pri_blocks=1107508801_383531966_0_0_0__96400&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESIGN APARTMENT - Spadolini, Campus Bocconi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>136.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/design-apartment-spadolini-campus-bocconi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=164&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=974140201_369797365_2_0_0&amp;highlighted_blocks=974140201_369797365_2_0_0&amp;matching_block_id=974140201_369797365_2_0_0&amp;sr_pri_blocks=974140201_369797365_2_0_0__68055&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Cherubini 6 - City Life</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegance-a-few-steps-from-citylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=166&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1256161501_398156122_2_0_0&amp;highlighted_blocks=1256161501_398156122_2_0_0&amp;matching_block_id=1256161501_398156122_2_0_0&amp;sr_pri_blocks=1256161501_398156122_2_0_0__99008&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BnButler - Pergolesi, 6 - Accogliente e Moderno a Due Passi da Tutto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>119.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/pergolesi-6-accogliente-e-moderno-a-due-passi-da-tutto.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=167&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=873063102_356089594_2_0_0&amp;highlighted_blocks=873063102_356089594_2_0_0&amp;matching_block_id=873063102_356089594_2_0_0&amp;sr_pri_blocks=873063102_356089594_2_0_0__59691&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOIVY Boutique Apartments Farneti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aria-boutique-apartments-farneti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=168&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=594316101_233175898_0_0_0&amp;highlighted_blocks=594316101_233175898_0_0_0&amp;matching_block_id=594316101_233175898_0_0_0&amp;sr_pri_blocks=594316101_233175898_0_0_0__80362&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I-Host Apartment - Maffei 20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/i-host-apartment-maffei-20.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=169&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1487736801_420243981_1_0_0&amp;highlighted_blocks=1487736801_420243981_1_0_0&amp;matching_block_id=1487736801_420243981_1_0_0&amp;sr_pri_blocks=1487736801_420243981_1_0_0__80183&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>One-Bedroom Apartment - Largo Treves 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments in San Marco</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brera-apartments-in-san-marco.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=170&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=309666304_112718597_2_0_0&amp;highlighted_blocks=309666304_112718597_2_0_0&amp;matching_block_id=309666304_112718597_2_0_0&amp;sr_pri_blocks=309666304_112718597_2_0_0__81505&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments in San Fermo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brera-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=173&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=18725213_88388315_2_0_0&amp;highlighted_blocks=18725213_88388315_2_0_0&amp;matching_block_id=18725213_88388315_2_0_0&amp;sr_pri_blocks=18725213_88388315_2_0_0__81505&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>LUVI - Savona</x:t>
   </x:si>
   <x:si>
-    <x:t>119</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luvi-savona.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=56&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1499858701_421654746_2_0_0&amp;highlighted_blocks=1499858701_421654746_2_0_0&amp;matching_block_id=1499858701_421654746_2_0_0&amp;sr_pri_blocks=1499858701_421654746_2_0_0__59520&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bellevue Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>198.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bellevue-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=57&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=866211901_354824185_1_0_0_263875&amp;highlighted_blocks=866211901_354824185_1_0_0_263875&amp;matching_block_id=866211901_354824185_1_0_0_263875&amp;sr_pri_blocks=866211901_354824185_1_0_0_263875_99174&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Medium Studio with Kitchenette and Balcony</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Numa Milan Sempione</x:t>
-  </x:si>
-  <x:si>
-    <x:t>106.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/numa-milan-sempione.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=59&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1244681402_396582596_1_0_0_1190352&amp;highlighted_blocks=1244681402_396582596_1_0_0_1190352&amp;matching_block_id=1244681402_396582596_1_0_0_1190352&amp;sr_pri_blocks=1244681402_396582596_1_0_0_1190352_53200&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Game On Apt - Corso Vercelli by InnStay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/game-on-apt-corso-vercelli-by-innstay.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=61&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1344161301_406785908_2_0_0&amp;highlighted_blocks=1344161301_406785908_2_0_0&amp;matching_block_id=1344161301_406785908_2_0_0&amp;sr_pri_blocks=1344161301_406785908_2_0_0__92270&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESIGN APARTMENT - Spadolini, Campus Bocconi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>136.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/design-apartment-spadolini-campus-bocconi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=62&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=974140201_369797365_2_0_0&amp;highlighted_blocks=974140201_369797365_2_0_0&amp;matching_block_id=974140201_369797365_2_0_0&amp;sr_pri_blocks=974140201_369797365_2_0_0__68055&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/luvi-savona.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=174&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1499858701_421654746_2_0_0&amp;highlighted_blocks=1499858701_421654746_2_0_0&amp;matching_block_id=1499858701_421654746_2_0_0&amp;sr_pri_blocks=1499858701_421654746_2_0_0__59520&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vanilla Rosemary House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>147.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/vanilla-rosemary-house.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=175&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134667&amp;all_sr_blocks=1496574801_421334125_1_0_0&amp;highlighted_blocks=1496574801_421334125_1_0_0&amp;matching_block_id=1496574801_421334125_1_0_0&amp;sr_pri_blocks=1496574801_421334125_1_0_0__73600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prestige Boutique Homes-Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>182.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/prestige-boutique-homes-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=176&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=786338308_338169295_0_0_0_1241771&amp;highlighted_blocks=786338308_338169295_0_0_0_1241771&amp;matching_block_id=786338308_338169295_0_0_0_1241771&amp;sr_pri_blocks=786338308_338169295_0_0_0_1241771_91442&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Ascanio Sforza 53 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-romantico-appartamento-sui-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=178&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1015534602_411297596_2_0_0&amp;highlighted_blocks=1015534602_411297596_2_0_0&amp;matching_block_id=1015534602_411297596_2_0_0&amp;sr_pri_blocks=1015534602_411297596_2_0_0__53018&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BnButler - Verona 12, Porta Romana District</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/verona-12-porta-romana-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=180&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=975304901_369904033_2_0_0&amp;highlighted_blocks=975304901_369904033_2_0_0&amp;matching_block_id=975304901_369904033_2_0_0&amp;sr_pri_blocks=975304901_369904033_2_0_0__80877&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ComeCasa Best View on Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/comecasa-cosy-navigli-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=181&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1138822802_386597482_2_0_0&amp;highlighted_blocks=1138822802_386597482_2_0_0&amp;matching_block_id=1138822802_386597482_2_0_0&amp;sr_pri_blocks=1138822802_386597482_2_0_0__99500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Xenia Apartments - Luminous Suite in Citylife</x:t>
+  </x:si>
+  <x:si>
+    <x:t>139.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/luminous-suite-in-citylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=182&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1215699501_416285264_2_0_0&amp;highlighted_blocks=1215699501_416285264_2_0_0&amp;matching_block_id=1215699501_416285264_2_0_0&amp;sr_pri_blocks=1215699501_416285264_2_0_0__69566&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loft Budget</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BB Hotels Aparthotel Città Studi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>108.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bb-hotels-residenza-giulia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=183&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=38781210_362089897_2_0_0&amp;highlighted_blocks=38781210_362089897_2_0_0&amp;matching_block_id=38781210_362089897_2_0_0&amp;sr_pri_blocks=38781210_362089897_2_0_0__54250&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Easylife - Milano - Teodosio 15 - Lambrate</x:t>
@@ -646,7 +1669,52 @@
     <x:t>83.4</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-colorato-studio-con-terrazzo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=63&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1025164002_411297676_2_0_0&amp;highlighted_blocks=1025164002_411297676_2_0_0&amp;matching_block_id=1025164002_411297676_2_0_0&amp;sr_pri_blocks=1025164002_411297676_2_0_0__41685&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/easylife-colorato-studio-con-terrazzo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=186&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1025164002_411297676_2_0_0&amp;highlighted_blocks=1025164002_411297676_2_0_0&amp;matching_block_id=1025164002_411297676_2_0_0&amp;sr_pri_blocks=1025164002_411297676_2_0_0__41685&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>La casa di Tessa - Navigli Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>157.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/la-casa-di-tessa-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=188&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1054980201_377688966_1_0_0&amp;highlighted_blocks=1054980201_377688966_1_0_0&amp;matching_block_id=1054980201_377688966_1_0_0&amp;sr_pri_blocks=1054980201_377688966_1_0_0__78775&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aparthotel Isola</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aparthotel-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=189&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=225027101_98891649_1_0_0&amp;highlighted_blocks=225027101_98891649_1_0_0&amp;matching_block_id=225027101_98891649_1_0_0&amp;sr_pri_blocks=225027101_98891649_1_0_0__66400&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sant' Ambrogio Flat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/sant-39-ambrogio-flat.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=190&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=305047102_394181144_2_0_0&amp;highlighted_blocks=305047102_394181144_2_0_0&amp;matching_block_id=305047102_394181144_2_0_0&amp;sr_pri_blocks=305047102_394181144_2_0_0__68530&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Il Melograno sul Naviglio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>138.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/il-melograno-sul-naviglio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=191&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1178347601_390390159_1_0_0&amp;highlighted_blocks=1178347601_390390159_1_0_0&amp;matching_block_id=1178347601_390390159_1_0_0&amp;sr_pri_blocks=1178347601_390390159_1_0_0__69250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Galleria Buenos Aires 11- Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>174.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/splendid-house-buenos-aires-piazza-lima.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=192&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=453008101_137552007_2_0_0&amp;highlighted_blocks=453008101_137552007_2_0_0&amp;matching_block_id=453008101_137552007_2_0_0&amp;sr_pri_blocks=453008101_137552007_2_0_0__87141&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Deluxe One-Bedroom Apartment</x:t>
@@ -658,25 +1726,7 @@
     <x:t>103.2</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/central-station-design-suites-b-home-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=65&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1444849001_415905141_2_0_0&amp;highlighted_blocks=1444849001_415905141_2_0_0&amp;matching_block_id=1444849001_415905141_2_0_0&amp;sr_pri_blocks=1444849001_415905141_2_0_0__51560&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Navigli Cozy Corner - La Vista Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>104.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/navigli-cozy-corner-la-vista-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=66&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1538125001_425343543_2_0_0&amp;highlighted_blocks=1538125001_425343543_2_0_0&amp;matching_block_id=1538125001_425343543_2_0_0&amp;sr_pri_blocks=1538125001_425343543_2_0_0__52446&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Friuli 15 - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/stupendo-e-accogliente-apt-15-min-dal-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=70&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=609060802_277504331_2_0_0&amp;highlighted_blocks=609060802_277504331_2_0_0&amp;matching_block_id=609060802_277504331_2_0_0&amp;sr_pri_blocks=609060802_277504331_2_0_0__46959&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/central-station-design-suites-b-home-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=193&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1444849001_415905141_2_0_0&amp;highlighted_blocks=1444849001_415905141_2_0_0&amp;matching_block_id=1444849001_415905141_2_0_0&amp;sr_pri_blocks=1444849001_415905141_2_0_0__51560&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>Eleven Suites - Cozy apartments</x:t>
@@ -685,850 +1735,34 @@
     <x:t>111.6</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/it/eleven-suites-cozy-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=72&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1226394103_395701254_2_0_0&amp;highlighted_blocks=1226394103_395701254_2_0_0&amp;matching_block_id=1226394103_395701254_2_0_0&amp;sr_pri_blocks=1226394103_395701254_2_0_0__55806&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Bixio 17 - Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>137.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-milano-bixio-17-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=73&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1500100301_421675795_0_0_0&amp;highlighted_blocks=1500100301_421675795_0_0_0&amp;matching_block_id=1500100301_421675795_0_0_0&amp;sr_pri_blocks=1500100301_421675795_0_0_0__68768&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Appartamento delizioso, vicino a Fiera, Duomo, San Siro</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/casa-andry-vicino-a-fiera-duomo-san-siro.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=74&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1341018101_406509649_1_0_0&amp;highlighted_blocks=1341018101_406509649_1_0_0&amp;matching_block_id=1341018101_406509649_1_0_0&amp;sr_pri_blocks=1341018101_406509649_1_0_0__45815&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Navigli Design Apartment with Balcony</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/navigli-comfy-location.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=75&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130903&amp;all_sr_blocks=1042185701_376636488_1_0_0_586913&amp;highlighted_blocks=1042185701_376636488_1_0_0_586913&amp;matching_block_id=1042185701_376636488_1_0_0_586913&amp;sr_pri_blocks=1042185701_376636488_1_0_0_586913_45750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Superior One-Bedroom Apartment with Balcony</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cefalonia Garden with Terrace &amp; Garage by NDP rent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>157.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/cefalonia-garden-with-terrace-amp-garage-by-ndp-rent.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=76&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1384074410_423109409_1_0_0_1234024&amp;highlighted_blocks=1384074410_423109409_1_0_0_1234024&amp;matching_block_id=1384074410_423109409_1_0_0_1234024&amp;sr_pri_blocks=1384074410_423109409_1_0_0_1234024_78736&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Michelangelo Navigli Loft Experience - Via Magolfa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/michelangelo-navigli-loft-experience-via-magolfa.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=77&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1049649204_377218682_1_0_0&amp;highlighted_blocks=1049649204_377218682_1_0_0&amp;matching_block_id=1049649204_377218682_1_0_0&amp;sr_pri_blocks=1049649204_377218682_1_0_0__37750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RRRapido Apartment - Via Casale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/rrrapido-apartment-in-via-casale-2-people.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=80&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1296030901_402510903_1_0_0_697918&amp;highlighted_blocks=1296030901_402510903_1_0_0_697918&amp;matching_block_id=1296030901_402510903_1_0_0_697918&amp;sr_pri_blocks=1296030901_402510903_1_0_0_697918_40425&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kaizen House - Bilocale De Angeli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/kaizen-house-bilocale-de-angeli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=81&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1047836101_377067817_2_0_0_666063&amp;highlighted_blocks=1047836101_377067817_2_0_0_666063&amp;matching_block_id=1047836101_377067817_2_0_0_666063&amp;sr_pri_blocks=1047836101_377067817_2_0_0_666063_50969&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Crema 23 - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/modern-and-central-apt-in-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=82&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=395164201_122892247_2_0_0&amp;highlighted_blocks=395164201_122892247_2_0_0&amp;matching_block_id=395164201_122892247_2_0_0&amp;sr_pri_blocks=395164201_122892247_2_0_0__46266&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Red Dragon Suite - Via Paolo Sarpi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/red-dragon-suite-via-paolo-sarpi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=83&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1328161501_405402817_1_0_0&amp;highlighted_blocks=1328161501_405402817_1_0_0&amp;matching_block_id=1328161501_405402817_1_0_0&amp;sr_pri_blocks=1328161501_405402817_1_0_0__40800&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Queen Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Orti House Apartments - total renovation on Apr 2023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bright-flat-in-via-orti.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=84&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=312357902_113322890_2_0_0&amp;highlighted_blocks=312357902_113322890_2_0_0&amp;matching_block_id=312357902_113322890_2_0_0&amp;sr_pri_blocks=312357902_113322890_2_0_0__67493&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Deluxe Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Suite Central Station</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/suite-central-station.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=85&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=607045011_326885500_1_0_0&amp;highlighted_blocks=607045011_326885500_1_0_0&amp;matching_block_id=607045011_326885500_1_0_0&amp;sr_pri_blocks=607045011_326885500_1_0_0__43500&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One-Bedroom Apartment with Terrace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Buenos Aires 77 A-Buenos Aires</x:t>
-  </x:si>
-  <x:si>
-    <x:t>109.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-appartamento-con-terrazzo-buenos-aires.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=88&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1271585902_399928876_2_0_0&amp;highlighted_blocks=1271585902_399928876_2_0_0&amp;matching_block_id=1271585902_399928876_2_0_0&amp;sr_pri_blocks=1271585902_399928876_2_0_0__54837&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Pier Lombardo 16 - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/nice-and-cozy-studio-in-porta-romana-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=89&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=794224002_342458649_0_0_0&amp;highlighted_blocks=794224002_342458649_0_0_0&amp;matching_block_id=794224002_342458649_0_0_0&amp;sr_pri_blocks=794224002_342458649_0_0_0__43178&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Lecco 11P3 - Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>113.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/tropical-and-new-flat-in-porta-venezia-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=90&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=881074302_411297533_2_0_0&amp;highlighted_blocks=881074302_411297533_2_0_0&amp;matching_block_id=881074302_411297533_2_0_0&amp;sr_pri_blocks=881074302_411297533_2_0_0__56758&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Mercato 5 - Brera</x:t>
-  </x:si>
-  <x:si>
-    <x:t>105.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-monolocale-di-lusso-in-brera.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=91&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1354728302_407797656_2_0_0&amp;highlighted_blocks=1354728302_407797656_2_0_0&amp;matching_block_id=1354728302_407797656_2_0_0&amp;sr_pri_blocks=1354728302_407797656_2_0_0__52764&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BasicVillage Milano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>192.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/basicvillage-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=92&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=974823202_369858095_0_0_0&amp;highlighted_blocks=974823202_369858095_0_0_0&amp;matching_block_id=974823202_369858095_0_0_0&amp;sr_pri_blocks=974823202_369858095_0_0_0__96250&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elegant Design Apartment[Duomo-Navigli]A/C e WI-FI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>142.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/elegant-design-apartment-duomo-navigli-a-c-e-wi-fi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=94&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1099984901_382857779_2_0_0&amp;highlighted_blocks=1099984901_382857779_2_0_0&amp;matching_block_id=1099984901_382857779_2_0_0&amp;sr_pri_blocks=1099984901_382857779_2_0_0__71050&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - MonteNero 62 - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-appartamento-in-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=95&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1010173502_411297344_2_0_0&amp;highlighted_blocks=1010173502_411297344_2_0_0&amp;matching_block_id=1010173502_411297344_2_0_0&amp;sr_pri_blocks=1010173502_411297344_2_0_0__53018&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Urban Nest Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/new-studio-apartment-sauro-orange.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=97&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=708995001_295734320_1_0_0&amp;highlighted_blocks=708995001_295734320_1_0_0&amp;matching_block_id=708995001_295734320_1_0_0&amp;sr_pri_blocks=708995001_295734320_1_0_0__49789&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Casati 2 - Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/stylish-and-new-apt-in-buenos-aires.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=99&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=414868501_126399064_2_0_0&amp;highlighted_blocks=414868501_126399064_2_0_0&amp;matching_block_id=414868501_126399064_2_0_0&amp;sr_pri_blocks=414868501_126399064_2_0_0__51018&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rifugio di Stile tra Tortona e Navigli a pochi passi da M4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/navigli-porta-genova-suite-eleganza-e-comfort-nel-cuore-di-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=100&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130905&amp;all_sr_blocks=1375179401_409666188_2_0_0&amp;highlighted_blocks=1375179401_409666188_2_0_0&amp;matching_block_id=1375179401_409666188_2_0_0&amp;sr_pri_blocks=1375179401_409666188_2_0_0__52950&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EasyTopStay - Sempione Cozy Flat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/sempione-accogliente-appartamento.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=101&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1231700301_395142529_2_0_0_852707&amp;highlighted_blocks=1231700301_395142529_2_0_0_852707&amp;matching_block_id=1231700301_395142529_2_0_0_852707&amp;sr_pri_blocks=1231700301_395142529_2_0_0_852707_48956&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRESTIGE BOUTIQUE HOMES - Arco della Pace 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/prestige-boutique-homes-via-rosmini-11.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=103&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=873812901_356198202_2_0_0_1241765&amp;highlighted_blocks=873812901_356198202_2_0_0_1241765&amp;matching_block_id=873812901_356198202_2_0_0_1241765&amp;sr_pri_blocks=873812901_356198202_2_0_0_1241765_46781&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEA DREAMS - Amendola Fiera near San Siro Stadium</x:t>
-  </x:si>
-  <x:si>
-    <x:t>163.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/dea-dreams-amendola-fiera-apartment-free-wi-fi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=104&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1131107502_385767618_2_0_0&amp;highlighted_blocks=1131107502_385767618_2_0_0&amp;matching_block_id=1131107502_385767618_2_0_0&amp;sr_pri_blocks=1131107502_385767618_2_0_0__81570&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Residenza Arcimboldi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>117.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/residenza-arcimboldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=105&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1467284602_418048755_2_0_0&amp;highlighted_blocks=1467284602_418048755_2_0_0&amp;matching_block_id=1467284602_418048755_2_0_0&amp;sr_pri_blocks=1467284602_418048755_2_0_0__58550&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Moscati 9A - Sarpi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-moderno-apt-con-terrazzo-in-paolo-sarpi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=106&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=984198602_411297670_2_0_0&amp;highlighted_blocks=984198602_411297670_2_0_0&amp;matching_block_id=984198602_411297670_2_0_0&amp;sr_pri_blocks=984198602_411297670_2_0_0__51397&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Coni Zugna 27 - Solari</x:t>
-  </x:si>
-  <x:si>
-    <x:t>106.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-nuovo-bilocale-con-balcone-sagostino.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=108&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1179690302_390440949_2_0_0&amp;highlighted_blocks=1179690302_390440949_2_0_0&amp;matching_block_id=1179690302_390440949_2_0_0&amp;sr_pri_blocks=1179690302_390440949_2_0_0__53118&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Luminoso bilocale in Porta Garibaldi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>150.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luminoso-bilocale-in-porta-garibaldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=111&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1474758001_418880118_2_0_0&amp;highlighted_blocks=1474758001_418880118_2_0_0&amp;matching_block_id=1474758001_418880118_2_0_0&amp;sr_pri_blocks=1474758001_418880118_2_0_0__75378&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Ripa Ticinese 69 - Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>106.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/lovely-apartment-on-the-navigli-river-by-easylife.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=112&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=849768102_411297141_2_0_0&amp;highlighted_blocks=849768102_411297141_2_0_0&amp;matching_block_id=849768102_411297141_2_0_0&amp;sr_pri_blocks=849768102_411297141_2_0_0__53318&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Two-Bedroom Suite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>La Villa bed &amp; breakfast</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/la-villa-bed-amp-breakfast.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=114&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=774698003_404327984_2_1_0&amp;highlighted_blocks=774698003_404327984_2_1_0&amp;matching_block_id=774698003_404327984_2_1_0&amp;sr_pri_blocks=774698003_404327984_2_1_0__81587&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The Bike Garage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/the-bike-garage.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=115&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=495282901_166389842_2_0_0&amp;highlighted_blocks=495282901_166389842_2_0_0&amp;matching_block_id=495282901_166389842_2_0_0&amp;sr_pri_blocks=495282901_166389842_2_0_0__87004&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standard Triple Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loreto Prestige - Parking Free &amp; Bulb Gym</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/loreto-prestige.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=116&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1239873204_395916420_3_0_0&amp;highlighted_blocks=1239873204_395916420_3_0_0&amp;matching_block_id=1239873204_395916420_3_0_0&amp;sr_pri_blocks=1239873204_395916420_3_0_0__48750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Duomo Deluxe Apartments #1-4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-duomo-deluxe-apartments-1-4.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=117&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1388996102_410894722_2_0_0&amp;highlighted_blocks=1388996102_410894722_2_0_0&amp;matching_block_id=1388996102_410894722_2_0_0&amp;sr_pri_blocks=1388996102_410894722_2_0_0__64637&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aprica16 Loft House Milano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>129.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/aprica-16-loft-house-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=118&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=770008001_334792646_1_0_0&amp;highlighted_blocks=770008001_334792646_1_0_0&amp;matching_block_id=770008001_334792646_1_0_0&amp;sr_pri_blocks=770008001_334792646_1_0_0__64779&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Xenia Apartments - Quiet and cozy two-room apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>117.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/quiet-and-cozy-two-room-apartment-20-min-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=119&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1152156201_388008256_2_0_0&amp;highlighted_blocks=1152156201_388008256_2_0_0&amp;matching_block_id=1152156201_388008256_2_0_0&amp;sr_pri_blocks=1152156201_388008256_2_0_0__58676&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano- Vetere 10 - Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>105.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-appartamento-elegante-moderno-e-accogliente-la-tua-oasi-in-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=120&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=983129002_411297608_2_0_0&amp;highlighted_blocks=983129002_411297608_2_0_0&amp;matching_block_id=983129002_411297608_2_0_0&amp;sr_pri_blocks=983129002_411297608_2_0_0__52737&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUVI - Misurata</x:t>
-  </x:si>
-  <x:si>
-    <x:t>122.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/casa-carmen-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=124&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=974749401_369851095_2_0_0&amp;highlighted_blocks=974749401_369851095_2_0_0&amp;matching_block_id=974749401_369851095_2_0_0&amp;sr_pri_blocks=974749401_369851095_2_0_0__61334&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RRRapido Home in Brera - Via Mercato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/rrrapido-home-in-brera-via-mercato.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=125&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130916&amp;all_sr_blocks=1360208804_408327303_0_0_0&amp;highlighted_blocks=1360208804_408327303_0_0_0&amp;matching_block_id=1360208804_408327303_0_0_0&amp;sr_pri_blocks=1360208804_408327303_0_0_0__48750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Crocetta 2 P1S - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-moderno-bilocale-in-zona-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=126&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=913089902_411297669_2_0_0&amp;highlighted_blocks=913089902_411297669_2_0_0&amp;matching_block_id=913089902_411297669_2_0_0&amp;sr_pri_blocks=913089902_411297669_2_0_0__54018&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Residence 2Gi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>131.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/ajraghi-halldis-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=128&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=122518401_98061898_1_0_0&amp;highlighted_blocks=122518401_98061898_1_0_0&amp;matching_block_id=122518401_98061898_1_0_0&amp;sr_pri_blocks=122518401_98061898_1_0_0__65650&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Residenza Cenisio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/residenza-cenisio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=130&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=28567108_88453047_0_0_0&amp;highlighted_blocks=28567108_88453047_0_0_0&amp;matching_block_id=28567108_88453047_0_0_0&amp;sr_pri_blocks=28567108_88453047_0_0_0__41865&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Eaylife - Milano - Corso Italia 68P4 - Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>109.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-comfort-e-armonia-sui-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=131&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1391470602_411119641_2_0_0&amp;highlighted_blocks=1391470602_411119641_2_0_0&amp;matching_block_id=1391470602_411119641_2_0_0&amp;sr_pri_blocks=1391470602_411119641_2_0_0__54737&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Urban Hub Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/urban-hub-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=132&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1379458101_410069510_1_0_0&amp;highlighted_blocks=1379458101_410069510_1_0_0&amp;matching_block_id=1379458101_410069510_1_0_0&amp;sr_pri_blocks=1379458101_410069510_1_0_0__45916&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Modrone 28 S1 - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>114.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/cityscape-milan-design-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=134&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1122526001_385012587_1_0_0&amp;highlighted_blocks=1122526001_385012587_1_0_0&amp;matching_block_id=1122526001_385012587_1_0_0&amp;sr_pri_blocks=1122526001_385012587_1_0_0__57277&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piranesi 246</x:t>
-  </x:si>
-  <x:si>
-    <x:t>177.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/piranesi-246.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=135&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=340652508_384712436_2_0_0&amp;highlighted_blocks=340652508_384712436_2_0_0&amp;matching_block_id=340652508_384712436_2_0_0&amp;sr_pri_blocks=340652508_384712436_2_0_0__88750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piazza Gramsci Amazing Apartment with Balcony - Top Collection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>113</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/piazza-gramsci-amazing-apartment-with-balcony-top-collection.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=136&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1235737801_395512689_1_0_0&amp;highlighted_blocks=1235737801_395512689_1_0_0&amp;matching_block_id=1235737801_395512689_1_0_0&amp;sr_pri_blocks=1235737801_395512689_1_0_0__56520&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mora 9 - The Boutique Suite - B Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/mora-9-the-boutique-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=137&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1495046101_421170065_2_0_0&amp;highlighted_blocks=1495046101_421170065_2_0_0&amp;matching_block_id=1495046101_421170065_2_0_0&amp;sr_pri_blocks=1495046101_421170065_2_0_0__64595&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Garibaldi's Gem - La Vista Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/garibaldis-gem-milanos-heart-la-vista-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=138&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1460732202_417378635_2_0_0&amp;highlighted_blocks=1460732202_417378635_2_0_0&amp;matching_block_id=1460732202_417378635_2_0_0&amp;sr_pri_blocks=1460732202_417378635_2_0_0__55543&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Suites in Porta Garibaldi &amp; Chinatown - City Center well connected</x:t>
-  </x:si>
-  <x:si>
-    <x:t>133.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/suites-in-porta-garibaldi-amp-chinatown-city-center-well-connected.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=139&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1249886302_397450220_2_0_0&amp;highlighted_blocks=1249886302_397450220_2_0_0&amp;matching_block_id=1249886302_397450220_2_0_0&amp;sr_pri_blocks=1249886302_397450220_2_0_0__66731&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Podgora 7 - Porta Vittoria</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-rifugio-nel-cuore-del-centro-storico-milanese-in-zona-piazz.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=141&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=950694002_411297560_2_0_0&amp;highlighted_blocks=950694002_411297560_2_0_0&amp;matching_block_id=950694002_411297560_2_0_0&amp;sr_pri_blocks=950694002_411297560_2_0_0__51263&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Correnti 24 - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/elegante-e-completamente-arredato-apt-in-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=144&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=414851001_126389632_2_0_0&amp;highlighted_blocks=414851001_126389632_2_0_0&amp;matching_block_id=414851001_126389632_2_0_0&amp;sr_pri_blocks=414851001_126389632_2_0_0__64837&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Albani 20 - City Life</x:t>
-  </x:si>
-  <x:si>
-    <x:t>138.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-modern-and-spacious-apt-in-fiera-city-life.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=146&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=753188602_342458560_2_0_0&amp;highlighted_blocks=753188602_342458560_2_0_0&amp;matching_block_id=753188602_342458560_2_0_0&amp;sr_pri_blocks=753188602_342458560_2_0_0__69164&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Kramer 13 D - Risorgimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-monolocale-con-balcone-in-risorgimento.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=148&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1184377902_390811285_2_0_0&amp;highlighted_blocks=1184377902_390811285_2_0_0&amp;matching_block_id=1184377902_390811285_2_0_0&amp;sr_pri_blocks=1184377902_390811285_2_0_0__46771&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Paoli 6 - Navigli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-modern-studio-in-the-heart-of-navigli.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=149&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=1301789401_403060367_2_0_0&amp;highlighted_blocks=1301789401_403060367_2_0_0&amp;matching_block_id=1301789401_403060367_2_0_0&amp;sr_pri_blocks=1301789401_403060367_2_0_0__50368&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aria di Casa - Navigli Darsena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>153.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/aria-di-casa-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=150&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130927&amp;all_sr_blocks=308977902_112593482_1_0_0&amp;highlighted_blocks=308977902_112593482_1_0_0&amp;matching_block_id=308977902_112593482_1_0_0&amp;sr_pri_blocks=308977902_112593482_1_0_0__76560&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Landscape Flats</x:t>
-  </x:si>
-  <x:si>
-    <x:t>115.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/landscape-flats.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=151&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1250259201_397504852_1_0_0&amp;highlighted_blocks=1250259201_397504852_1_0_0&amp;matching_block_id=1250259201_397504852_1_0_0&amp;sr_pri_blocks=1250259201_397504852_1_0_0__57554&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MiaHome43 - Cozy Milan Apartment Near Loreto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/new-charming-milanese-apartment-near-loreto-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=152&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1402908301_420762435_1_0_0&amp;highlighted_blocks=1402908301_420762435_1_0_0&amp;matching_block_id=1402908301_420762435_1_0_0&amp;sr_pri_blocks=1402908301_420762435_1_0_0__54160&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elegante bilocale San Calocero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>147.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/elegante-bilocale-san-calocero.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=153&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1075591401_402147700_2_0_0&amp;highlighted_blocks=1075591401_402147700_2_0_0&amp;matching_block_id=1075591401_402147700_2_0_0&amp;sr_pri_blocks=1075591401_402147700_2_0_0__73887&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Appartamento con 1 Camera da Letto – Via della Spiga 46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brera Apartments in Via della Spiga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>170.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/spiga-46-suites-by-brera-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=154&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=989858402_371633451_2_0_0&amp;highlighted_blocks=989858402_371633451_2_0_0&amp;matching_block_id=989858402_371633451_2_0_0&amp;sr_pri_blocks=989858402_371633451_2_0_0__85415&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Amazing Studio in Corso Como next Brera</x:t>
-  </x:si>
-  <x:si>
-    <x:t>104</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/amazing-studio-in-corso-como-next-brera.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=155&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1510791401_422835329_1_0_0&amp;highlighted_blocks=1510791401_422835329_1_0_0&amp;matching_block_id=1510791401_422835329_1_0_0&amp;sr_pri_blocks=1510791401_422835329_1_0_0__51969&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skyline Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bilocale-6degp-con-wi-fi-ac-posto-auto-a-30-mt-da-m3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=156&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=677119601_276398597_4_0_0&amp;highlighted_blocks=677119601_276398597_4_0_0&amp;matching_block_id=677119601_276398597_4_0_0&amp;sr_pri_blocks=677119601_276398597_4_0_0__55750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>APARTHOTEL CASA MIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/aparthotel-casa-mia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=157&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=481374401_361771404_0_0_0&amp;highlighted_blocks=481374401_361771404_0_0_0&amp;matching_block_id=481374401_361771404_0_0_0&amp;sr_pri_blocks=481374401_361771404_0_0_0__79750&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Centrale Suite with Balcony - Top Collection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>130</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/centrale-suite-with-balcony-top-collection.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=159&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1043242001_376708779_1_0_0&amp;highlighted_blocks=1043242001_376708779_1_0_0&amp;matching_block_id=1043242001_376708779_1_0_0&amp;sr_pri_blocks=1043242001_376708779_1_0_0__65020&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alta Vista Milano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/alta-vista-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=161&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1503671601_422083140_1_0_0&amp;highlighted_blocks=1503671601_422083140_1_0_0&amp;matching_block_id=1503671601_422083140_1_0_0&amp;sr_pri_blocks=1503671601_422083140_1_0_0__47610&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fabbri Palace - B Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>138.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/fabbri-palace-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=162&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1491884508_420837644_2_0_0&amp;highlighted_blocks=1491884508_420837644_2_0_0&amp;matching_block_id=1491884508_420837644_2_0_0&amp;sr_pri_blocks=1491884508_420837644_2_0_0__69274&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Gregorio 43 A - Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-the-magnificent-flat-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=163&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=688652402_295393454_2_0_0&amp;highlighted_blocks=688652402_295393454_2_0_0&amp;matching_block_id=688652402_295393454_2_0_0&amp;sr_pri_blocks=688652402_295393454_2_0_0__50397&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Calco 2P3 - Sant'Agostino</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-mono-con-balcone-in-sant-agostino.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=164&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1342493002_406630968_2_0_0&amp;highlighted_blocks=1342493002_406630968_2_0_0&amp;matching_block_id=1342493002_406630968_2_0_0&amp;sr_pri_blocks=1342493002_406630968_2_0_0__46771&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Orti 4 - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-splendido-bilocale-in-porta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=165&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=925804302_411297180_2_0_0&amp;highlighted_blocks=925804302_411297180_2_0_0&amp;matching_block_id=925804302_411297180_2_0_0&amp;sr_pri_blocks=925804302_411297180_2_0_0__51018&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Garigliano 10 - Isola</x:t>
-  </x:si>
-  <x:si>
-    <x:t>128.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-unita-su-due-livelli-a-isola.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=166&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1179646202_390438749_2_0_0&amp;highlighted_blocks=1179646202_390438749_2_0_0&amp;matching_block_id=1179646202_390438749_2_0_0&amp;sr_pri_blocks=1179646202_390438749_2_0_0__64110&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Schiaparelli4 - Central Station Suite - B Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>119.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/schiaparelli4-central-station-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=167&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1490630401_420726927_2_0_0&amp;highlighted_blocks=1490630401_420726927_2_0_0&amp;matching_block_id=1490630401_420726927_2_0_0&amp;sr_pri_blocks=1490630401_420726927_2_0_0__59855&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Santa Sofia House - Duomo Milano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>154.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/santa-sofia-house.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=168&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=920028002_363620357_0_0_0&amp;highlighted_blocks=920028002_363620357_0_0_0&amp;matching_block_id=920028002_363620357_0_0_0&amp;sr_pri_blocks=920028002_363620357_0_0_0__77374&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Central Station Milano Room - 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/central-station-milano-room-3.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=169&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=779843701_337790221_1_0_0_587702&amp;highlighted_blocks=779843701_337790221_1_0_0_587702&amp;matching_block_id=779843701_337790221_1_0_0_587702&amp;sr_pri_blocks=779843701_337790221_1_0_0_587702_35975&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - G Emiliani 1 115 - Porta Romana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/beautiful-flat-fully-furnished-in-pta-romana.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=170&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=414216301_126143408_2_0_0&amp;highlighted_blocks=414216301_126143408_2_0_0&amp;matching_block_id=414216301_126143408_2_0_0&amp;sr_pri_blocks=414216301_126143408_2_0_0__48297&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Lecco 5 P2 - in Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>107.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-comodo-appartamento-in-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=171&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1154859902_388280300_2_0_0&amp;highlighted_blocks=1154859902_388280300_2_0_0&amp;matching_block_id=1154859902_388280300_2_0_0&amp;sr_pri_blocks=1154859902_388280300_2_0_0__53837&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Duomo Suite - B Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>167.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/duomo-suite-b-home.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=172&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1378811801_410003981_2_0_0&amp;highlighted_blocks=1378811801_410003981_2_0_0&amp;matching_block_id=1378811801_410003981_2_0_0&amp;sr_pri_blocks=1378811801_410003981_2_0_0__83555&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Velasca Tower Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>155.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/velasca-tower-apartments-milano.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=173&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1275181361_400377746_1_0_0&amp;highlighted_blocks=1275181361_400377746_1_0_0&amp;matching_block_id=1275181361_400377746_1_0_0&amp;sr_pri_blocks=1275181361_400377746_1_0_0__77730&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Luminoso Piano Alto con Terrazzo - Mirable PM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>113.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bright-loft-with-terrace-mirable-pm.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=174&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=1443250601_415766843_0_0_0&amp;highlighted_blocks=1443250601_415766843_0_0_0&amp;matching_block_id=1443250601_415766843_0_0_0&amp;sr_pri_blocks=1443250601_415766843_0_0_0__56600&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Maffucci 53 - Dergano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-dimora-con-balcone.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=175&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130938&amp;all_sr_blocks=987239102_411297538_2_0_0&amp;highlighted_blocks=987239102_411297538_2_0_0&amp;matching_block_id=987239102_411297538_2_0_0&amp;sr_pri_blocks=987239102_411297538_2_0_0__48141&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EasyTopStay - Moscova Modern Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/moscova-modern-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=176&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=905968401_361678059_2_0_0_852695&amp;highlighted_blocks=905968401_361678059_2_0_0_852695&amp;matching_block_id=905968401_361678059_2_0_0_852695&amp;sr_pri_blocks=905968401_361678059_2_0_0_852695_73086&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Penthouse Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hosting Dreams Attics - Duomo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>177.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/hosting-dreams-attics-duomo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=177&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1088925913_381812816_1_0_0_338935&amp;highlighted_blocks=1088925913_381812816_1_0_0_338935&amp;matching_block_id=1088925913_381812816_1_0_0_338935&amp;sr_pri_blocks=1088925913_381812816_1_0_0_338935_88852&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loft Moderno in Dateo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>107.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/modern-loft-in-dateo.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=179&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=800171601_340971950_1_0_0&amp;highlighted_blocks=800171601_340971950_1_0_0&amp;matching_block_id=800171601_340971950_1_0_0&amp;sr_pri_blocks=800171601_340971950_1_0_0__53602&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BnButler - Archimede 53 - Bright Studio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/monolocale-con-spazio-esterno.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=180&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=968435001_369272242_2_0_0&amp;highlighted_blocks=968435001_369272242_2_0_0&amp;matching_block_id=968435001_369272242_2_0_0&amp;sr_pri_blocks=968435001_369272242_2_0_0__53278&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ComeCasa modern Terraced &amp; Palestra Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>172.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/comecasa-porta-romana-terraced-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=181&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1220752801_394226527_2_0_0&amp;highlighted_blocks=1220752801_394226527_2_0_0&amp;matching_block_id=1220752801_394226527_2_0_0&amp;sr_pri_blocks=1220752801_394226527_2_0_0__86200&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Washington 91 p7 - Solari</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-elegante-appartamento-in-solari.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=183&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1085204302_381393382_2_0_0&amp;highlighted_blocks=1085204302_381393382_2_0_0&amp;matching_block_id=1085204302_381393382_2_0_0&amp;sr_pri_blocks=1085204302_381393382_2_0_0__54814&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lovelyloft - Alzaia Naviglio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/lovelyloft-alzaia-naviglio.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=184&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=211441401_96023455_2_0_0&amp;highlighted_blocks=211441401_96023455_2_0_0&amp;matching_block_id=211441401_96023455_2_0_0&amp;sr_pri_blocks=211441401_96023455_2_0_0__39801&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Maroncelli 14 - Garibaldi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>111.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-luminoso-bilocale-in-zona-garibaldi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=185&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=920802502_411297558_2_0_0&amp;highlighted_blocks=920802502_411297558_2_0_0&amp;matching_block_id=920802502_411297558_2_0_0&amp;sr_pri_blocks=920802502_411297558_2_0_0__55737&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4 Pax Luxury Milano Duomo San Babila</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/4-pax-luxury-milano-duomo-san-babila.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=186&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1500952001_421765283_1_0_0&amp;highlighted_blocks=1500952001_421765283_1_0_0&amp;matching_block_id=1500952001_421765283_1_0_0&amp;sr_pri_blocks=1500952001_421765283_1_0_0__85412&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STAR RIBBON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/star-ribbon.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=187&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=794654902_339549249_2_2_0&amp;highlighted_blocks=794654902_339549249_2_2_0&amp;matching_block_id=794654902_339549249_2_2_0&amp;sr_pri_blocks=794654902_339549249_2_2_0__57985&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Studio - Annex</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Andreola Central Hotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>139.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/andreolacentralhotel.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=189&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=8078766_88153824_0_33_0&amp;highlighted_blocks=8078766_88153824_0_33_0&amp;matching_block_id=8078766_88153824_0_33_0&amp;sr_pri_blocks=8078766_88153824_0_33_0__69800&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - DellaChiusa 8 - Porta Ticinese</x:t>
-  </x:si>
-  <x:si>
-    <x:t>153.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easylife-pearl-with-balcony-on-ticinese-district.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=190&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1311590301_403939277_2_0_0&amp;highlighted_blocks=1311590301_403939277_2_0_0&amp;matching_block_id=1311590301_403939277_2_0_0&amp;sr_pri_blocks=1311590301_403939277_2_0_0__76798&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EasyTopStay - Porta Garibaldi Cozy Flat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/porta-garibaldi-grazioso-bilocale.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=191&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1138260701_386545476_1_0_0_852718&amp;highlighted_blocks=1138260701_386545476_1_0_0_852718&amp;matching_block_id=1138260701_386545476_1_0_0_852718&amp;sr_pri_blocks=1138260701_386545476_1_0_0_852718_53237&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Living La Corte Segreta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>156.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/buonarroti-la-corte-segreta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=193&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1451587401_416516876_1_0_0&amp;highlighted_blocks=1451587401_416516876_1_0_0&amp;matching_block_id=1451587401_416516876_1_0_0&amp;sr_pri_blocks=1451587401_416516876_1_0_0__78358&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Maisonette</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mi casa Cesalpino</x:t>
-  </x:si>
-  <x:si>
-    <x:t>117.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/mi-casa-cesalpino.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=196&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1454210002_416749810_1_0_0&amp;highlighted_blocks=1454210002_416749810_1_0_0&amp;matching_block_id=1454210002_416749810_1_0_0&amp;sr_pri_blocks=1454210002_416749810_1_0_0__58777&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EasyTopStay - Porta Romana Lovely Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>118.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/porta-romana-lovely-apartment.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=197&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1186688801_391031971_2_0_0_852711&amp;highlighted_blocks=1186688801_391031971_2_0_0_852711&amp;matching_block_id=1186688801_391031971_2_0_0_852711&amp;sr_pri_blocks=1186688801_391031971_2_0_0_852711_59358&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Luxurious Designer Studio - Centrale Station</x:t>
-  </x:si>
-  <x:si>
-    <x:t>112.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/luxurious-designer-studio-centrale-station.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=198&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=1492391701_420884423_2_0_0&amp;highlighted_blocks=1492391701_420884423_2_0_0&amp;matching_block_id=1492391701_420884423_2_0_0&amp;sr_pri_blocks=1492391701_420884423_2_0_0__56410&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Easylife - Milano - Pisacane 19 - Porta Venezia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>121.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/easy-life-elegante-trilocale-in-zona-porta-venezia.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuAK-ko7LBsACAdICJDFkYjVkMjg4LTUxODktNDk5OC05ZDg3LTMzZjVmZGY1YThjNdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=199&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=cdb96d2ae18a54b363bcf29f56b51da9&amp;srepoch=1768130949&amp;all_sr_blocks=952472502_411297279_2_0_0&amp;highlighted_blocks=952472502_411297279_2_0_0&amp;matching_block_id=952472502_411297279_2_0_0&amp;sr_pri_blocks=952472502_411297279_2_0_0__60745&amp;from=searchresults</x:t>
+    <x:t>https://www.booking.com/hotel/it/eleven-suites-cozy-apartments.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=196&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=1226394103_395701254_2_0_0&amp;highlighted_blocks=1226394103_395701254_2_0_0&amp;matching_block_id=1226394103_395701254_2_0_0&amp;sr_pri_blocks=1226394103_395701254_2_0_0__55806&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Algarotti 4 - Porta Nuova</x:t>
+  </x:si>
+  <x:si>
+    <x:t>131.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-moderno-e-fresco-trilocale-in-uno-dei-quartieri-piu-moderni-della-citta.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=197&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=924822002_411297083_2_0_0&amp;highlighted_blocks=924822002_411297083_2_0_0&amp;matching_block_id=924822002_411297083_2_0_0&amp;sr_pri_blocks=924822002_411297083_2_0_0__65872&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Rontgen 24D - Bocconi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-appartamento-in-bocconi.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=199&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=993685902_411297557_2_0_0&amp;highlighted_blocks=993685902_411297557_2_0_0&amp;matching_block_id=993685902_411297557_2_0_0&amp;sr_pri_blocks=993685902_411297557_2_0_0__56177&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Studio - Via Passarella 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments in San Babila</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brera-apartments-in-san-babila.html?label=gen173bo-10CAEoggI46AdIM1gDaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBmAICqAIBuALPr47LBsACAdICJGYyYmJiMjAyLWY1ZTMtNDQ5Yy1iNDg0LWM5Mzg0NzJhODkzONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=200&amp;sr_order=popularity&amp;nflt=ht_id%3D201&amp;srpvid=d8907e41348682bc1ebd4be5c00c05d4&amp;srepoch=1768134678&amp;all_sr_blocks=106267107_88400509_2_0_0&amp;highlighted_blocks=106267107_88400509_2_0_0&amp;matching_block_id=106267107_88400509_2_0_0&amp;sr_pri_blocks=106267107_88400509_2_0_0__81505&amp;from=searchresults</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1879,7 +2113,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F156"/>
+  <x:dimension ref="A1:F177"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:6">
@@ -1947,19 +2181,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -1967,19 +2201,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -1987,19 +2221,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -2007,19 +2241,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -2027,7 +2261,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>35</x:v>
@@ -2047,19 +2281,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -2067,7 +2301,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>44</x:v>
@@ -2076,7 +2310,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>46</x:v>
@@ -2087,7 +2321,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>47</x:v>
@@ -2096,10 +2330,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -2107,19 +2341,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="E12" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="F12" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -2127,7 +2361,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>55</x:v>
@@ -2136,7 +2370,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>57</x:v>
@@ -2167,19 +2401,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -2187,19 +2421,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -2210,16 +2444,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -2227,7 +2461,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>75</x:v>
@@ -2236,7 +2470,7 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>77</x:v>
@@ -2247,19 +2481,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C19" s="0" t="s">
+      <x:c r="D19" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D19" s="0" t="s">
+      <x:c r="E19" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
@@ -2267,19 +2501,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -2287,19 +2521,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -2307,19 +2541,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -2327,19 +2561,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -2347,19 +2581,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -2367,19 +2601,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -2387,19 +2621,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
@@ -2407,19 +2641,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
@@ -2427,19 +2661,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -2447,19 +2681,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -2467,19 +2701,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -2487,19 +2721,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
@@ -2507,19 +2741,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
@@ -2527,19 +2761,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
@@ -2547,19 +2781,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
@@ -2567,19 +2801,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
@@ -2587,19 +2821,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -2610,16 +2844,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -2627,19 +2861,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="D38" s="0" t="s">
+      <x:c r="E38" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -2647,7 +2881,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>151</x:v>
@@ -2656,10 +2890,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
@@ -2667,7 +2901,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>155</x:v>
@@ -2676,7 +2910,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>157</x:v>
@@ -2687,19 +2921,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>158</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="E41" s="0" t="s">
+      <x:c r="F41" s="0" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
@@ -2707,19 +2941,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="D42" s="0" t="s">
+      <x:c r="E42" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6">
@@ -2727,16 +2961,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="D43" s="0" t="s">
+      <x:c r="E43" s="0" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
         <x:v>167</x:v>
@@ -2747,7 +2981,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>168</x:v>
@@ -2756,10 +2990,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -2767,16 +3001,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
         <x:v>174</x:v>
@@ -2787,7 +3021,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>175</x:v>
@@ -2796,7 +3030,7 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
         <x:v>177</x:v>
@@ -2807,19 +3041,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="C47" s="0" t="s">
+      <x:c r="D47" s="0" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="D47" s="0" t="s">
+      <x:c r="E47" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F47" s="0" t="s">
-        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:6">
@@ -2827,19 +3061,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D48" s="0" t="s">
+      <x:c r="E48" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -2850,16 +3084,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6">
@@ -2867,19 +3101,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="D50" s="0" t="s">
+      <x:c r="F50" s="0" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:6">
@@ -2887,19 +3121,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="D51" s="0" t="s">
+      <x:c r="F51" s="0" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="E51" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F51" s="0" t="s">
-        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -2907,19 +3141,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="D52" s="0" t="s">
+      <x:c r="E52" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F52" s="0" t="s">
-        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -2927,16 +3161,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="C53" s="0" t="s">
+      <x:c r="D53" s="0" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D53" s="0" t="s">
+      <x:c r="E53" s="0" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
         <x:v>202</x:v>
@@ -2947,19 +3181,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>203</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -2967,19 +3201,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
@@ -2987,19 +3221,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:6">
@@ -3007,19 +3241,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:6">
@@ -3027,19 +3261,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -3047,19 +3281,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -3067,19 +3301,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -3087,19 +3321,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -3107,19 +3341,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -3127,19 +3361,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6">
@@ -3147,19 +3381,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:6">
@@ -3167,19 +3401,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -3187,19 +3421,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -3207,19 +3441,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -3227,19 +3461,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6">
@@ -3247,19 +3481,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:6">
@@ -3267,19 +3501,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:6">
@@ -3287,19 +3521,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
@@ -3307,19 +3541,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:6">
@@ -3327,19 +3561,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:6">
@@ -3347,19 +3581,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -3367,19 +3601,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
@@ -3387,19 +3621,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:6">
@@ -3407,19 +3641,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:6">
@@ -3430,16 +3664,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:6">
@@ -3447,19 +3681,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:6">
@@ -3467,19 +3701,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:6">
@@ -3487,19 +3721,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:6">
@@ -3507,19 +3741,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:6">
@@ -3527,19 +3761,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:6">
@@ -3547,19 +3781,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:6">
@@ -3567,19 +3801,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:6">
@@ -3590,16 +3824,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:6">
@@ -3607,19 +3841,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:6">
@@ -3627,19 +3861,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:6">
@@ -3647,19 +3881,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:6">
@@ -3667,19 +3901,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:6">
@@ -3687,19 +3921,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:6">
@@ -3707,19 +3941,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:6">
@@ -3727,19 +3961,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:6">
@@ -3747,19 +3981,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:6">
@@ -3767,19 +4001,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:6">
@@ -3787,19 +4021,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:6">
@@ -3807,19 +4041,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:6">
@@ -3827,19 +4061,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:6">
@@ -3847,19 +4081,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>347</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:6">
@@ -3867,19 +4101,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:6">
@@ -3887,19 +4121,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:6">
@@ -3907,19 +4141,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>359</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:6">
@@ -3927,19 +4161,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>362</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:6">
@@ -3947,19 +4181,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>364</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:6">
@@ -3967,19 +4201,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:6">
@@ -3987,19 +4221,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:6">
@@ -4007,19 +4241,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:6">
@@ -4027,19 +4261,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:6">
@@ -4047,19 +4281,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>379</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:6">
@@ -4067,19 +4301,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:6">
@@ -4087,19 +4321,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:6">
@@ -4107,19 +4341,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>389</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:6">
@@ -4127,19 +4361,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>392</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:6">
@@ -4147,19 +4381,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:6">
@@ -4167,19 +4401,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:6">
@@ -4187,19 +4421,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>401</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:6">
@@ -4207,19 +4441,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:6">
@@ -4227,19 +4461,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:6">
@@ -4247,19 +4481,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>411</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:6">
@@ -4267,19 +4501,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:6">
@@ -4287,19 +4521,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>418</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:6">
@@ -4307,19 +4541,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:6">
@@ -4327,19 +4561,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:6">
@@ -4347,19 +4581,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>427</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:6">
@@ -4367,19 +4601,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:6">
@@ -4387,19 +4621,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>433</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:6">
@@ -4410,16 +4644,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:6">
@@ -4430,16 +4664,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:6">
@@ -4447,19 +4681,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>442</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:6">
@@ -4467,19 +4701,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:6">
@@ -4487,19 +4721,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:6">
@@ -4507,19 +4741,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>451</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:6">
@@ -4527,19 +4761,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:6">
@@ -4547,19 +4781,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:6">
@@ -4567,19 +4801,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:6">
@@ -4587,19 +4821,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:6">
@@ -4607,19 +4841,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>466</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:6">
@@ -4627,19 +4861,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:6">
@@ -4647,19 +4881,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:6">
@@ -4667,19 +4901,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:6">
@@ -4687,19 +4921,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>478</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:6">
@@ -4707,19 +4941,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:6">
@@ -4727,19 +4961,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>482</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:6">
@@ -4747,19 +4981,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:6">
@@ -4767,19 +5001,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:6">
@@ -4787,19 +5021,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>491</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:6">
@@ -4807,19 +5041,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:6">
@@ -4827,19 +5061,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:6">
@@ -4847,19 +5081,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:6">
@@ -4867,19 +5101,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>503</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:6">
@@ -4887,19 +5121,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>507</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:6">
@@ -4907,19 +5141,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:6">
@@ -4927,19 +5161,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>512</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:6">
@@ -4947,19 +5181,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>515</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:6">
@@ -4967,19 +5201,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>518</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:6">
@@ -4990,16 +5224,436 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F156" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:6">
+      <x:c r="A157" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F156" s="0" t="s">
-        <x:v>504</x:v>
+      <x:c r="F157" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:6">
+      <x:c r="A158" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F158" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:6">
+      <x:c r="A159" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="E159" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F159" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:6">
+      <x:c r="A160" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F160" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:6">
+      <x:c r="A161" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F161" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:6">
+      <x:c r="A162" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F162" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:6">
+      <x:c r="A163" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E163" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F163" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:6">
+      <x:c r="A164" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F164" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:6">
+      <x:c r="A165" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F165" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:6">
+      <x:c r="A166" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F166" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:6">
+      <x:c r="A167" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F167" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:6">
+      <x:c r="A168" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F168" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:6">
+      <x:c r="A169" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F169" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:6">
+      <x:c r="A170" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F170" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:6">
+      <x:c r="A171" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F171" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:6">
+      <x:c r="A172" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F172" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:6">
+      <x:c r="A173" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F173" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:6">
+      <x:c r="A174" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="E174" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F174" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:6">
+      <x:c r="A175" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="E175" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F175" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:6">
+      <x:c r="A176" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="E176" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F176" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:6">
+      <x:c r="A177" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="E177" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F177" s="0" t="s">
+        <x:v>582</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
